--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -594,7 +594,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
         <v>1000</v>
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1">
         <v>2000</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,6 +115,18 @@
   </si>
   <si>
     <t>iconName</t>
+  </si>
+  <si>
+    <t>小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/1_69</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -472,7 +484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:H7"/>
+  <dimension ref="A2:H8"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -635,6 +647,32 @@
         <v>1</v>
       </c>
       <c r="H7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1">
+        <v>100</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,10 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Head/0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CharacterImage/1_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -102,14 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Head/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/head_20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CharacterImage/1_21</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,6 +115,56 @@
   <si>
     <t>CharacterImage/1_69</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Bussiness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>behavior</t>
+  </si>
+  <si>
+    <t>packageId</t>
+  </si>
+  <si>
+    <t>playerOperateEventId</t>
+  </si>
+  <si>
+    <t>nextTalkEventId</t>
+  </si>
+  <si>
+    <t>tempTalkEventId</t>
+  </si>
+  <si>
+    <t>shopName</t>
+  </si>
+  <si>
+    <t>functionIds</t>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
   </si>
 </sst>
 </file>
@@ -484,7 +522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:H8"/>
+  <dimension ref="A2:P8"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -494,10 +532,18 @@
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="7.75" style="1"/>
+    <col min="9" max="9" width="7.75" style="1"/>
+    <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -522,8 +568,32 @@
       <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -534,7 +604,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -548,8 +618,32 @@
       <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -560,13 +654,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -574,8 +668,29 @@
       <c r="H4" s="1">
         <v>0</v>
       </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -586,24 +701,45 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -612,24 +748,48 @@
         <v>1000</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>8001</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -638,10 +798,10 @@
         <v>2000</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -649,10 +809,34 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>200</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1">
         <v>100</v>
@@ -661,19 +845,40 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -165,13 +165,45 @@
   </si>
   <si>
     <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>CharacterImage/1_13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/1_59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +216,14 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2F2F2F"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -210,12 +250,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,7 +565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P8"/>
+  <dimension ref="A2:P10"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -745,7 +788,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
@@ -779,9 +822,6 @@
       </c>
       <c r="N6" s="1">
         <v>0</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>38</v>
@@ -795,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>20</v>
@@ -827,31 +867,28 @@
       <c r="N7" s="1">
         <v>200</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="P7" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
+      <c r="A8" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B8" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -877,7 +914,107 @@
       <c r="N8" s="1">
         <v>0</v>
       </c>
+      <c r="O8" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="P8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1">
+        <v>100</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,15 +187,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Prefabs/Character/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -615,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>0</v>
@@ -714,9 +718,6 @@
       <c r="I4" s="1">
         <v>0</v>
       </c>
-      <c r="J4" s="1">
-        <v>2</v>
-      </c>
       <c r="K4" s="1">
         <v>1</v>
       </c>
@@ -761,9 +762,6 @@
       <c r="I5" s="1">
         <v>0</v>
       </c>
-      <c r="J5" s="1">
-        <v>2</v>
-      </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
@@ -808,9 +806,6 @@
       <c r="I6" s="1">
         <v>0</v>
       </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
@@ -852,9 +847,6 @@
       <c r="I7" s="1">
         <v>0</v>
       </c>
-      <c r="J7" s="1">
-        <v>2</v>
-      </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
@@ -873,7 +865,7 @@
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -898,9 +890,6 @@
       </c>
       <c r="I8" s="1">
         <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>2</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -923,7 +912,7 @@
     </row>
     <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -938,7 +927,7 @@
         <v>42</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -949,17 +938,17 @@
       <c r="I9" s="1">
         <v>0</v>
       </c>
-      <c r="J9" s="1">
-        <v>2</v>
+      <c r="J9" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>8002</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>8002</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
@@ -967,8 +956,8 @@
       <c r="O9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P9" s="1">
-        <v>1</v>
+      <c r="P9" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -998,9 +987,6 @@
       </c>
       <c r="I10" s="1">
         <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>2</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -191,15 +191,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>NPC/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -865,7 +873,7 @@
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -891,14 +899,17 @@
       <c r="I8" s="1">
         <v>0</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>8003</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>8003</v>
       </c>
       <c r="N8" s="1">
         <v>0</v>
@@ -906,13 +917,13 @@
       <c r="O8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P8" s="1">
-        <v>1</v>
+      <c r="P8" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -939,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -998,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P10" s="1">
         <v>1</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -142,72 +142,73 @@
     <t>packageId</t>
   </si>
   <si>
+    <t>nextTalkEventId</t>
+  </si>
+  <si>
+    <t>tempTalkEventId</t>
+  </si>
+  <si>
+    <t>shopName</t>
+  </si>
+  <si>
+    <t>functionIds</t>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>CharacterImage/1_13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/1_59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>playerOperateEventId</t>
-  </si>
-  <si>
-    <t>nextTalkEventId</t>
-  </si>
-  <si>
-    <t>tempTalkEventId</t>
-  </si>
-  <si>
-    <t>shopName</t>
-  </si>
-  <si>
-    <t>functionIds</t>
-  </si>
-  <si>
-    <t>植物店</t>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>CharacterImage/1_13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldWoman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -645,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -683,19 +684,19 @@
         <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -827,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -873,7 +874,7 @@
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -882,14 +883,14 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
@@ -900,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -915,15 +916,15 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -932,25 +933,25 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -965,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -209,6 +209,10 @@
   </si>
   <si>
     <t>playerOperateEventId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fightBehavior</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -578,7 +582,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P10"/>
+  <dimension ref="A2:Q10"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -589,17 +593,17 @@
     <col min="7" max="7" width="10.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="7.75" style="1"/>
-    <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="7.75" style="1"/>
+    <col min="10" max="11" width="9.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="10.375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -631,7 +635,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>0</v>
@@ -643,13 +647,16 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -681,25 +688,28 @@
         <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -728,10 +738,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
@@ -739,11 +749,14 @@
       <c r="N4" s="1">
         <v>0</v>
       </c>
-      <c r="P4" s="1">
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -772,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
@@ -783,11 +796,14 @@
       <c r="N5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="1">
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -816,22 +832,25 @@
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
         <v>8001</v>
       </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
       <c r="N6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -857,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -866,13 +885,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
         <v>200</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -904,25 +926,28 @@
         <v>48</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="1">
-        <v>8003</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1">
         <v>8003</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1" t="s">
+        <v>8003</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>46</v>
       </c>
@@ -954,25 +979,28 @@
         <v>45</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="1">
-        <v>8002</v>
+        <v>0</v>
       </c>
       <c r="M9" s="1">
         <v>8002</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1" t="s">
+        <v>8002</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -1001,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1010,9 +1038,12 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
         <v>200</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -714,7 +714,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -761,7 +761,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -213,6 +213,18 @@
   </si>
   <si>
     <t>fightBehavior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/1_18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -582,7 +594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q10"/>
+  <dimension ref="A2:Q11"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -1044,6 +1056,50 @@
         <v>200</v>
       </c>
       <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q11" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -172,59 +172,103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerOperateEventId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fightBehavior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/1_18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Head/Boy4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Head/OldWoman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>playerOperateEventId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fightBehavior</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_18</t>
+    <t>Head/Girl1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/1_46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/1_51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q11"/>
+  <dimension ref="A2:Q13"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -700,13 +744,13 @@
         <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>32</v>
@@ -908,7 +952,7 @@
     </row>
     <row r="8" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -920,11 +964,11 @@
         <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
@@ -935,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" s="1">
         <v>2</v>
@@ -956,12 +1000,12 @@
         <v>36</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -973,22 +1017,22 @@
         <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="K9" s="1">
         <v>2</v>
@@ -1014,22 +1058,22 @@
     </row>
     <row r="10" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1040,6 +1084,9 @@
       <c r="I10" s="1">
         <v>0</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="K10" s="1">
         <v>2</v>
       </c>
@@ -1047,59 +1094,165 @@
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>8004</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>8004</v>
       </c>
       <c r="O10" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>8005</v>
+      </c>
+      <c r="N11" s="1">
+        <v>8005</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="1">
-        <v>3000</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>2</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="E13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
         <v>200</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q13" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -269,6 +269,22 @@
   </si>
   <si>
     <t>Prefabs/Character/小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/SmallChicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -638,7 +654,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q13"/>
+  <dimension ref="A2:Q14"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -1203,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="1">
         <v>1</v>
@@ -1223,7 +1239,7 @@
         <v>52</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>65</v>
@@ -1244,16 +1260,63 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="O13" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>8100</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8100</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -136,9 +136,6 @@
     <t>level</t>
   </si>
   <si>
-    <t>behavior</t>
-  </si>
-  <si>
     <t>packageId</t>
   </si>
   <si>
@@ -184,10 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NPC/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>布莱兹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -196,10 +189,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NPC/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>玛德琳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -236,18 +225,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NPC/丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/Character/格吉尔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NPC/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Head/Boy4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -272,10 +253,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>9,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Head/SmallChicken</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -285,6 +262,14 @@
   </si>
   <si>
     <t>Prefabs/Character/鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,9,10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -654,7 +639,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:Q14"/>
+  <dimension ref="A2:P14"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -665,17 +650,17 @@
     <col min="7" max="7" width="10.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="7.75" style="1"/>
-    <col min="10" max="11" width="9.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.375" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="7.75" style="1"/>
+    <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -707,7 +692,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>0</v>
@@ -719,16 +704,13 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,16 +739,16 @@
         <v>29</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="L3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>32</v>
@@ -777,11 +759,8 @@
       <c r="P3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="4" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -809,11 +788,14 @@
       <c r="I4" s="1">
         <v>0</v>
       </c>
+      <c r="J4" s="1">
+        <v>2</v>
+      </c>
       <c r="K4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
@@ -821,14 +803,11 @@
       <c r="N4" s="1">
         <v>0</v>
       </c>
-      <c r="O4" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="1">
+      <c r="P4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -856,11 +835,14 @@
       <c r="I5" s="1">
         <v>0</v>
       </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
       <c r="K5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
@@ -868,14 +850,11 @@
       <c r="N5" s="1">
         <v>0</v>
       </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
+      <c r="P5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -903,26 +882,26 @@
       <c r="I6" s="1">
         <v>0</v>
       </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
       <c r="K6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>8001</v>
       </c>
       <c r="M6" s="1">
-        <v>8001</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
       </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>37</v>
+      <c r="P6" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -947,8 +926,11 @@
       <c r="I7" s="1">
         <v>0</v>
       </c>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
       <c r="K7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -957,18 +939,15 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
         <v>200</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="P7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -977,14 +956,14 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
@@ -994,34 +973,31 @@
       <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>47</v>
+      <c r="J8" s="1">
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>8003</v>
       </c>
       <c r="M8" s="1">
         <v>8003</v>
       </c>
       <c r="N8" s="1">
-        <v>8003</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1030,13 +1006,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1047,34 +1023,31 @@
       <c r="I9" s="1">
         <v>0</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>44</v>
+      <c r="J9" s="1">
+        <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>8002</v>
       </c>
       <c r="M9" s="1">
         <v>8002</v>
       </c>
       <c r="N9" s="1">
-        <v>8002</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="10" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -1083,13 +1056,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1100,34 +1073,31 @@
       <c r="I10" s="1">
         <v>0</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>57</v>
+      <c r="J10" s="1">
+        <v>2</v>
       </c>
       <c r="K10" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>0</v>
+        <v>8004</v>
       </c>
       <c r="M10" s="1">
         <v>8004</v>
       </c>
       <c r="N10" s="1">
-        <v>8004</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1136,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1153,32 +1123,29 @@
       <c r="I11" s="1">
         <v>0</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>59</v>
+      <c r="J11" s="1">
+        <v>2</v>
       </c>
       <c r="K11" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>8005</v>
       </c>
       <c r="M11" s="1">
         <v>8005</v>
       </c>
       <c r="N11" s="1">
-        <v>8005</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1206,8 +1173,11 @@
       <c r="I12" s="1">
         <v>0</v>
       </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
       <c r="K12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -1218,16 +1188,13 @@
       <c r="N12" s="1">
         <v>0</v>
       </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
+      <c r="P12" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B13" s="1">
         <v>3000</v>
@@ -1236,13 +1203,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1253,28 +1220,28 @@
       <c r="I13" s="1">
         <v>0</v>
       </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
       <c r="K13" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M13" s="1">
         <v>8100</v>
       </c>
       <c r="N13" s="1">
-        <v>8100</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>66</v>
+        <v>0</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="27" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1">
         <v>3001</v>
@@ -1283,13 +1250,13 @@
         <v>0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1300,23 +1267,23 @@
       <c r="I14" s="1">
         <v>0</v>
       </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
       <c r="K14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M14" s="1">
         <v>8100</v>
       </c>
       <c r="N14" s="1">
-        <v>8100</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>66</v>
+        <v>0</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -261,15 +261,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/Character/鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4,9,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/母鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1">
         <v>3000</v>
@@ -1236,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -1256,7 +1256,7 @@
         <v>62</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -265,11 +265,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4,9,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/Character/母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,9,10,11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1236,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -1256,7 +1256,7 @@
         <v>62</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,26 +63,162 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Prefabs/Character/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconName</t>
+  </si>
+  <si>
+    <t>小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Bussiness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>packageId</t>
+  </si>
+  <si>
+    <t>nextTalkEventId</t>
+  </si>
+  <si>
+    <t>tempTalkEventId</t>
+  </si>
+  <si>
+    <t>shopName</t>
+  </si>
+  <si>
+    <t>functionIds</t>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerOperateEventId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fightBehavior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/SmallChicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,9,10,11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>主角女</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterImage/1_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_4</t>
+    <t>CharacterImage/主角女</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>班尼迪克</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/班尼迪克</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -90,102 +226,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/Character/马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_61</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iconName</t>
-  </si>
-  <si>
-    <t>小丑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_69</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldMan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Bussiness</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>packageId</t>
-  </si>
-  <si>
-    <t>nextTalkEventId</t>
-  </si>
-  <si>
-    <t>tempTalkEventId</t>
-  </si>
-  <si>
-    <t>shopName</t>
-  </si>
-  <si>
-    <t>functionIds</t>
-  </si>
-  <si>
-    <t>植物店</t>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>CharacterImage/1_13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldWoman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
+    <t>CharacterImage/马</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -193,19 +234,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>playerOperateEventId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fightBehavior</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_18</t>
+    <t>CharacterImage/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/丝特芬妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -213,63 +254,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>动物店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_46</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/1_51</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/SmallChicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Chicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,9,10,11</t>
+    <t>CharacterImage/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/母鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -707,7 +712,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -721,7 +726,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -736,28 +741,28 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -771,13 +776,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -809,22 +814,22 @@
     </row>
     <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -856,7 +861,7 @@
     </row>
     <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -865,13 +870,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -898,12 +903,12 @@
         <v>0</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -912,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -947,7 +952,7 @@
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -956,13 +961,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -989,15 +994,15 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1006,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1039,15 +1044,15 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -1056,13 +1061,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1089,15 +1094,15 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1106,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1139,15 +1144,15 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1">
         <v>100</v>
@@ -1156,13 +1161,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1203,13 +1208,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1236,12 +1241,12 @@
         <v>0</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B14" s="1">
         <v>3001</v>
@@ -1250,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1283,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="284">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,214 +75,922 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>小丑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Bussiness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>packageId</t>
+  </si>
+  <si>
+    <t>nextTalkEventId</t>
+  </si>
+  <si>
+    <t>tempTalkEventId</t>
+  </si>
+  <si>
+    <t>shopName</t>
+  </si>
+  <si>
+    <t>functionIds</t>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerOperateEventId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fightBehavior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/SmallChicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,9,10,11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterImage/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火烈鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鹿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺猬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>企鹅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>袋鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼兔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔女郎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莎拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制服小孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>女诗人</t>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>武道女</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杰克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+  </si>
+  <si>
+    <t>轻战士</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
     <t>iconName</t>
-  </si>
-  <si>
-    <t>小丑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鸭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/woman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家兔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+  </si>
+  <si>
+    <t>Head/公主</t>
+  </si>
+  <si>
+    <t>Head/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Head/国王</t>
+  </si>
+  <si>
+    <t>Head/天使</t>
+  </si>
+  <si>
+    <t>Head/女仆</t>
+  </si>
+  <si>
+    <t>Head/女骑士</t>
+  </si>
+  <si>
+    <t>Head/朵儿洁</t>
+  </si>
+  <si>
+    <t>Head/渔夫</t>
+  </si>
+  <si>
+    <t>Head/船长</t>
+  </si>
+  <si>
+    <t>Head/水手</t>
+  </si>
+  <si>
+    <t>Head/游侠</t>
+  </si>
+  <si>
+    <t>Head/牧师</t>
+  </si>
+  <si>
+    <t>Head/王子</t>
+  </si>
+  <si>
+    <t>Head/王后</t>
+  </si>
+  <si>
+    <t>Head/管家</t>
+  </si>
+  <si>
+    <t>Head/金发女</t>
+  </si>
+  <si>
+    <t>Head/鸭子</t>
+  </si>
+  <si>
+    <t>Head/绵羊</t>
+  </si>
+  <si>
+    <t>Head/猪</t>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+  </si>
+  <si>
+    <t>Head/马</t>
+  </si>
+  <si>
+    <t>Head/松鼠</t>
+  </si>
+  <si>
+    <t>Head/野兔</t>
+  </si>
+  <si>
+    <t>Head/火烈鸟</t>
+  </si>
+  <si>
+    <t>Head/鹿</t>
+  </si>
+  <si>
+    <t>Head/刺猬</t>
+  </si>
+  <si>
+    <t>Head/大象</t>
+  </si>
+  <si>
+    <t>Head/企鹅</t>
+  </si>
+  <si>
+    <t>Head/袋鼠</t>
+  </si>
+  <si>
+    <t>Head/Rabbit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/亚度尼斯</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/修女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/公主</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/国王</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/坎蒂丝</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/天使</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女仆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布拉德利</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布蓝达</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/希贝儿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/帕特里克</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/朵儿洁</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/梅林</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/渔夫</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/船长</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/水手</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/游侠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/爱格伯特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/牧师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王后</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/瓦尔特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/侦探</t>
   </si>
   <si>
     <t>Prefabs/Character/小丑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldMan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Bussiness</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>packageId</t>
-  </si>
-  <si>
-    <t>nextTalkEventId</t>
-  </si>
-  <si>
-    <t>tempTalkEventId</t>
-  </si>
-  <si>
-    <t>shopName</t>
-  </si>
-  <si>
-    <t>functionIds</t>
-  </si>
-  <si>
-    <t>植物店</t>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>Head/OldWoman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>playerOperateEventId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fightBehavior</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>动物店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Character/小鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/SmallChicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Chicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,9,10,11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/小丑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/小鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸭</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/白兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/松鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/野兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/火烈鸟</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/刺猬</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/大象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/企鹅</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/袋鼠</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +1009,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF2F2F2F"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -329,7 +1044,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -339,6 +1054,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -644,17 +1360,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P14"/>
+  <dimension ref="A2:P101"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.75" style="1"/>
+    <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="10.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="10.625" style="1" customWidth="1"/>
     <col min="12" max="12" width="13.375" style="1" customWidth="1"/>
@@ -712,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -726,7 +1441,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -741,28 +1456,28 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -776,10 +1491,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
@@ -814,7 +1529,7 @@
     </row>
     <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -823,10 +1538,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>11</v>
@@ -861,7 +1576,7 @@
     </row>
     <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -870,10 +1585,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>12</v>
@@ -903,12 +1618,12 @@
         <v>0</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -917,7 +1632,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -952,7 +1670,7 @@
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -961,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -994,15 +1712,15 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1011,13 +1729,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1044,15 +1762,15 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -1061,13 +1779,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1094,15 +1812,15 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1111,13 +1829,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1144,30 +1862,30 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1182,7 +1900,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -1199,22 +1917,22 @@
     </row>
     <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B13" s="1">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>42</v>
+        <v>196</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1229,66 +1947,4056 @@
         <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>46</v>
+      <c r="P13" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="1">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="1">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="1">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="1">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="1">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="1">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="1">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="1">
+        <v>19</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="1">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="1">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="1">
+        <v>22</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="1">
+        <v>23</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="1">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="1">
+        <v>26</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="1">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>2</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="1">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="1">
+        <v>29</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="1">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>2</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" s="1">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="1">
+        <v>32</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="1">
+        <v>33</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="1">
+        <v>34</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A38" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="1">
+        <v>35</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A39" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="1">
+        <v>36</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="1">
+        <v>37</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>2</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" s="1">
+        <v>38</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="1">
+        <v>39</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>2</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="1">
+        <v>40</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>2</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="1">
+        <v>41</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>2</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="1">
+        <v>42</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>2</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="1">
+        <v>43</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>2</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="1">
+        <v>44</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2</v>
+      </c>
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>2</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0</v>
+      </c>
+      <c r="P48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="1">
+        <v>47</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>2</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1">
+        <v>48</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>2</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="P51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="1">
+        <v>49</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="P52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="1">
+        <v>50</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>2</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" s="1">
+        <v>51</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>2</v>
+      </c>
+      <c r="K54" s="1">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0</v>
+      </c>
+      <c r="P54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="1">
+        <v>52</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>2</v>
+      </c>
+      <c r="K55" s="1">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="P55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="1">
+        <v>53</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G56" s="1">
+        <v>1</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>2</v>
+      </c>
+      <c r="K56" s="1">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A57" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" s="1">
+        <v>54</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <v>2</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="1">
+        <v>55</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G58" s="1">
+        <v>1</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>2</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0</v>
+      </c>
+      <c r="P58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B59" s="1">
+        <v>56</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G59" s="1">
+        <v>1</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>2</v>
+      </c>
+      <c r="K59" s="1">
+        <v>1</v>
+      </c>
+      <c r="L59" s="1">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>0</v>
+      </c>
+      <c r="P59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B60" s="1">
+        <v>57</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G60" s="1">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>2</v>
+      </c>
+      <c r="K60" s="1">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B61" s="1">
+        <v>58</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
+        <v>2</v>
+      </c>
+      <c r="K61" s="1">
+        <v>1</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" s="1">
+        <v>59</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>2</v>
+      </c>
+      <c r="K62" s="1">
+        <v>1</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" s="1">
+        <v>60</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="1">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
+        <v>2</v>
+      </c>
+      <c r="K63" s="1">
+        <v>1</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="1">
+        <v>61</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
+        <v>2</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1">
+        <v>0</v>
+      </c>
+      <c r="P64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="1">
+        <v>62</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>2</v>
+      </c>
+      <c r="K65" s="1">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="P65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" s="1">
+        <v>63</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>2</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A67" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" s="1">
+        <v>64</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <v>2</v>
+      </c>
+      <c r="K67" s="1">
+        <v>1</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A68" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" s="1">
         <v>65</v>
       </c>
-      <c r="B14" s="1">
+      <c r="C68" s="1">
+        <v>2</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>2</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="1">
+        <v>66</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
+        <v>2</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1</v>
+      </c>
+      <c r="L69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="P69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" s="1">
+        <v>67</v>
+      </c>
+      <c r="C70" s="1">
+        <v>2</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
+        <v>2</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="1">
+        <v>68</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
+        <v>2</v>
+      </c>
+      <c r="K71" s="1">
+        <v>1</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1">
+        <v>0</v>
+      </c>
+      <c r="P71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1">
+        <v>69</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
+        <v>2</v>
+      </c>
+      <c r="K72" s="1">
+        <v>1</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="P72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1">
+        <v>70</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <v>2</v>
+      </c>
+      <c r="K73" s="1">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0</v>
+      </c>
+      <c r="P73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A74" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="1">
+        <v>71</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
+        <v>2</v>
+      </c>
+      <c r="K74" s="1">
+        <v>1</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1">
+        <v>0</v>
+      </c>
+      <c r="N74" s="1">
+        <v>0</v>
+      </c>
+      <c r="P74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A75" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="1">
+        <v>72</v>
+      </c>
+      <c r="C75" s="1">
+        <v>2</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G75" s="1">
+        <v>1</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <v>2</v>
+      </c>
+      <c r="K75" s="1">
+        <v>1</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0</v>
+      </c>
+      <c r="P75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="1">
+        <v>73</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G76" s="1">
+        <v>1</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>2</v>
+      </c>
+      <c r="K76" s="1">
+        <v>1</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
+        <v>0</v>
+      </c>
+      <c r="P76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="1">
+        <v>100</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
+        <v>2</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+      <c r="L77" s="1">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1">
+        <v>0</v>
+      </c>
+      <c r="P77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A78" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+      <c r="I78" s="1">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <v>2</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>8100</v>
+      </c>
+      <c r="M78" s="1">
+        <v>8100</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="P78" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A79" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B79" s="1">
         <v>3001</v>
       </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C79" s="1">
+        <v>0</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>2</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>8100</v>
+      </c>
+      <c r="M79" s="1">
+        <v>8100</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="P79" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A80" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B80" s="3">
+        <v>3002</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G80" s="1">
+        <v>1</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1">
+        <v>2</v>
+      </c>
+      <c r="K80" s="1">
+        <v>0</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>0</v>
+      </c>
+      <c r="P80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A81" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="3">
+        <v>3003</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1">
+        <v>2</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A82" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B82" s="3">
+        <v>3004</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G82" s="1">
+        <v>1</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1">
+        <v>2</v>
+      </c>
+      <c r="K82" s="1">
+        <v>0</v>
+      </c>
+      <c r="L82" s="1">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1">
+        <v>0</v>
+      </c>
+      <c r="P82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A83" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="3">
+        <v>3005</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G83" s="1">
+        <v>1</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1">
+        <v>2</v>
+      </c>
+      <c r="K83" s="1">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1">
+        <v>0</v>
+      </c>
+      <c r="M83" s="1">
+        <v>0</v>
+      </c>
+      <c r="N83" s="1">
+        <v>0</v>
+      </c>
+      <c r="P83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A84" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B84" s="3">
+        <v>3006</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G84" s="1">
+        <v>1</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1">
+        <v>2</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0</v>
+      </c>
+      <c r="L84" s="1">
+        <v>0</v>
+      </c>
+      <c r="M84" s="1">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1">
+        <v>0</v>
+      </c>
+      <c r="P84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A85" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B85" s="3">
+        <v>3007</v>
+      </c>
+      <c r="C85" s="1">
+        <v>0</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G85" s="1">
+        <v>1</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1">
+        <v>2</v>
+      </c>
+      <c r="K85" s="1">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1">
+        <v>0</v>
+      </c>
+      <c r="P85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A86" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B86" s="3">
+        <v>3008</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G86" s="1">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1">
+        <v>2</v>
+      </c>
+      <c r="K86" s="1">
+        <v>0</v>
+      </c>
+      <c r="L86" s="1">
+        <v>0</v>
+      </c>
+      <c r="M86" s="1">
+        <v>0</v>
+      </c>
+      <c r="N86" s="1">
+        <v>0</v>
+      </c>
+      <c r="P86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A87" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B87" s="3">
+        <v>3009</v>
+      </c>
+      <c r="C87" s="1">
+        <v>0</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G87" s="1">
+        <v>1</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1">
+        <v>2</v>
+      </c>
+      <c r="K87" s="1">
+        <v>0</v>
+      </c>
+      <c r="L87" s="1">
+        <v>0</v>
+      </c>
+      <c r="M87" s="1">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1">
+        <v>0</v>
+      </c>
+      <c r="P87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A88" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B88" s="3">
+        <v>3010</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G88" s="1">
+        <v>1</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1">
+        <v>2</v>
+      </c>
+      <c r="K88" s="1">
+        <v>0</v>
+      </c>
+      <c r="L88" s="1">
+        <v>0</v>
+      </c>
+      <c r="M88" s="1">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1">
+        <v>0</v>
+      </c>
+      <c r="P88" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A89" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B89" s="3">
+        <v>3011</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G89" s="1">
+        <v>1</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1">
+        <v>2</v>
+      </c>
+      <c r="K89" s="1">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1">
+        <v>0</v>
+      </c>
+      <c r="M89" s="1">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1">
+        <v>0</v>
+      </c>
+      <c r="P89" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A90" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B90" s="3">
+        <v>3012</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G90" s="1">
+        <v>1</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1">
+        <v>2</v>
+      </c>
+      <c r="K90" s="1">
+        <v>0</v>
+      </c>
+      <c r="L90" s="1">
+        <v>0</v>
+      </c>
+      <c r="M90" s="1">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1">
+        <v>0</v>
+      </c>
+      <c r="P90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A91" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B91" s="3">
+        <v>3013</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G91" s="1">
+        <v>1</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1">
+        <v>2</v>
+      </c>
+      <c r="K91" s="1">
+        <v>0</v>
+      </c>
+      <c r="L91" s="1">
+        <v>0</v>
+      </c>
+      <c r="M91" s="1">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1">
+        <v>0</v>
+      </c>
+      <c r="P91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A92" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B92" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C92" s="1">
+        <v>0</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G92" s="1">
+        <v>1</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1">
+        <v>2</v>
+      </c>
+      <c r="K92" s="1">
+        <v>0</v>
+      </c>
+      <c r="L92" s="1">
+        <v>0</v>
+      </c>
+      <c r="M92" s="1">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1">
+        <v>0</v>
+      </c>
+      <c r="P92" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A93" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B93" s="3">
+        <v>3102</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G93" s="1">
+        <v>1</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1">
+        <v>2</v>
+      </c>
+      <c r="K93" s="1">
+        <v>0</v>
+      </c>
+      <c r="L93" s="1">
+        <v>0</v>
+      </c>
+      <c r="M93" s="1">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1">
+        <v>0</v>
+      </c>
+      <c r="P93" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A94" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" s="3">
+        <v>3104</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G94" s="1">
+        <v>1</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1">
+        <v>2</v>
+      </c>
+      <c r="K94" s="1">
+        <v>0</v>
+      </c>
+      <c r="L94" s="1">
+        <v>0</v>
+      </c>
+      <c r="M94" s="1">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1">
+        <v>0</v>
+      </c>
+      <c r="P94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A95" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B95" s="3">
+        <v>3106</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G95" s="1">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1">
+        <v>2</v>
+      </c>
+      <c r="K95" s="1">
+        <v>0</v>
+      </c>
+      <c r="L95" s="1">
+        <v>0</v>
+      </c>
+      <c r="M95" s="1">
+        <v>0</v>
+      </c>
+      <c r="N95" s="1">
+        <v>0</v>
+      </c>
+      <c r="P95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A96" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" s="3">
+        <v>3107</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G96" s="1">
+        <v>1</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1">
+        <v>2</v>
+      </c>
+      <c r="K96" s="1">
+        <v>0</v>
+      </c>
+      <c r="L96" s="1">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1">
+        <v>0</v>
+      </c>
+      <c r="P96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A97" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>8100</v>
-      </c>
-      <c r="M14" s="1">
-        <v>8100</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>46</v>
+      <c r="B97" s="3">
+        <v>3108</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G97" s="1">
+        <v>1</v>
+      </c>
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+      <c r="I97" s="1">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1">
+        <v>2</v>
+      </c>
+      <c r="K97" s="1">
+        <v>0</v>
+      </c>
+      <c r="L97" s="1">
+        <v>0</v>
+      </c>
+      <c r="M97" s="1">
+        <v>0</v>
+      </c>
+      <c r="N97" s="1">
+        <v>0</v>
+      </c>
+      <c r="P97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A98" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B98" s="3">
+        <v>3110</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G98" s="1">
+        <v>1</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1">
+        <v>2</v>
+      </c>
+      <c r="K98" s="1">
+        <v>0</v>
+      </c>
+      <c r="L98" s="1">
+        <v>0</v>
+      </c>
+      <c r="M98" s="1">
+        <v>0</v>
+      </c>
+      <c r="N98" s="1">
+        <v>0</v>
+      </c>
+      <c r="P98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A99" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" s="3">
+        <v>3111</v>
+      </c>
+      <c r="C99" s="1">
+        <v>0</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G99" s="1">
+        <v>1</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1">
+        <v>2</v>
+      </c>
+      <c r="K99" s="1">
+        <v>0</v>
+      </c>
+      <c r="L99" s="1">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1">
+        <v>0</v>
+      </c>
+      <c r="N99" s="1">
+        <v>0</v>
+      </c>
+      <c r="P99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A100" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B100" s="3">
+        <v>3112</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G100" s="1">
+        <v>1</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2</v>
+      </c>
+      <c r="K100" s="1">
+        <v>0</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1">
+        <v>0</v>
+      </c>
+      <c r="P100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A101" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B101" s="1">
+        <v>3114</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G101" s="1">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1">
+        <v>2</v>
+      </c>
+      <c r="K101" s="1">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1">
+        <v>0</v>
+      </c>
+      <c r="P101" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -334,9 +334,6 @@
     <t>匪徒</t>
   </si>
   <si>
-    <t>占卜婆婆</t>
-  </si>
-  <si>
     <t>双辫女孩</t>
   </si>
   <si>
@@ -984,6 +981,10 @@
   </si>
   <si>
     <t>Prefabs/Character/袋鼠</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1022,12 +1023,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1044,7 +1051,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1055,6 +1062,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1367,7 +1377,7 @@
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.375" style="1" customWidth="1"/>
     <col min="7" max="8" width="10.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="7.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
@@ -1441,7 +1451,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1575,7 +1585,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="1">
@@ -1623,7 +1633,7 @@
     </row>
     <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1635,7 +1645,7 @@
         <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -1835,7 +1845,7 @@
         <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1882,10 +1892,10 @@
         <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1929,10 +1939,10 @@
         <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1976,10 +1986,10 @@
         <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2011,7 +2021,7 @@
     </row>
     <row r="15" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2023,10 +2033,10 @@
         <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2058,7 +2068,7 @@
     </row>
     <row r="16" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" s="1">
         <v>13</v>
@@ -2070,10 +2080,10 @@
         <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2105,7 +2115,7 @@
     </row>
     <row r="17" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B17" s="1">
         <v>14</v>
@@ -2117,10 +2127,10 @@
         <v>55</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2152,7 +2162,7 @@
     </row>
     <row r="18" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
@@ -2164,10 +2174,10 @@
         <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2199,7 +2209,7 @@
     </row>
     <row r="19" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B19" s="1">
         <v>16</v>
@@ -2211,10 +2221,10 @@
         <v>55</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2246,7 +2256,7 @@
     </row>
     <row r="20" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2258,10 +2268,10 @@
         <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2293,7 +2303,7 @@
     </row>
     <row r="21" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2305,10 +2315,10 @@
         <v>55</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2340,7 +2350,7 @@
     </row>
     <row r="22" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2352,10 +2362,10 @@
         <v>55</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2387,7 +2397,7 @@
     </row>
     <row r="23" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2399,10 +2409,10 @@
         <v>55</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2434,7 +2444,7 @@
     </row>
     <row r="24" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2446,10 +2456,10 @@
         <v>55</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2481,7 +2491,7 @@
     </row>
     <row r="25" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2493,10 +2503,10 @@
         <v>55</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2528,7 +2538,7 @@
     </row>
     <row r="26" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2540,10 +2550,10 @@
         <v>55</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2575,7 +2585,7 @@
     </row>
     <row r="27" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2587,10 +2597,10 @@
         <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2622,7 +2632,7 @@
     </row>
     <row r="28" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2634,10 +2644,10 @@
         <v>55</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2669,7 +2679,7 @@
     </row>
     <row r="29" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2681,10 +2691,10 @@
         <v>55</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2716,7 +2726,7 @@
     </row>
     <row r="30" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2728,10 +2738,10 @@
         <v>55</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2763,7 +2773,7 @@
     </row>
     <row r="31" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -2775,10 +2785,10 @@
         <v>55</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2810,7 +2820,7 @@
     </row>
     <row r="32" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2822,10 +2832,10 @@
         <v>55</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2857,7 +2867,7 @@
     </row>
     <row r="33" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2869,10 +2879,10 @@
         <v>55</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2904,7 +2914,7 @@
     </row>
     <row r="34" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -2916,10 +2926,10 @@
         <v>55</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2951,7 +2961,7 @@
     </row>
     <row r="35" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -2963,10 +2973,10 @@
         <v>55</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -2998,7 +3008,7 @@
     </row>
     <row r="36" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -3010,10 +3020,10 @@
         <v>55</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -3044,8 +3054,8 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A37" s="1" t="s">
-        <v>118</v>
+      <c r="A37" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -3057,10 +3067,10 @@
         <v>55</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -3091,8 +3101,8 @@
       </c>
     </row>
     <row r="38" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A38" s="1" t="s">
-        <v>119</v>
+      <c r="A38" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -3104,10 +3114,10 @@
         <v>55</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -3138,8 +3148,8 @@
       </c>
     </row>
     <row r="39" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A39" s="1" t="s">
-        <v>122</v>
+      <c r="A39" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -3151,10 +3161,10 @@
         <v>55</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -3185,8 +3195,8 @@
       </c>
     </row>
     <row r="40" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A40" s="1" t="s">
-        <v>123</v>
+      <c r="A40" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -3198,10 +3208,10 @@
         <v>55</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -3232,8 +3242,8 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A41" s="1" t="s">
-        <v>128</v>
+      <c r="A41" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -3245,10 +3255,10 @@
         <v>55</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -3279,8 +3289,8 @@
       </c>
     </row>
     <row r="42" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A42" s="1" t="s">
-        <v>129</v>
+      <c r="A42" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3292,10 +3302,10 @@
         <v>55</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3326,8 +3336,8 @@
       </c>
     </row>
     <row r="43" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A43" s="1" t="s">
-        <v>131</v>
+      <c r="A43" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3339,10 +3349,10 @@
         <v>55</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3374,7 +3384,7 @@
     </row>
     <row r="44" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3386,7 +3396,7 @@
         <v>55</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3418,7 +3428,7 @@
     </row>
     <row r="45" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3430,7 +3440,7 @@
         <v>55</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3462,7 +3472,7 @@
     </row>
     <row r="46" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3474,7 +3484,7 @@
         <v>55</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3506,7 +3516,7 @@
     </row>
     <row r="47" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3518,7 +3528,7 @@
         <v>55</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3550,7 +3560,7 @@
     </row>
     <row r="48" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3562,7 +3572,7 @@
         <v>55</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3594,7 +3604,7 @@
     </row>
     <row r="49" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3606,7 +3616,7 @@
         <v>55</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3638,7 +3648,7 @@
     </row>
     <row r="50" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3650,7 +3660,7 @@
         <v>55</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3682,7 +3692,7 @@
     </row>
     <row r="51" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3694,7 +3704,7 @@
         <v>55</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3726,7 +3736,7 @@
     </row>
     <row r="52" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3738,7 +3748,7 @@
         <v>55</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3770,7 +3780,7 @@
     </row>
     <row r="53" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3782,7 +3792,7 @@
         <v>55</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3814,7 +3824,7 @@
     </row>
     <row r="54" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -3826,7 +3836,7 @@
         <v>55</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3858,7 +3868,7 @@
     </row>
     <row r="55" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -3870,7 +3880,7 @@
         <v>55</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -3902,7 +3912,7 @@
     </row>
     <row r="56" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -3914,7 +3924,7 @@
         <v>55</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3946,7 +3956,7 @@
     </row>
     <row r="57" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -3958,7 +3968,7 @@
         <v>55</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3990,7 +4000,7 @@
     </row>
     <row r="58" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -4002,7 +4012,7 @@
         <v>55</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -4034,7 +4044,7 @@
     </row>
     <row r="59" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -4046,7 +4056,7 @@
         <v>55</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -4078,7 +4088,7 @@
     </row>
     <row r="60" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -4090,7 +4100,7 @@
         <v>55</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -4122,7 +4132,7 @@
     </row>
     <row r="61" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -4134,7 +4144,7 @@
         <v>55</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -4166,7 +4176,7 @@
     </row>
     <row r="62" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -4178,7 +4188,7 @@
         <v>55</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -4210,7 +4220,7 @@
     </row>
     <row r="63" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -4222,7 +4232,7 @@
         <v>55</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -4254,7 +4264,7 @@
     </row>
     <row r="64" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -4266,7 +4276,7 @@
         <v>55</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4298,7 +4308,7 @@
     </row>
     <row r="65" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -4310,7 +4320,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -4342,7 +4352,7 @@
     </row>
     <row r="66" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -4354,7 +4364,7 @@
         <v>55</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -4386,7 +4396,7 @@
     </row>
     <row r="67" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -4398,7 +4408,7 @@
         <v>55</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -4430,7 +4440,7 @@
     </row>
     <row r="68" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -4442,7 +4452,7 @@
         <v>55</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -4474,7 +4484,7 @@
     </row>
     <row r="69" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B69" s="1">
         <v>66</v>
@@ -4486,7 +4496,7 @@
         <v>55</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -4518,7 +4528,7 @@
     </row>
     <row r="70" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B70" s="1">
         <v>67</v>
@@ -4530,7 +4540,7 @@
         <v>55</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -4574,7 +4584,7 @@
         <v>55</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -4618,7 +4628,7 @@
         <v>55</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -4662,7 +4672,7 @@
         <v>55</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -4706,7 +4716,7 @@
         <v>55</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -4750,7 +4760,7 @@
         <v>55</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -4794,7 +4804,7 @@
         <v>55</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4841,7 +4851,7 @@
         <v>17</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4888,7 +4898,7 @@
         <v>39</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4920,7 +4930,7 @@
     </row>
     <row r="79" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B79" s="1">
         <v>3001</v>
@@ -4935,7 +4945,7 @@
         <v>40</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4967,7 +4977,7 @@
     </row>
     <row r="80" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B80" s="3">
         <v>3002</v>
@@ -4979,10 +4989,10 @@
         <v>55</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G80" s="1">
         <v>1</v>
@@ -5014,7 +5024,7 @@
     </row>
     <row r="81" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" s="3">
         <v>3003</v>
@@ -5026,10 +5036,10 @@
         <v>55</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -5073,10 +5083,10 @@
         <v>55</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G82" s="1">
         <v>1</v>
@@ -5108,7 +5118,7 @@
     </row>
     <row r="83" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B83" s="3">
         <v>3005</v>
@@ -5120,10 +5130,10 @@
         <v>55</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G83" s="1">
         <v>1</v>
@@ -5155,7 +5165,7 @@
     </row>
     <row r="84" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B84" s="3">
         <v>3006</v>
@@ -5167,10 +5177,10 @@
         <v>55</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G84" s="1">
         <v>1</v>
@@ -5202,7 +5212,7 @@
     </row>
     <row r="85" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B85" s="3">
         <v>3007</v>
@@ -5214,10 +5224,10 @@
         <v>55</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -5249,7 +5259,7 @@
     </row>
     <row r="86" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B86" s="3">
         <v>3008</v>
@@ -5261,10 +5271,10 @@
         <v>55</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G86" s="1">
         <v>1</v>
@@ -5308,10 +5318,10 @@
         <v>55</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G87" s="1">
         <v>1</v>
@@ -5355,10 +5365,10 @@
         <v>55</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -5402,10 +5412,10 @@
         <v>55</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -5449,10 +5459,10 @@
         <v>55</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G90" s="1">
         <v>1</v>
@@ -5496,10 +5506,10 @@
         <v>55</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5543,10 +5553,10 @@
         <v>55</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5590,10 +5600,10 @@
         <v>55</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5637,10 +5647,10 @@
         <v>55</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -5684,10 +5694,10 @@
         <v>55</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -5731,10 +5741,10 @@
         <v>55</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -5778,10 +5788,10 @@
         <v>55</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -5825,10 +5835,10 @@
         <v>55</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5872,10 +5882,10 @@
         <v>55</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -5919,10 +5929,10 @@
         <v>55</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -5966,10 +5976,10 @@
         <v>55</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="330">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,10 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Head/OldMan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Head/Bussiness</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,55 +179,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterImage/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主角女</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterImage/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>班尼迪克</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterImage/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>玛德琳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterImage/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>丝特芬妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterImage/丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterImage/格吉尔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -303,9 +267,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>亚度尼斯</t>
-  </si>
-  <si>
     <t>侦探</t>
   </si>
   <si>
@@ -360,10 +321,6 @@
     <t>女轻战士</t>
   </si>
   <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>官员</t>
   </si>
   <si>
@@ -391,18 +348,6 @@
     <t>小花</t>
   </si>
   <si>
-    <t>布拉德利</t>
-  </si>
-  <si>
-    <t>布莱兹</t>
-  </si>
-  <si>
-    <t>布蓝达</t>
-  </si>
-  <si>
-    <t>帕特里克</t>
-  </si>
-  <si>
     <t>异国女子</t>
   </si>
   <si>
@@ -412,9 +357,6 @@
     <t>格斗家</t>
   </si>
   <si>
-    <t>梅林</t>
-  </si>
-  <si>
     <t>武士</t>
   </si>
   <si>
@@ -449,9 +391,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>瓦尔特</t>
-  </si>
-  <si>
     <t>阿普敦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -463,12 +402,6 @@
     <t>老英雄</t>
   </si>
   <si>
-    <t>艾琳娜</t>
-  </si>
-  <si>
-    <t>莱特</t>
-  </si>
-  <si>
     <t>贵族骑士</t>
   </si>
   <si>
@@ -481,19 +414,9 @@
     <t>重装战士</t>
   </si>
   <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-  </si>
-  <si>
     <t>骑士</t>
   </si>
   <si>
-    <t>黛芙妮</t>
-  </si>
-  <si>
     <t>iconName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -534,10 +457,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Head/Girl6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -567,10 +486,6 @@
   </si>
   <si>
     <t>Head/Girl4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -618,372 +533,619 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Head/公主</t>
+  </si>
+  <si>
+    <t>Head/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Head/国王</t>
+  </si>
+  <si>
+    <t>Head/天使</t>
+  </si>
+  <si>
+    <t>Head/女仆</t>
+  </si>
+  <si>
+    <t>Head/女骑士</t>
+  </si>
+  <si>
+    <t>Head/朵儿洁</t>
+  </si>
+  <si>
+    <t>Head/渔夫</t>
+  </si>
+  <si>
+    <t>Head/船长</t>
+  </si>
+  <si>
+    <t>Head/水手</t>
+  </si>
+  <si>
+    <t>Head/游侠</t>
+  </si>
+  <si>
+    <t>Head/牧师</t>
+  </si>
+  <si>
+    <t>Head/王子</t>
+  </si>
+  <si>
+    <t>Head/王后</t>
+  </si>
+  <si>
+    <t>Head/管家</t>
+  </si>
+  <si>
+    <t>Head/金发女</t>
+  </si>
+  <si>
+    <t>Head/鸭子</t>
+  </si>
+  <si>
+    <t>Head/绵羊</t>
+  </si>
+  <si>
+    <t>Head/猪</t>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+  </si>
+  <si>
+    <t>Head/马</t>
+  </si>
+  <si>
+    <t>Head/松鼠</t>
+  </si>
+  <si>
+    <t>Head/野兔</t>
+  </si>
+  <si>
+    <t>Head/火烈鸟</t>
+  </si>
+  <si>
+    <t>Head/鹿</t>
+  </si>
+  <si>
+    <t>Head/刺猬</t>
+  </si>
+  <si>
+    <t>Head/大象</t>
+  </si>
+  <si>
+    <t>Head/企鹅</t>
+  </si>
+  <si>
+    <t>Head/袋鼠</t>
+  </si>
+  <si>
+    <t>Head/Rabbit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/亚度尼斯</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/修女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/公主</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/国王</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/坎蒂丝</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/天使</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女仆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布拉德利</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布蓝达</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/希贝儿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/帕特里克</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/朵儿洁</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/梅林</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/渔夫</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/船长</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/水手</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/游侠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/爱格伯特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/牧师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王后</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/瓦尔特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/侦探</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸭</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/白兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/松鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/野兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/火烈鸟</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/刺猬</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/大象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/企鹅</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/袋鼠</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Head/修女</t>
-  </si>
-  <si>
-    <t>Head/公主</t>
-  </si>
-  <si>
-    <t>Head/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Head/国王</t>
-  </si>
-  <si>
-    <t>Head/天使</t>
-  </si>
-  <si>
-    <t>Head/女仆</t>
-  </si>
-  <si>
-    <t>Head/女骑士</t>
-  </si>
-  <si>
-    <t>Head/朵儿洁</t>
-  </si>
-  <si>
-    <t>Head/渔夫</t>
-  </si>
-  <si>
-    <t>Head/船长</t>
-  </si>
-  <si>
-    <t>Head/水手</t>
-  </si>
-  <si>
-    <t>Head/游侠</t>
-  </si>
-  <si>
-    <t>Head/牧师</t>
-  </si>
-  <si>
-    <t>Head/王子</t>
-  </si>
-  <si>
-    <t>Head/王后</t>
-  </si>
-  <si>
-    <t>Head/管家</t>
-  </si>
-  <si>
-    <t>Head/金发女</t>
-  </si>
-  <si>
-    <t>Head/鸭子</t>
-  </si>
-  <si>
-    <t>Head/绵羊</t>
-  </si>
-  <si>
-    <t>Head/猪</t>
-  </si>
-  <si>
-    <t>Head/奶牛</t>
-  </si>
-  <si>
-    <t>Head/马</t>
-  </si>
-  <si>
-    <t>Head/松鼠</t>
-  </si>
-  <si>
-    <t>Head/野兔</t>
-  </si>
-  <si>
-    <t>Head/火烈鸟</t>
-  </si>
-  <si>
-    <t>Head/鹿</t>
-  </si>
-  <si>
-    <t>Head/刺猬</t>
-  </si>
-  <si>
-    <t>Head/大象</t>
-  </si>
-  <si>
-    <t>Head/企鹅</t>
-  </si>
-  <si>
-    <t>Head/袋鼠</t>
-  </si>
-  <si>
-    <t>Head/Rabbit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/亚度尼斯</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/修女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/公主</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/国王</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/坎蒂丝</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/天使</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女仆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布拉德利</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布蓝达</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/希贝儿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/帕特里克</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/朵儿洁</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/梅林</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/渔夫</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/船长</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/水手</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/游侠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/爱格伯特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/牧师</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王后</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/瓦尔特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/管家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/艾琳娜</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/莱特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/金发女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/女仆</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/SmallChicken</t>
+  </si>
+  <si>
+    <t>Icon/Chicken</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/Rabbit</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/松鼠</t>
+  </si>
+  <si>
+    <t>Icon/野兔</t>
+  </si>
+  <si>
+    <t>Icon/火烈鸟</t>
+  </si>
+  <si>
+    <t>Icon/鹿</t>
+  </si>
+  <si>
+    <t>Icon/刺猬</t>
+  </si>
+  <si>
+    <t>Icon/大象</t>
+  </si>
+  <si>
+    <t>Icon/企鹅</t>
+  </si>
+  <si>
+    <t>Icon/袋鼠</t>
   </si>
   <si>
     <t>Prefabs/Character/黛芙妮</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/贵族骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老英雄</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老公公</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武道女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/格斗家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/战斗学者</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/异国女子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小花</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小美</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小混混</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/官员</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女诗人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/商人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/双辫女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/匪徒</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/制服小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔女郎</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/侦探</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸭</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/白兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/松鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/野兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/火烈鸟</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/刺猬</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/大象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/企鹅</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/袋鼠</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/坎蒂丝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1437,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
@@ -1451,7 +1613,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1466,31 +1628,31 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1501,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
@@ -1537,9 +1699,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1548,7 +1710,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>260</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1584,9 +1746,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1595,10 +1757,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>261</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>12</v>
@@ -1628,12 +1790,12 @@
         <v>0</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1642,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>262</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -1680,7 +1842,7 @@
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -1689,13 +1851,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>263</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1722,15 +1884,15 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1739,13 +1901,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>264</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1772,15 +1934,15 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -1789,13 +1951,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>265</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1822,15 +1984,15 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1839,13 +2001,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>258</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1872,15 +2034,15 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1889,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>267</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1925,9 +2087,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
@@ -1936,13 +2098,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>269</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1972,9 +2134,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B14" s="1">
         <v>11</v>
@@ -1983,13 +2145,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2019,9 +2181,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2030,13 +2192,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>271</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2066,9 +2228,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B16" s="1">
         <v>13</v>
@@ -2077,13 +2239,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>272</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2113,9 +2275,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B17" s="1">
         <v>14</v>
@@ -2124,13 +2286,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>329</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2160,9 +2322,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
@@ -2171,13 +2333,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>273</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2207,9 +2369,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>141</v>
+        <v>327</v>
       </c>
       <c r="B19" s="1">
         <v>16</v>
@@ -2218,13 +2380,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>328</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2254,9 +2416,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2265,13 +2427,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>274</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2301,9 +2463,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2312,13 +2474,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>326</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2348,9 +2510,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>100</v>
+        <v>323</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2359,13 +2521,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2395,9 +2557,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>101</v>
+        <v>321</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2406,13 +2568,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>55</v>
+        <v>322</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2442,9 +2604,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>102</v>
+        <v>319</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2453,13 +2615,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2489,9 +2651,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2500,13 +2662,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>55</v>
+        <v>318</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2536,9 +2698,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>103</v>
+        <v>316</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2547,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>55</v>
+        <v>317</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2583,9 +2745,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2594,13 +2756,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>275</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2630,9 +2792,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>107</v>
+        <v>314</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2641,13 +2803,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>55</v>
+        <v>315</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2677,9 +2839,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2688,13 +2850,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>55</v>
+        <v>276</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2724,9 +2886,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2735,13 +2897,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>55</v>
+        <v>277</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2771,9 +2933,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -2782,13 +2944,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>55</v>
+        <v>278</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2818,9 +2980,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2829,13 +2991,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>55</v>
+        <v>279</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2865,9 +3027,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>150</v>
+        <v>312</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2876,13 +3038,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>55</v>
+        <v>313</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2912,9 +3074,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -2923,13 +3085,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2959,9 +3121,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -2970,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -3006,9 +3168,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -3017,13 +3179,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>55</v>
+        <v>282</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -3053,9 +3215,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>117</v>
+        <v>310</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -3064,13 +3226,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>55</v>
+        <v>311</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -3100,9 +3262,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -3111,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>55</v>
+        <v>283</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -3147,9 +3309,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>121</v>
+        <v>308</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -3158,13 +3320,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -3194,9 +3356,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>122</v>
+        <v>306</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -3205,13 +3367,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -3241,9 +3403,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>127</v>
+        <v>304</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -3252,13 +3414,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>55</v>
+        <v>305</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -3288,9 +3450,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>128</v>
+        <v>302</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3299,13 +3461,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>55</v>
+        <v>303</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3335,9 +3497,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3346,13 +3508,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>55</v>
+        <v>301</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>225</v>
+        <v>299</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3382,9 +3544,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3392,11 +3554,8 @@
       <c r="C44" s="1">
         <v>1</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F44" s="1" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3426,9 +3585,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3436,11 +3595,8 @@
       <c r="C45" s="1">
         <v>1</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F45" s="1" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3470,9 +3626,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3480,11 +3636,8 @@
       <c r="C46" s="1">
         <v>2</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3514,9 +3667,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3524,11 +3677,8 @@
       <c r="C47" s="1">
         <v>1</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F47" s="1" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3558,9 +3708,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3568,11 +3718,8 @@
       <c r="C48" s="1">
         <v>1</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F48" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3602,9 +3749,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3612,11 +3759,8 @@
       <c r="C49" s="1">
         <v>1</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3646,9 +3790,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3656,11 +3800,8 @@
       <c r="C50" s="1">
         <v>1</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3690,9 +3831,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3700,11 +3841,8 @@
       <c r="C51" s="1">
         <v>1</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3734,9 +3872,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3744,11 +3882,8 @@
       <c r="C52" s="1">
         <v>2</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3778,9 +3913,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3788,11 +3923,8 @@
       <c r="C53" s="1">
         <v>1</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3822,9 +3954,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -3832,11 +3964,8 @@
       <c r="C54" s="1">
         <v>1</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3866,9 +3995,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -3876,11 +4005,8 @@
       <c r="C55" s="1">
         <v>1</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -3910,9 +4036,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -3920,11 +4046,8 @@
       <c r="C56" s="1">
         <v>2</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F56" s="1" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3954,9 +4077,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -3964,11 +4087,8 @@
       <c r="C57" s="1">
         <v>2</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3998,9 +4118,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -4008,11 +4128,8 @@
       <c r="C58" s="1">
         <v>2</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -4042,9 +4159,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -4052,11 +4169,8 @@
       <c r="C59" s="1">
         <v>1</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -4086,9 +4200,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -4096,11 +4210,8 @@
       <c r="C60" s="1">
         <v>1</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -4130,9 +4241,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -4140,11 +4251,8 @@
       <c r="C61" s="1">
         <v>1</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -4174,9 +4282,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -4184,11 +4292,8 @@
       <c r="C62" s="1">
         <v>1</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -4218,9 +4323,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -4228,11 +4333,8 @@
       <c r="C63" s="1">
         <v>2</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F63" s="1" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -4262,9 +4364,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -4272,11 +4374,8 @@
       <c r="C64" s="1">
         <v>2</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F64" s="1" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4306,9 +4405,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -4316,11 +4415,8 @@
       <c r="C65" s="1">
         <v>1</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -4350,9 +4446,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -4360,11 +4456,8 @@
       <c r="C66" s="1">
         <v>2</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F66" s="1" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -4394,9 +4487,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -4404,11 +4497,8 @@
       <c r="C67" s="1">
         <v>2</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -4438,9 +4528,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -4448,11 +4538,8 @@
       <c r="C68" s="1">
         <v>2</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -4482,9 +4569,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B69" s="1">
         <v>66</v>
@@ -4492,11 +4579,8 @@
       <c r="C69" s="1">
         <v>1</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F69" s="1" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -4526,9 +4610,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B70" s="1">
         <v>67</v>
@@ -4536,11 +4620,8 @@
       <c r="C70" s="1">
         <v>2</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F70" s="1" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -4570,9 +4651,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B71" s="1">
         <v>68</v>
@@ -4580,11 +4661,8 @@
       <c r="C71" s="1">
         <v>1</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -4614,9 +4692,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B72" s="1">
         <v>69</v>
@@ -4624,11 +4702,8 @@
       <c r="C72" s="1">
         <v>2</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F72" s="1" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -4658,9 +4733,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1">
         <v>70</v>
@@ -4668,11 +4743,8 @@
       <c r="C73" s="1">
         <v>1</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F73" s="1" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -4702,9 +4774,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B74" s="1">
         <v>71</v>
@@ -4712,11 +4784,8 @@
       <c r="C74" s="1">
         <v>1</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F74" s="1" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -4746,9 +4815,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B75" s="1">
         <v>72</v>
@@ -4756,11 +4825,8 @@
       <c r="C75" s="1">
         <v>2</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -4790,9 +4856,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B76" s="1">
         <v>73</v>
@@ -4800,11 +4866,8 @@
       <c r="C76" s="1">
         <v>1</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4834,7 +4897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>14</v>
       </c>
@@ -4844,14 +4907,8 @@
       <c r="C77" s="1">
         <v>1</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4883,7 +4940,7 @@
     </row>
     <row r="78" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B78" s="1">
         <v>3000</v>
@@ -4892,13 +4949,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>55</v>
+        <v>284</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4925,12 +4982,12 @@
         <v>0</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B79" s="1">
         <v>3001</v>
@@ -4939,13 +4996,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>55</v>
+        <v>285</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4972,12 +5029,12 @@
         <v>0</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B80" s="3">
         <v>3002</v>
@@ -4986,13 +5043,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="G80" s="1">
         <v>1</v>
@@ -5022,9 +5079,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B81" s="3">
         <v>3003</v>
@@ -5033,13 +5090,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -5069,9 +5126,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B82" s="3">
         <v>3004</v>
@@ -5080,13 +5137,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>55</v>
+        <v>287</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="G82" s="1">
         <v>1</v>
@@ -5116,9 +5173,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="B83" s="3">
         <v>3005</v>
@@ -5127,13 +5184,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>55</v>
+        <v>287</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="G83" s="1">
         <v>1</v>
@@ -5163,9 +5220,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="B84" s="3">
         <v>3006</v>
@@ -5174,13 +5231,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>55</v>
+        <v>288</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="G84" s="1">
         <v>1</v>
@@ -5210,9 +5267,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="B85" s="3">
         <v>3007</v>
@@ -5221,13 +5278,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>55</v>
+        <v>288</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -5257,9 +5314,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="B86" s="3">
         <v>3008</v>
@@ -5268,13 +5325,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>55</v>
+        <v>289</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="G86" s="1">
         <v>1</v>
@@ -5304,9 +5361,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B87" s="3">
         <v>3009</v>
@@ -5315,13 +5372,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>55</v>
+        <v>289</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="G87" s="1">
         <v>1</v>
@@ -5351,9 +5408,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B88" s="3">
         <v>3010</v>
@@ -5362,13 +5419,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -5398,9 +5455,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B89" s="3">
         <v>3011</v>
@@ -5409,13 +5466,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -5445,9 +5502,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B90" s="3">
         <v>3012</v>
@@ -5456,13 +5513,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>55</v>
+        <v>262</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="G90" s="1">
         <v>1</v>
@@ -5492,9 +5549,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B91" s="3">
         <v>3013</v>
@@ -5503,13 +5560,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>55</v>
+        <v>262</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5539,9 +5596,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B92" s="3">
         <v>3100</v>
@@ -5550,13 +5607,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>55</v>
+        <v>291</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5586,9 +5643,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B93" s="3">
         <v>3102</v>
@@ -5597,13 +5654,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>55</v>
+        <v>292</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5633,9 +5690,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B94" s="3">
         <v>3104</v>
@@ -5644,45 +5701,45 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G94" s="1">
+        <v>1</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1">
+        <v>2</v>
+      </c>
+      <c r="K94" s="1">
+        <v>0</v>
+      </c>
+      <c r="L94" s="1">
+        <v>0</v>
+      </c>
+      <c r="M94" s="1">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1">
+        <v>0</v>
+      </c>
+      <c r="P94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A95" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G94" s="1">
-        <v>1</v>
-      </c>
-      <c r="H94" s="1">
-        <v>0</v>
-      </c>
-      <c r="I94" s="1">
-        <v>0</v>
-      </c>
-      <c r="J94" s="1">
-        <v>2</v>
-      </c>
-      <c r="K94" s="1">
-        <v>0</v>
-      </c>
-      <c r="L94" s="1">
-        <v>0</v>
-      </c>
-      <c r="M94" s="1">
-        <v>0</v>
-      </c>
-      <c r="N94" s="1">
-        <v>0</v>
-      </c>
-      <c r="P94" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A95" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="B95" s="3">
         <v>3106</v>
@@ -5691,13 +5748,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>55</v>
+        <v>294</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -5727,9 +5784,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B96" s="3">
         <v>3107</v>
@@ -5738,13 +5795,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>55</v>
+        <v>294</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -5774,9 +5831,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B97" s="3">
         <v>3108</v>
@@ -5785,13 +5842,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>55</v>
+        <v>295</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -5821,9 +5878,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B98" s="3">
         <v>3110</v>
@@ -5832,13 +5889,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>55</v>
+        <v>296</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5868,9 +5925,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B99" s="3">
         <v>3111</v>
@@ -5879,13 +5936,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>55</v>
+        <v>296</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -5915,9 +5972,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B100" s="3">
         <v>3112</v>
@@ -5926,13 +5983,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>55</v>
+        <v>297</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -5962,9 +6019,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B101" s="1">
         <v>3114</v>
@@ -5973,13 +6030,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>55</v>
+        <v>298</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="350">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -814,339 +814,400 @@
     <t>Prefabs/Character/兔女郎</t>
   </si>
   <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸭</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/白兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/松鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/野兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/火烈鸟</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/刺猬</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/大象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/企鹅</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/袋鼠</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/女仆</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/SmallChicken</t>
+  </si>
+  <si>
+    <t>Icon/Chicken</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/Rabbit</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/松鼠</t>
+  </si>
+  <si>
+    <t>Icon/野兔</t>
+  </si>
+  <si>
+    <t>Icon/火烈鸟</t>
+  </si>
+  <si>
+    <t>Icon/鹿</t>
+  </si>
+  <si>
+    <t>Icon/刺猬</t>
+  </si>
+  <si>
+    <t>Icon/大象</t>
+  </si>
+  <si>
+    <t>Icon/企鹅</t>
+  </si>
+  <si>
+    <t>Icon/袋鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>魔族大将</t>
+  </si>
+  <si>
+    <t>魔族法师</t>
+  </si>
+  <si>
+    <t>魔族娃娃</t>
+  </si>
+  <si>
+    <t>女鬼</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>小精灵黄</t>
+  </si>
+  <si>
+    <t>邪恶法师</t>
+  </si>
+  <si>
+    <t>幽灵战士</t>
+  </si>
+  <si>
     <t>Prefabs/Character/侦探</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸭</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/白兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/松鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/野兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/火烈鸟</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/刺猬</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/大象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/企鹅</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/袋鼠</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/格吉尔</t>
-  </si>
-  <si>
-    <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/马</t>
-  </si>
-  <si>
-    <t>Icon/玛德琳</t>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-  </si>
-  <si>
-    <t>Icon/丝特芬妮</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/修女</t>
-  </si>
-  <si>
-    <t>Icon/公主</t>
-  </si>
-  <si>
-    <t>Icon/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Icon/国王</t>
-  </si>
-  <si>
-    <t>Icon/天使</t>
-  </si>
-  <si>
-    <t>Icon/女仆</t>
-  </si>
-  <si>
-    <t>Icon/朵儿洁</t>
-  </si>
-  <si>
-    <t>Icon/渔夫</t>
-  </si>
-  <si>
-    <t>Icon/船长</t>
-  </si>
-  <si>
-    <t>Icon/水手</t>
-  </si>
-  <si>
-    <t>Icon/游侠</t>
-  </si>
-  <si>
-    <t>Icon/牧师</t>
-  </si>
-  <si>
-    <t>Icon/王子</t>
-  </si>
-  <si>
-    <t>Icon/王后</t>
-  </si>
-  <si>
-    <t>Icon/管家</t>
-  </si>
-  <si>
-    <t>Icon/SmallChicken</t>
-  </si>
-  <si>
-    <t>Icon/Chicken</t>
-  </si>
-  <si>
-    <t>Icon/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/Rabbit</t>
-  </si>
-  <si>
-    <t>Icon/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/猪</t>
-  </si>
-  <si>
-    <t>Icon/奶牛</t>
-  </si>
-  <si>
-    <t>Icon/松鼠</t>
-  </si>
-  <si>
-    <t>Icon/野兔</t>
-  </si>
-  <si>
-    <t>Icon/火烈鸟</t>
-  </si>
-  <si>
-    <t>Icon/鹿</t>
-  </si>
-  <si>
-    <t>Icon/刺猬</t>
-  </si>
-  <si>
-    <t>Icon/大象</t>
-  </si>
-  <si>
-    <t>Icon/企鹅</t>
-  </si>
-  <si>
-    <t>Icon/袋鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鬼族男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/魔族大将</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/魔族法师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/魔族娃娃</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女鬼</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女魔族</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小精灵红</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小精灵黄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/邪恶法师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幽灵战士</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P101"/>
+  <dimension ref="A2:P111"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -1663,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
@@ -1710,7 +1771,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1757,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1793,7 +1854,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>114</v>
       </c>
@@ -1804,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>115</v>
@@ -1840,7 +1901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
@@ -1851,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>27</v>
@@ -1890,7 +1951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -1901,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>35</v>
@@ -1940,7 +2001,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>45</v>
       </c>
@@ -1951,7 +2012,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>36</v>
@@ -1990,7 +2051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -2001,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
@@ -2042,7 +2103,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -2051,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>116</v>
@@ -2098,10 +2159,10 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>170</v>
@@ -2145,7 +2206,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>138</v>
@@ -2183,7 +2244,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2192,7 +2253,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>139</v>
@@ -2239,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>140</v>
@@ -2286,7 +2347,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>118</v>
@@ -2333,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>141</v>
@@ -2371,7 +2432,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B19" s="1">
         <v>16</v>
@@ -2380,7 +2441,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>119</v>
@@ -2427,7 +2488,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>142</v>
@@ -2465,7 +2526,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2474,7 +2535,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>143</v>
@@ -2512,7 +2573,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2521,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>120</v>
@@ -2559,7 +2620,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2568,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>121</v>
@@ -2606,7 +2667,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2615,7 +2676,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>123</v>
@@ -2662,7 +2723,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>124</v>
@@ -2700,7 +2761,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2709,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>125</v>
@@ -2756,7 +2817,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>144</v>
@@ -2794,7 +2855,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2803,7 +2864,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>126</v>
@@ -2850,7 +2911,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>145</v>
@@ -2897,7 +2958,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>146</v>
@@ -2944,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>147</v>
@@ -2991,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>148</v>
@@ -3029,7 +3090,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -3038,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>127</v>
@@ -3085,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>149</v>
@@ -3132,7 +3193,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>150</v>
@@ -3179,7 +3240,7 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>151</v>
@@ -3217,7 +3278,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -3226,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>129</v>
@@ -3273,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>152</v>
@@ -3311,7 +3372,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -3320,7 +3381,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>130</v>
@@ -3358,7 +3419,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -3367,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>131</v>
@@ -3405,7 +3466,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -3414,7 +3475,7 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>153</v>
@@ -3452,7 +3513,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3461,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>132</v>
@@ -3499,7 +3560,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3508,13 +3569,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -4867,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>231</v>
+        <v>339</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4898,17 +4959,17 @@
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A77" s="1" t="s">
-        <v>14</v>
+      <c r="A77" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="B77" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>232</v>
+        <v>340</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4923,7 +4984,7 @@
         <v>2</v>
       </c>
       <c r="K77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="1">
         <v>0</v>
@@ -4938,24 +4999,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A78" s="1" t="s">
-        <v>49</v>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A78" s="3" t="s">
+        <v>330</v>
       </c>
       <c r="B78" s="1">
-        <v>3000</v>
+        <v>201</v>
       </c>
       <c r="C78" s="1">
-        <v>0</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>233</v>
+        <v>341</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4970,39 +5025,33 @@
         <v>2</v>
       </c>
       <c r="K78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M78" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N78" s="1">
         <v>0</v>
       </c>
-      <c r="P78" s="1" t="s">
-        <v>40</v>
+      <c r="P78" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A79" s="1" t="s">
-        <v>113</v>
+      <c r="A79" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="B79" s="1">
-        <v>3001</v>
+        <v>202</v>
       </c>
       <c r="C79" s="1">
-        <v>0</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>234</v>
+        <v>342</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -5017,39 +5066,33 @@
         <v>2</v>
       </c>
       <c r="K79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M79" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N79" s="1">
         <v>0</v>
       </c>
-      <c r="P79" s="1" t="s">
-        <v>40</v>
+      <c r="P79" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A80" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B80" s="3">
-        <v>3002</v>
+      <c r="A80" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B80" s="1">
+        <v>203</v>
       </c>
       <c r="C80" s="1">
-        <v>0</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>235</v>
+        <v>343</v>
       </c>
       <c r="G80" s="1">
         <v>1</v>
@@ -5064,7 +5107,7 @@
         <v>2</v>
       </c>
       <c r="K80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="1">
         <v>0</v>
@@ -5080,23 +5123,17 @@
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A81" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B81" s="3">
-        <v>3003</v>
+      <c r="A81" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B81" s="1">
+        <v>204</v>
       </c>
       <c r="C81" s="1">
-        <v>0</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -5111,7 +5148,7 @@
         <v>2</v>
       </c>
       <c r="K81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="1">
         <v>0</v>
@@ -5128,22 +5165,16 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B82" s="3">
-        <v>3004</v>
+        <v>334</v>
+      </c>
+      <c r="B82" s="1">
+        <v>205</v>
       </c>
       <c r="C82" s="1">
-        <v>0</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>237</v>
+        <v>345</v>
       </c>
       <c r="G82" s="1">
         <v>1</v>
@@ -5158,7 +5189,7 @@
         <v>2</v>
       </c>
       <c r="K82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="1">
         <v>0</v>
@@ -5175,22 +5206,16 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B83" s="3">
-        <v>3005</v>
+        <v>335</v>
+      </c>
+      <c r="B83" s="1">
+        <v>206</v>
       </c>
       <c r="C83" s="1">
-        <v>0</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="G83" s="1">
         <v>1</v>
@@ -5205,7 +5230,7 @@
         <v>2</v>
       </c>
       <c r="K83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="1">
         <v>0</v>
@@ -5221,23 +5246,17 @@
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A84" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B84" s="3">
-        <v>3006</v>
+      <c r="A84" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B84" s="1">
+        <v>207</v>
       </c>
       <c r="C84" s="1">
-        <v>0</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>239</v>
+        <v>347</v>
       </c>
       <c r="G84" s="1">
         <v>1</v>
@@ -5252,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="K84" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="1">
         <v>0</v>
@@ -5268,23 +5287,17 @@
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A85" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B85" s="3">
-        <v>3007</v>
+      <c r="A85" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B85" s="1">
+        <v>208</v>
       </c>
       <c r="C85" s="1">
-        <v>0</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>240</v>
+        <v>348</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -5299,7 +5312,7 @@
         <v>2</v>
       </c>
       <c r="K85" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="1">
         <v>0</v>
@@ -5315,23 +5328,17 @@
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A86" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B86" s="3">
-        <v>3008</v>
+      <c r="A86" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B86" s="1">
+        <v>209</v>
       </c>
       <c r="C86" s="1">
-        <v>0</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>241</v>
+        <v>349</v>
       </c>
       <c r="G86" s="1">
         <v>1</v>
@@ -5346,7 +5353,7 @@
         <v>2</v>
       </c>
       <c r="K86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="1">
         <v>0</v>
@@ -5363,22 +5370,16 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B87" s="3">
-        <v>3009</v>
+        <v>14</v>
+      </c>
+      <c r="B87" s="1">
+        <v>100</v>
       </c>
       <c r="C87" s="1">
-        <v>0</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G87" s="1">
         <v>1</v>
@@ -5408,24 +5409,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B88" s="3">
-        <v>3010</v>
+        <v>49</v>
+      </c>
+      <c r="B88" s="1">
+        <v>3000</v>
       </c>
       <c r="C88" s="1">
         <v>0</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -5443,36 +5444,36 @@
         <v>0</v>
       </c>
       <c r="L88" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M88" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N88" s="1">
         <v>0</v>
       </c>
-      <c r="P88" s="1">
-        <v>1</v>
+      <c r="P88" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B89" s="3">
-        <v>3011</v>
+        <v>113</v>
+      </c>
+      <c r="B89" s="1">
+        <v>3001</v>
       </c>
       <c r="C89" s="1">
         <v>0</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -5490,36 +5491,36 @@
         <v>0</v>
       </c>
       <c r="L89" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M89" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N89" s="1">
         <v>0</v>
       </c>
-      <c r="P89" s="1">
-        <v>1</v>
+      <c r="P89" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="B90" s="3">
-        <v>3012</v>
+        <v>3002</v>
       </c>
       <c r="C90" s="1">
         <v>0</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="G90" s="1">
         <v>1</v>
@@ -5551,22 +5552,22 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="B91" s="3">
-        <v>3013</v>
+        <v>3003</v>
       </c>
       <c r="C91" s="1">
         <v>0</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5597,23 +5598,23 @@
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A92" s="1" t="s">
-        <v>52</v>
+      <c r="A92" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="B92" s="3">
-        <v>3100</v>
+        <v>3004</v>
       </c>
       <c r="C92" s="1">
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5644,23 +5645,23 @@
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A93" s="1" t="s">
-        <v>53</v>
+      <c r="A93" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="B93" s="3">
-        <v>3102</v>
+        <v>3005</v>
       </c>
       <c r="C93" s="1">
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5692,22 +5693,22 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B94" s="3">
-        <v>3104</v>
+        <v>3006</v>
       </c>
       <c r="C94" s="1">
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -5739,22 +5740,22 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="B95" s="3">
-        <v>3106</v>
+        <v>3007</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -5786,22 +5787,22 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="B96" s="3">
-        <v>3107</v>
+        <v>3008</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -5833,22 +5834,22 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B97" s="3">
-        <v>3108</v>
+        <v>3009</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -5880,22 +5881,22 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B98" s="3">
-        <v>3110</v>
+        <v>3010</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5927,22 +5928,22 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B99" s="3">
-        <v>3111</v>
+        <v>3011</v>
       </c>
       <c r="C99" s="1">
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -5974,22 +5975,22 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B100" s="3">
-        <v>3112</v>
+        <v>3012</v>
       </c>
       <c r="C100" s="1">
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -6021,48 +6022,518 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B101" s="3">
+        <v>3013</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G101" s="1">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1">
+        <v>2</v>
+      </c>
+      <c r="K101" s="1">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1">
+        <v>0</v>
+      </c>
+      <c r="P101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A102" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G102" s="1">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1">
+        <v>2</v>
+      </c>
+      <c r="K102" s="1">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1">
+        <v>0</v>
+      </c>
+      <c r="M102" s="1">
+        <v>0</v>
+      </c>
+      <c r="N102" s="1">
+        <v>0</v>
+      </c>
+      <c r="P102" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A103" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B103" s="3">
+        <v>3102</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G103" s="1">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1">
+        <v>2</v>
+      </c>
+      <c r="K103" s="1">
+        <v>0</v>
+      </c>
+      <c r="L103" s="1">
+        <v>0</v>
+      </c>
+      <c r="M103" s="1">
+        <v>0</v>
+      </c>
+      <c r="N103" s="1">
+        <v>0</v>
+      </c>
+      <c r="P103" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A104" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B104" s="3">
+        <v>3104</v>
+      </c>
+      <c r="C104" s="1">
+        <v>0</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G104" s="1">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1">
+        <v>2</v>
+      </c>
+      <c r="K104" s="1">
+        <v>0</v>
+      </c>
+      <c r="L104" s="1">
+        <v>0</v>
+      </c>
+      <c r="M104" s="1">
+        <v>0</v>
+      </c>
+      <c r="N104" s="1">
+        <v>0</v>
+      </c>
+      <c r="P104" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A105" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B105" s="3">
+        <v>3106</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G105" s="1">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1">
+        <v>2</v>
+      </c>
+      <c r="K105" s="1">
+        <v>0</v>
+      </c>
+      <c r="L105" s="1">
+        <v>0</v>
+      </c>
+      <c r="M105" s="1">
+        <v>0</v>
+      </c>
+      <c r="N105" s="1">
+        <v>0</v>
+      </c>
+      <c r="P105" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A106" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B106" s="3">
+        <v>3107</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G106" s="1">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1">
+        <v>2</v>
+      </c>
+      <c r="K106" s="1">
+        <v>0</v>
+      </c>
+      <c r="L106" s="1">
+        <v>0</v>
+      </c>
+      <c r="M106" s="1">
+        <v>0</v>
+      </c>
+      <c r="N106" s="1">
+        <v>0</v>
+      </c>
+      <c r="P106" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A107" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B107" s="3">
+        <v>3108</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G107" s="1">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1">
+        <v>2</v>
+      </c>
+      <c r="K107" s="1">
+        <v>0</v>
+      </c>
+      <c r="L107" s="1">
+        <v>0</v>
+      </c>
+      <c r="M107" s="1">
+        <v>0</v>
+      </c>
+      <c r="N107" s="1">
+        <v>0</v>
+      </c>
+      <c r="P107" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A108" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B108" s="3">
+        <v>3110</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G108" s="1">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1">
+        <v>2</v>
+      </c>
+      <c r="K108" s="1">
+        <v>0</v>
+      </c>
+      <c r="L108" s="1">
+        <v>0</v>
+      </c>
+      <c r="M108" s="1">
+        <v>0</v>
+      </c>
+      <c r="N108" s="1">
+        <v>0</v>
+      </c>
+      <c r="P108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A109" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B109" s="3">
+        <v>3111</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G109" s="1">
+        <v>1</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1">
+        <v>0</v>
+      </c>
+      <c r="J109" s="1">
+        <v>2</v>
+      </c>
+      <c r="K109" s="1">
+        <v>0</v>
+      </c>
+      <c r="L109" s="1">
+        <v>0</v>
+      </c>
+      <c r="M109" s="1">
+        <v>0</v>
+      </c>
+      <c r="N109" s="1">
+        <v>0</v>
+      </c>
+      <c r="P109" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A110" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B110" s="3">
+        <v>3112</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G110" s="1">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1">
+        <v>2</v>
+      </c>
+      <c r="K110" s="1">
+        <v>0</v>
+      </c>
+      <c r="L110" s="1">
+        <v>0</v>
+      </c>
+      <c r="M110" s="1">
+        <v>0</v>
+      </c>
+      <c r="N110" s="1">
+        <v>0</v>
+      </c>
+      <c r="P110" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A111" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B111" s="1">
         <v>3114</v>
       </c>
-      <c r="C101" s="1">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="C111" s="1">
+        <v>0</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G101" s="1">
-        <v>1</v>
-      </c>
-      <c r="H101" s="1">
-        <v>0</v>
-      </c>
-      <c r="I101" s="1">
-        <v>0</v>
-      </c>
-      <c r="J101" s="1">
-        <v>2</v>
-      </c>
-      <c r="K101" s="1">
-        <v>0</v>
-      </c>
-      <c r="L101" s="1">
-        <v>0</v>
-      </c>
-      <c r="M101" s="1">
-        <v>0</v>
-      </c>
-      <c r="N101" s="1">
-        <v>0</v>
-      </c>
-      <c r="P101" s="1">
+      <c r="F111" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G111" s="1">
+        <v>1</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1">
+        <v>0</v>
+      </c>
+      <c r="J111" s="1">
+        <v>2</v>
+      </c>
+      <c r="K111" s="1">
+        <v>0</v>
+      </c>
+      <c r="L111" s="1">
+        <v>0</v>
+      </c>
+      <c r="M111" s="1">
+        <v>0</v>
+      </c>
+      <c r="N111" s="1">
+        <v>0</v>
+      </c>
+      <c r="P111" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="351">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1155,12 +1155,6 @@
     <t>魔族法师</t>
   </si>
   <si>
-    <t>魔族娃娃</t>
-  </si>
-  <si>
-    <t>女鬼</t>
-  </si>
-  <si>
     <t>女魔族</t>
   </si>
   <si>
@@ -1170,9 +1164,6 @@
     <t>小精灵黄</t>
   </si>
   <si>
-    <t>邪恶法师</t>
-  </si>
-  <si>
     <t>幽灵战士</t>
   </si>
   <si>
@@ -1189,12 +1180,6 @@
     <t>Prefabs/Character/魔族法师</t>
   </si>
   <si>
-    <t>Prefabs/Character/魔族娃娃</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女鬼</t>
-  </si>
-  <si>
     <t>Prefabs/Character/女魔族</t>
   </si>
   <si>
@@ -1204,10 +1189,32 @@
     <t>Prefabs/Character/小精灵黄</t>
   </si>
   <si>
-    <t>Prefabs/Character/邪恶法师</t>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
   </si>
   <si>
     <t>Prefabs/Character/幽灵战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1593,7 +1600,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P111"/>
+  <dimension ref="A2:P115"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -4928,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4969,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -5010,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -5051,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -5086,13 +5093,13 @@
         <v>332</v>
       </c>
       <c r="B80" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C80" s="1">
         <v>2</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G80" s="1">
         <v>1</v>
@@ -5127,13 +5134,13 @@
         <v>333</v>
       </c>
       <c r="B81" s="1">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C81" s="1">
         <v>2</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -5168,13 +5175,13 @@
         <v>334</v>
       </c>
       <c r="B82" s="1">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G82" s="1">
         <v>1</v>
@@ -5209,13 +5216,13 @@
         <v>335</v>
       </c>
       <c r="B83" s="1">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G83" s="1">
         <v>1</v>
@@ -5247,16 +5254,17 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B84" s="1">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C84" s="1">
         <v>2</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>347</v>
+      <c r="F84" s="1" t="str">
+        <f>"Prefabs/Character/"&amp;A84</f>
+        <v>Prefabs/Character/中年路人女</v>
       </c>
       <c r="G84" s="1">
         <v>1</v>
@@ -5288,16 +5296,17 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B85" s="1">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C85" s="1">
         <v>1</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>348</v>
+      <c r="F85" s="1" t="str">
+        <f t="shared" ref="F85:F90" si="0">"Prefabs/Character/"&amp;A85</f>
+        <v>Prefabs/Character/中年路人男</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -5329,16 +5338,17 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B86" s="1">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>349</v>
+        <v>2</v>
+      </c>
+      <c r="F86" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/红发小孩</v>
       </c>
       <c r="G86" s="1">
         <v>1</v>
@@ -5369,17 +5379,18 @@
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A87" s="1" t="s">
-        <v>14</v>
+      <c r="A87" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="B87" s="1">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>231</v>
+      <c r="F87" s="1" t="str">
+        <f>"Prefabs/Character/"&amp;A87</f>
+        <v>Prefabs/Character/纺织婆婆</v>
       </c>
       <c r="G87" s="1">
         <v>1</v>
@@ -5394,7 +5405,7 @@
         <v>2</v>
       </c>
       <c r="K87" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="1">
         <v>0</v>
@@ -5409,24 +5420,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A88" s="1" t="s">
-        <v>49</v>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A88" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="B88" s="1">
-        <v>3000</v>
+        <v>214</v>
       </c>
       <c r="C88" s="1">
-        <v>0</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>232</v>
+        <v>2</v>
+      </c>
+      <c r="F88" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/路人女</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -5441,39 +5447,34 @@
         <v>2</v>
       </c>
       <c r="K88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M88" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N88" s="1">
         <v>0</v>
       </c>
-      <c r="P88" s="1" t="s">
-        <v>40</v>
+      <c r="P88" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A89" s="1" t="s">
-        <v>113</v>
+      <c r="A89" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="B89" s="1">
-        <v>3001</v>
+        <v>215</v>
       </c>
       <c r="C89" s="1">
-        <v>0</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>233</v>
+        <v>1</v>
+      </c>
+      <c r="F89" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/路人男</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -5488,39 +5489,34 @@
         <v>2</v>
       </c>
       <c r="K89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M89" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="1">
         <v>0</v>
       </c>
-      <c r="P89" s="1" t="s">
-        <v>40</v>
+      <c r="P89" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A90" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" s="3">
-        <v>3002</v>
+      <c r="A90" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B90" s="1">
+        <v>216</v>
       </c>
       <c r="C90" s="1">
-        <v>0</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>234</v>
+        <v>2</v>
+      </c>
+      <c r="F90" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/黄衣服小女孩</v>
       </c>
       <c r="G90" s="1">
         <v>1</v>
@@ -5535,7 +5531,7 @@
         <v>2</v>
       </c>
       <c r="K90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="1">
         <v>0</v>
@@ -5552,22 +5548,16 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B91" s="3">
-        <v>3003</v>
+        <v>14</v>
+      </c>
+      <c r="B91" s="1">
+        <v>100</v>
       </c>
       <c r="C91" s="1">
-        <v>0</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5597,24 +5587,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A92" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B92" s="3">
-        <v>3004</v>
+    <row r="92" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A92" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B92" s="1">
+        <v>3000</v>
       </c>
       <c r="C92" s="1">
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5632,36 +5622,36 @@
         <v>0</v>
       </c>
       <c r="L92" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M92" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N92" s="1">
         <v>0</v>
       </c>
-      <c r="P92" s="1">
-        <v>1</v>
+      <c r="P92" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A93" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B93" s="3">
-        <v>3005</v>
+      <c r="A93" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" s="1">
+        <v>3001</v>
       </c>
       <c r="C93" s="1">
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5679,36 +5669,36 @@
         <v>0</v>
       </c>
       <c r="L93" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M93" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N93" s="1">
         <v>0</v>
       </c>
-      <c r="P93" s="1">
-        <v>1</v>
+      <c r="P93" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B94" s="3">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="C94" s="1">
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -5740,22 +5730,22 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B95" s="3">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -5786,23 +5776,23 @@
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A96" s="1" t="s">
-        <v>137</v>
+      <c r="A96" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="B96" s="3">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -5833,23 +5823,23 @@
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A97" s="1" t="s">
-        <v>47</v>
+      <c r="A97" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="B97" s="3">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -5881,22 +5871,22 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="B98" s="3">
-        <v>3010</v>
+        <v>3006</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5928,22 +5918,22 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="B99" s="3">
-        <v>3011</v>
+        <v>3007</v>
       </c>
       <c r="C99" s="1">
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -5975,22 +5965,22 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="B100" s="3">
-        <v>3012</v>
+        <v>3008</v>
       </c>
       <c r="C100" s="1">
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -6022,22 +6012,22 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B101" s="3">
-        <v>3013</v>
+        <v>3009</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -6069,22 +6059,22 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B102" s="3">
-        <v>3100</v>
+        <v>3010</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -6116,22 +6106,22 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B103" s="3">
-        <v>3102</v>
+        <v>3011</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -6163,22 +6153,22 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B104" s="3">
-        <v>3104</v>
+        <v>3012</v>
       </c>
       <c r="C104" s="1">
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -6210,22 +6200,22 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B105" s="3">
-        <v>3106</v>
+        <v>3013</v>
       </c>
       <c r="C105" s="1">
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -6257,22 +6247,22 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B106" s="3">
-        <v>3107</v>
+        <v>3100</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -6304,22 +6294,22 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B107" s="3">
-        <v>3108</v>
+        <v>3102</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -6351,22 +6341,22 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B108" s="3">
-        <v>3110</v>
+        <v>3104</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -6398,22 +6388,22 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B109" s="3">
-        <v>3111</v>
+        <v>3106</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -6445,22 +6435,22 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B110" s="3">
-        <v>3112</v>
+        <v>3107</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -6492,48 +6482,236 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B111" s="3">
+        <v>3108</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G111" s="1">
+        <v>1</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1">
+        <v>0</v>
+      </c>
+      <c r="J111" s="1">
+        <v>2</v>
+      </c>
+      <c r="K111" s="1">
+        <v>0</v>
+      </c>
+      <c r="L111" s="1">
+        <v>0</v>
+      </c>
+      <c r="M111" s="1">
+        <v>0</v>
+      </c>
+      <c r="N111" s="1">
+        <v>0</v>
+      </c>
+      <c r="P111" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A112" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B112" s="3">
+        <v>3110</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G112" s="1">
+        <v>1</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1">
+        <v>0</v>
+      </c>
+      <c r="J112" s="1">
+        <v>2</v>
+      </c>
+      <c r="K112" s="1">
+        <v>0</v>
+      </c>
+      <c r="L112" s="1">
+        <v>0</v>
+      </c>
+      <c r="M112" s="1">
+        <v>0</v>
+      </c>
+      <c r="N112" s="1">
+        <v>0</v>
+      </c>
+      <c r="P112" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A113" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B113" s="3">
+        <v>3111</v>
+      </c>
+      <c r="C113" s="1">
+        <v>0</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G113" s="1">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+      <c r="I113" s="1">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1">
+        <v>2</v>
+      </c>
+      <c r="K113" s="1">
+        <v>0</v>
+      </c>
+      <c r="L113" s="1">
+        <v>0</v>
+      </c>
+      <c r="M113" s="1">
+        <v>0</v>
+      </c>
+      <c r="N113" s="1">
+        <v>0</v>
+      </c>
+      <c r="P113" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A114" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B114" s="3">
+        <v>3112</v>
+      </c>
+      <c r="C114" s="1">
+        <v>0</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G114" s="1">
+        <v>1</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+      <c r="I114" s="1">
+        <v>0</v>
+      </c>
+      <c r="J114" s="1">
+        <v>2</v>
+      </c>
+      <c r="K114" s="1">
+        <v>0</v>
+      </c>
+      <c r="L114" s="1">
+        <v>0</v>
+      </c>
+      <c r="M114" s="1">
+        <v>0</v>
+      </c>
+      <c r="N114" s="1">
+        <v>0</v>
+      </c>
+      <c r="P114" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A115" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B115" s="1">
         <v>3114</v>
       </c>
-      <c r="C111" s="1">
-        <v>0</v>
-      </c>
-      <c r="D111" s="1" t="s">
+      <c r="C115" s="1">
+        <v>0</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="F115" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="G111" s="1">
-        <v>1</v>
-      </c>
-      <c r="H111" s="1">
-        <v>0</v>
-      </c>
-      <c r="I111" s="1">
-        <v>0</v>
-      </c>
-      <c r="J111" s="1">
-        <v>2</v>
-      </c>
-      <c r="K111" s="1">
-        <v>0</v>
-      </c>
-      <c r="L111" s="1">
-        <v>0</v>
-      </c>
-      <c r="M111" s="1">
-        <v>0</v>
-      </c>
-      <c r="N111" s="1">
-        <v>0</v>
-      </c>
-      <c r="P111" s="1">
+      <c r="G115" s="1">
+        <v>1</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+      <c r="I115" s="1">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1">
+        <v>2</v>
+      </c>
+      <c r="K115" s="1">
+        <v>0</v>
+      </c>
+      <c r="L115" s="1">
+        <v>0</v>
+      </c>
+      <c r="M115" s="1">
+        <v>0</v>
+      </c>
+      <c r="N115" s="1">
+        <v>0</v>
+      </c>
+      <c r="P115" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="355">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1215,6 +1215,18 @@
   <si>
     <t>路人男</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1293,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1294,6 +1306,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1600,7 +1615,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P115"/>
+  <dimension ref="A2:P119"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -5305,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="1" t="str">
-        <f t="shared" ref="F85:F90" si="0">"Prefabs/Character/"&amp;A85</f>
+        <f t="shared" ref="F85:F94" si="0">"Prefabs/Character/"&amp;A85</f>
         <v>Prefabs/Character/中年路人男</v>
       </c>
       <c r="G85" s="1">
@@ -5547,17 +5562,18 @@
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A91" s="1" t="s">
-        <v>14</v>
+      <c r="A91" s="5" t="s">
+        <v>351</v>
       </c>
       <c r="B91" s="1">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="C91" s="1">
         <v>1</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>231</v>
+      <c r="F91" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/侍者</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5572,7 +5588,7 @@
         <v>2</v>
       </c>
       <c r="K91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="1">
         <v>0</v>
@@ -5587,24 +5603,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A92" s="1" t="s">
-        <v>49</v>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A92" s="5" t="s">
+        <v>352</v>
       </c>
       <c r="B92" s="1">
-        <v>3000</v>
+        <v>218</v>
       </c>
       <c r="C92" s="1">
-        <v>0</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>232</v>
+        <v>2</v>
+      </c>
+      <c r="F92" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/服务员</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5619,39 +5630,34 @@
         <v>2</v>
       </c>
       <c r="K92" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M92" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N92" s="1">
         <v>0</v>
       </c>
-      <c r="P92" s="1" t="s">
-        <v>40</v>
+      <c r="P92" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A93" s="1" t="s">
-        <v>113</v>
+      <c r="A93" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="B93" s="1">
-        <v>3001</v>
+        <v>219</v>
       </c>
       <c r="C93" s="1">
-        <v>0</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>233</v>
+        <v>1</v>
+      </c>
+      <c r="F93" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/船员</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5666,39 +5672,34 @@
         <v>2</v>
       </c>
       <c r="K93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M93" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N93" s="1">
         <v>0</v>
       </c>
-      <c r="P93" s="1" t="s">
-        <v>40</v>
+      <c r="P93" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A94" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B94" s="3">
-        <v>3002</v>
+      <c r="A94" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B94" s="1">
+        <v>220</v>
       </c>
       <c r="C94" s="1">
-        <v>0</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>234</v>
+        <v>1</v>
+      </c>
+      <c r="F94" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/贵族商人</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -5713,7 +5714,7 @@
         <v>2</v>
       </c>
       <c r="K94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="1">
         <v>0</v>
@@ -5730,22 +5731,16 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B95" s="3">
-        <v>3003</v>
+        <v>14</v>
+      </c>
+      <c r="B95" s="1">
+        <v>100</v>
       </c>
       <c r="C95" s="1">
-        <v>0</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -5775,24 +5770,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A96" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B96" s="3">
-        <v>3004</v>
+    <row r="96" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A96" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" s="1">
+        <v>3000</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -5810,36 +5805,36 @@
         <v>0</v>
       </c>
       <c r="L96" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M96" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N96" s="1">
         <v>0</v>
       </c>
-      <c r="P96" s="1">
-        <v>1</v>
+      <c r="P96" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A97" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B97" s="3">
-        <v>3005</v>
+      <c r="A97" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" s="1">
+        <v>3001</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -5857,36 +5852,36 @@
         <v>0</v>
       </c>
       <c r="L97" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M97" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N97" s="1">
         <v>0</v>
       </c>
-      <c r="P97" s="1">
-        <v>1</v>
+      <c r="P97" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B98" s="3">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5918,22 +5913,22 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B99" s="3">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="C99" s="1">
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -5964,23 +5959,23 @@
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A100" s="1" t="s">
-        <v>137</v>
+      <c r="A100" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="B100" s="3">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="C100" s="1">
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -6011,23 +6006,23 @@
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A101" s="1" t="s">
-        <v>47</v>
+      <c r="A101" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="B101" s="3">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -6059,22 +6054,22 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="B102" s="3">
-        <v>3010</v>
+        <v>3006</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -6106,22 +6101,22 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="B103" s="3">
-        <v>3011</v>
+        <v>3007</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -6153,22 +6148,22 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="B104" s="3">
-        <v>3012</v>
+        <v>3008</v>
       </c>
       <c r="C104" s="1">
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -6200,22 +6195,22 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B105" s="3">
-        <v>3013</v>
+        <v>3009</v>
       </c>
       <c r="C105" s="1">
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -6247,22 +6242,22 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B106" s="3">
-        <v>3100</v>
+        <v>3010</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -6294,22 +6289,22 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B107" s="3">
-        <v>3102</v>
+        <v>3011</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -6341,22 +6336,22 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B108" s="3">
-        <v>3104</v>
+        <v>3012</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -6388,22 +6383,22 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B109" s="3">
-        <v>3106</v>
+        <v>3013</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -6435,22 +6430,22 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B110" s="3">
-        <v>3107</v>
+        <v>3100</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -6482,22 +6477,22 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B111" s="3">
-        <v>3108</v>
+        <v>3102</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G111" s="1">
         <v>1</v>
@@ -6529,22 +6524,22 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B112" s="3">
-        <v>3110</v>
+        <v>3104</v>
       </c>
       <c r="C112" s="1">
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G112" s="1">
         <v>1</v>
@@ -6576,22 +6571,22 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B113" s="3">
-        <v>3111</v>
+        <v>3106</v>
       </c>
       <c r="C113" s="1">
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G113" s="1">
         <v>1</v>
@@ -6623,22 +6618,22 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B114" s="3">
-        <v>3112</v>
+        <v>3107</v>
       </c>
       <c r="C114" s="1">
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -6670,48 +6665,236 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B115" s="3">
+        <v>3108</v>
+      </c>
+      <c r="C115" s="1">
+        <v>0</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G115" s="1">
+        <v>1</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+      <c r="I115" s="1">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1">
+        <v>2</v>
+      </c>
+      <c r="K115" s="1">
+        <v>0</v>
+      </c>
+      <c r="L115" s="1">
+        <v>0</v>
+      </c>
+      <c r="M115" s="1">
+        <v>0</v>
+      </c>
+      <c r="N115" s="1">
+        <v>0</v>
+      </c>
+      <c r="P115" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A116" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B116" s="3">
+        <v>3110</v>
+      </c>
+      <c r="C116" s="1">
+        <v>0</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G116" s="1">
+        <v>1</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+      <c r="I116" s="1">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1">
+        <v>2</v>
+      </c>
+      <c r="K116" s="1">
+        <v>0</v>
+      </c>
+      <c r="L116" s="1">
+        <v>0</v>
+      </c>
+      <c r="M116" s="1">
+        <v>0</v>
+      </c>
+      <c r="N116" s="1">
+        <v>0</v>
+      </c>
+      <c r="P116" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A117" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B117" s="3">
+        <v>3111</v>
+      </c>
+      <c r="C117" s="1">
+        <v>0</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G117" s="1">
+        <v>1</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1">
+        <v>2</v>
+      </c>
+      <c r="K117" s="1">
+        <v>0</v>
+      </c>
+      <c r="L117" s="1">
+        <v>0</v>
+      </c>
+      <c r="M117" s="1">
+        <v>0</v>
+      </c>
+      <c r="N117" s="1">
+        <v>0</v>
+      </c>
+      <c r="P117" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A118" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B118" s="3">
+        <v>3112</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G118" s="1">
+        <v>1</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1">
+        <v>0</v>
+      </c>
+      <c r="J118" s="1">
+        <v>2</v>
+      </c>
+      <c r="K118" s="1">
+        <v>0</v>
+      </c>
+      <c r="L118" s="1">
+        <v>0</v>
+      </c>
+      <c r="M118" s="1">
+        <v>0</v>
+      </c>
+      <c r="N118" s="1">
+        <v>0</v>
+      </c>
+      <c r="P118" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A119" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B119" s="1">
         <v>3114</v>
       </c>
-      <c r="C115" s="1">
-        <v>0</v>
-      </c>
-      <c r="D115" s="1" t="s">
+      <c r="C119" s="1">
+        <v>0</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F119" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="G115" s="1">
-        <v>1</v>
-      </c>
-      <c r="H115" s="1">
-        <v>0</v>
-      </c>
-      <c r="I115" s="1">
-        <v>0</v>
-      </c>
-      <c r="J115" s="1">
-        <v>2</v>
-      </c>
-      <c r="K115" s="1">
-        <v>0</v>
-      </c>
-      <c r="L115" s="1">
-        <v>0</v>
-      </c>
-      <c r="M115" s="1">
-        <v>0</v>
-      </c>
-      <c r="N115" s="1">
-        <v>0</v>
-      </c>
-      <c r="P115" s="1">
+      <c r="G119" s="1">
+        <v>1</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1">
+        <v>0</v>
+      </c>
+      <c r="J119" s="1">
+        <v>2</v>
+      </c>
+      <c r="K119" s="1">
+        <v>0</v>
+      </c>
+      <c r="L119" s="1">
+        <v>0</v>
+      </c>
+      <c r="M119" s="1">
+        <v>0</v>
+      </c>
+      <c r="N119" s="1">
+        <v>0</v>
+      </c>
+      <c r="P119" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="347">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -379,10 +379,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>杰克</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -405,9 +401,6 @@
     <t>贵族骑士</t>
   </si>
   <si>
-    <t>轻战士</t>
-  </si>
-  <si>
     <t>重装女战士</t>
   </si>
   <si>
@@ -494,10 +487,6 @@
   </si>
   <si>
     <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -703,530 +692,519 @@
     <t>Prefabs/Character/王后</t>
   </si>
   <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸭</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/白兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/松鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/野兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/火烈鸟</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/刺猬</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/大象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/企鹅</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/袋鼠</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/女仆</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/SmallChicken</t>
+  </si>
+  <si>
+    <t>Icon/Chicken</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/Rabbit</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/松鼠</t>
+  </si>
+  <si>
+    <t>Icon/野兔</t>
+  </si>
+  <si>
+    <t>Icon/火烈鸟</t>
+  </si>
+  <si>
+    <t>Icon/鹿</t>
+  </si>
+  <si>
+    <t>Icon/刺猬</t>
+  </si>
+  <si>
+    <t>Icon/大象</t>
+  </si>
+  <si>
+    <t>Icon/企鹅</t>
+  </si>
+  <si>
+    <t>Icon/袋鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/侦探</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鬼族男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女魔族</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小精灵红</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通士兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Prefabs/Character/瓦尔特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/管家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/艾琳娜</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/莱特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/金发女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/阿尔杰农</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装女战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Character/轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/贵族骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老英雄</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老公公</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武道女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/格斗家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/战斗学者</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/异国女子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小花</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小美</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小混混</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/官员</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女诗人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/商人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/双辫女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/匪徒</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/制服小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔女郎</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸭</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/白兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/松鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/野兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/火烈鸟</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/刺猬</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/大象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/企鹅</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/袋鼠</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/格吉尔</t>
-  </si>
-  <si>
-    <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/马</t>
-  </si>
-  <si>
-    <t>Icon/玛德琳</t>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-  </si>
-  <si>
-    <t>Icon/丝特芬妮</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/修女</t>
-  </si>
-  <si>
-    <t>Icon/公主</t>
-  </si>
-  <si>
-    <t>Icon/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Icon/国王</t>
-  </si>
-  <si>
-    <t>Icon/天使</t>
-  </si>
-  <si>
-    <t>Icon/女仆</t>
-  </si>
-  <si>
-    <t>Icon/朵儿洁</t>
-  </si>
-  <si>
-    <t>Icon/渔夫</t>
-  </si>
-  <si>
-    <t>Icon/船长</t>
-  </si>
-  <si>
-    <t>Icon/水手</t>
-  </si>
-  <si>
-    <t>Icon/游侠</t>
-  </si>
-  <si>
-    <t>Icon/牧师</t>
-  </si>
-  <si>
-    <t>Icon/王子</t>
-  </si>
-  <si>
-    <t>Icon/王后</t>
-  </si>
-  <si>
-    <t>Icon/管家</t>
-  </si>
-  <si>
-    <t>Icon/SmallChicken</t>
-  </si>
-  <si>
-    <t>Icon/Chicken</t>
-  </si>
-  <si>
-    <t>Icon/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/Rabbit</t>
-  </si>
-  <si>
-    <t>Icon/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/猪</t>
-  </si>
-  <si>
-    <t>Icon/奶牛</t>
-  </si>
-  <si>
-    <t>Icon/松鼠</t>
-  </si>
-  <si>
-    <t>Icon/野兔</t>
-  </si>
-  <si>
-    <t>Icon/火烈鸟</t>
-  </si>
-  <si>
-    <t>Icon/鹿</t>
-  </si>
-  <si>
-    <t>Icon/刺猬</t>
-  </si>
-  <si>
-    <t>Icon/大象</t>
-  </si>
-  <si>
-    <t>Icon/企鹅</t>
-  </si>
-  <si>
-    <t>Icon/袋鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鬼族男</t>
-  </si>
-  <si>
-    <t>魔族大将</t>
-  </si>
-  <si>
-    <t>魔族法师</t>
-  </si>
-  <si>
-    <t>女魔族</t>
-  </si>
-  <si>
-    <t>小精灵红</t>
-  </si>
-  <si>
-    <t>小精灵黄</t>
-  </si>
-  <si>
-    <t>幽灵战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/侦探</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/鬼族男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/魔族大将</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/魔族法师</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女魔族</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小精灵红</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小精灵黄</t>
-  </si>
-  <si>
-    <t>中年路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中年路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红发小孩</t>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-  </si>
-  <si>
-    <t>路人女</t>
-  </si>
-  <si>
-    <t>黄衣服小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幽灵战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者</t>
-  </si>
-  <si>
-    <t>服务员</t>
-  </si>
-  <si>
-    <t>船员</t>
-  </si>
-  <si>
-    <t>贵族商人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1615,7 +1593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P119"/>
+  <dimension ref="A2:P115"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -1696,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1746,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
@@ -1793,7 +1771,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1840,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1878,7 +1856,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1887,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -1934,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>27</v>
@@ -1984,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>35</v>
@@ -2034,7 +2012,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>36</v>
@@ -2084,13 +2062,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -2125,7 +2103,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -2134,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2181,13 +2159,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2228,13 +2206,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2266,7 +2244,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2275,13 +2253,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2322,13 +2300,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2360,7 +2338,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B17" s="1">
         <v>14</v>
@@ -2369,13 +2347,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2416,13 +2394,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2454,7 +2432,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B19" s="1">
         <v>16</v>
@@ -2463,13 +2441,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2510,13 +2488,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2548,7 +2526,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2557,13 +2535,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2595,7 +2573,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2604,13 +2582,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2642,7 +2620,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2651,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2689,7 +2667,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2698,13 +2676,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2736,7 +2714,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2745,13 +2723,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2783,7 +2761,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2792,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2830,7 +2808,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2839,13 +2817,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2877,7 +2855,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2886,13 +2864,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2933,13 +2911,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2980,13 +2958,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -3027,13 +3005,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -3065,7 +3043,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>98</v>
+        <v>342</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -3074,13 +3052,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -3112,7 +3090,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -3121,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -3159,7 +3137,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -3168,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -3206,7 +3184,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -3215,13 +3193,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -3253,7 +3231,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -3262,13 +3240,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -3300,7 +3278,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -3309,13 +3287,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>129</v>
+        <v>346</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -3347,7 +3325,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -3356,13 +3334,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -3394,7 +3372,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -3403,13 +3381,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -3441,7 +3419,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -3450,13 +3428,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -3488,7 +3466,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -3497,13 +3475,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -3535,7 +3513,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3544,13 +3522,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3582,7 +3560,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3591,13 +3569,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3629,7 +3607,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3638,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3670,7 +3648,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3679,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3711,7 +3689,7 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3720,7 +3698,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3752,7 +3730,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>105</v>
+        <v>343</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3761,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>203</v>
+        <v>344</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3793,7 +3771,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3802,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3834,7 +3812,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3843,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3875,7 +3853,7 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3884,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3925,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3966,7 +3944,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -4007,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -4048,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -4089,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -4130,7 +4108,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -4171,7 +4149,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -4212,7 +4190,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -4253,7 +4231,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -4294,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -4335,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -4376,7 +4354,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -4417,7 +4395,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -4458,7 +4436,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4499,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -4540,7 +4518,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -4581,7 +4559,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -4622,7 +4600,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -4663,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -4704,7 +4682,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -4745,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -4786,7 +4764,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -4827,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -4868,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -4909,7 +4887,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -4950,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4982,7 +4960,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4991,7 +4969,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -5023,16 +5001,16 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B78" s="1">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C78" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -5064,16 +5042,16 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B79" s="1">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C79" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -5105,16 +5083,17 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B80" s="1">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C80" s="1">
         <v>2</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>340</v>
+      <c r="F80" s="1" t="str">
+        <f>"Prefabs/Character/"&amp;A80</f>
+        <v>Prefabs/Character/中年路人女</v>
       </c>
       <c r="G80" s="1">
         <v>1</v>
@@ -5146,16 +5125,17 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B81" s="1">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C81" s="1">
-        <v>2</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>341</v>
+        <v>1</v>
+      </c>
+      <c r="F81" s="1" t="str">
+        <f t="shared" ref="F81:F90" si="0">"Prefabs/Character/"&amp;A81</f>
+        <v>Prefabs/Character/中年路人男</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -5187,16 +5167,17 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B82" s="1">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>342</v>
+      <c r="F82" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/红发小孩</v>
       </c>
       <c r="G82" s="1">
         <v>1</v>
@@ -5228,16 +5209,17 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B83" s="1">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C83" s="1">
         <v>1</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>349</v>
+      <c r="F83" s="1" t="str">
+        <f>"Prefabs/Character/"&amp;A83</f>
+        <v>Prefabs/Character/纺织婆婆</v>
       </c>
       <c r="G83" s="1">
         <v>1</v>
@@ -5269,17 +5251,17 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B84" s="1">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C84" s="1">
         <v>2</v>
       </c>
       <c r="F84" s="1" t="str">
-        <f>"Prefabs/Character/"&amp;A84</f>
-        <v>Prefabs/Character/中年路人女</v>
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/路人女</v>
       </c>
       <c r="G84" s="1">
         <v>1</v>
@@ -5311,17 +5293,17 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B85" s="1">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C85" s="1">
         <v>1</v>
       </c>
       <c r="F85" s="1" t="str">
-        <f t="shared" ref="F85:F94" si="0">"Prefabs/Character/"&amp;A85</f>
-        <v>Prefabs/Character/中年路人男</v>
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/路人男</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -5353,17 +5335,17 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B86" s="1">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
       </c>
       <c r="F86" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Prefabs/Character/红发小孩</v>
+        <v>Prefabs/Character/黄衣服小女孩</v>
       </c>
       <c r="G86" s="1">
         <v>1</v>
@@ -5394,18 +5376,18 @@
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A87" s="3" t="s">
-        <v>346</v>
+      <c r="A87" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="B87" s="1">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
       </c>
       <c r="F87" s="1" t="str">
-        <f>"Prefabs/Character/"&amp;A87</f>
-        <v>Prefabs/Character/纺织婆婆</v>
+        <f t="shared" si="0"/>
+        <v>Prefabs/Character/侍者</v>
       </c>
       <c r="G87" s="1">
         <v>1</v>
@@ -5436,18 +5418,18 @@
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A88" s="3" t="s">
-        <v>347</v>
+      <c r="A88" s="5" t="s">
+        <v>339</v>
       </c>
       <c r="B88" s="1">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C88" s="1">
         <v>2</v>
       </c>
       <c r="F88" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Prefabs/Character/路人女</v>
+        <v>Prefabs/Character/服务员</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -5478,18 +5460,18 @@
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A89" s="3" t="s">
-        <v>350</v>
+      <c r="A89" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="B89" s="1">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C89" s="1">
         <v>1</v>
       </c>
       <c r="F89" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Prefabs/Character/路人男</v>
+        <v>Prefabs/Character/船员</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -5520,18 +5502,18 @@
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A90" s="3" t="s">
-        <v>348</v>
+      <c r="A90" s="5" t="s">
+        <v>341</v>
       </c>
       <c r="B90" s="1">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C90" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Prefabs/Character/黄衣服小女孩</v>
+        <v>Prefabs/Character/贵族商人</v>
       </c>
       <c r="G90" s="1">
         <v>1</v>
@@ -5562,18 +5544,17 @@
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A91" s="5" t="s">
-        <v>351</v>
+      <c r="A91" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B91" s="1">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="C91" s="1">
         <v>1</v>
       </c>
-      <c r="F91" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Prefabs/Character/侍者</v>
+      <c r="F91" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5588,7 +5569,7 @@
         <v>2</v>
       </c>
       <c r="K91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="1">
         <v>0</v>
@@ -5603,19 +5584,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A92" s="5" t="s">
-        <v>352</v>
+    <row r="92" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+      <c r="A92" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B92" s="1">
-        <v>218</v>
+        <v>3000</v>
       </c>
       <c r="C92" s="1">
-        <v>2</v>
-      </c>
-      <c r="F92" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Prefabs/Character/服务员</v>
+        <v>0</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5630,34 +5616,39 @@
         <v>2</v>
       </c>
       <c r="K92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M92" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N92" s="1">
         <v>0</v>
       </c>
-      <c r="P92" s="1">
-        <v>1</v>
+      <c r="P92" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A93" s="5" t="s">
-        <v>353</v>
+      <c r="A93" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="B93" s="1">
-        <v>219</v>
+        <v>3001</v>
       </c>
       <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Prefabs/Character/船员</v>
+        <v>0</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5672,34 +5663,39 @@
         <v>2</v>
       </c>
       <c r="K93" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="M93" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="N93" s="1">
         <v>0</v>
       </c>
-      <c r="P93" s="1">
-        <v>1</v>
+      <c r="P93" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A94" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B94" s="1">
-        <v>220</v>
+      <c r="A94" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" s="3">
+        <v>3002</v>
       </c>
       <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="F94" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Prefabs/Character/贵族商人</v>
+        <v>0</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -5714,7 +5710,7 @@
         <v>2</v>
       </c>
       <c r="K94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="1">
         <v>0</v>
@@ -5731,111 +5727,117 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B95" s="1">
-        <v>100</v>
+        <v>132</v>
+      </c>
+      <c r="B95" s="3">
+        <v>3003</v>
       </c>
       <c r="C95" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G95" s="1">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1">
+        <v>2</v>
+      </c>
+      <c r="K95" s="1">
+        <v>0</v>
+      </c>
+      <c r="L95" s="1">
+        <v>0</v>
+      </c>
+      <c r="M95" s="1">
+        <v>0</v>
+      </c>
+      <c r="N95" s="1">
+        <v>0</v>
+      </c>
+      <c r="P95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A96" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B96" s="3">
+        <v>3004</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G95" s="1">
-        <v>1</v>
-      </c>
-      <c r="H95" s="1">
-        <v>0</v>
-      </c>
-      <c r="I95" s="1">
-        <v>0</v>
-      </c>
-      <c r="J95" s="1">
-        <v>2</v>
-      </c>
-      <c r="K95" s="1">
-        <v>0</v>
-      </c>
-      <c r="L95" s="1">
-        <v>0</v>
-      </c>
-      <c r="M95" s="1">
-        <v>0</v>
-      </c>
-      <c r="N95" s="1">
-        <v>0</v>
-      </c>
-      <c r="P95" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="27" x14ac:dyDescent="0.15">
-      <c r="A96" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B96" s="1">
-        <v>3000</v>
-      </c>
-      <c r="C96" s="1">
-        <v>0</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="G96" s="1">
+        <v>1</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1">
+        <v>2</v>
+      </c>
+      <c r="K96" s="1">
+        <v>0</v>
+      </c>
+      <c r="L96" s="1">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1">
+        <v>0</v>
+      </c>
+      <c r="P96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A97" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B97" s="3">
+        <v>3005</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G96" s="1">
-        <v>1</v>
-      </c>
-      <c r="H96" s="1">
-        <v>0</v>
-      </c>
-      <c r="I96" s="1">
-        <v>0</v>
-      </c>
-      <c r="J96" s="1">
-        <v>2</v>
-      </c>
-      <c r="K96" s="1">
-        <v>0</v>
-      </c>
-      <c r="L96" s="1">
-        <v>8100</v>
-      </c>
-      <c r="M96" s="1">
-        <v>8100</v>
-      </c>
-      <c r="N96" s="1">
-        <v>0</v>
-      </c>
-      <c r="P96" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A97" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B97" s="1">
-        <v>3001</v>
-      </c>
-      <c r="C97" s="1">
-        <v>0</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="G97" s="1">
         <v>1</v>
       </c>
@@ -5852,36 +5854,36 @@
         <v>0</v>
       </c>
       <c r="L97" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="M97" s="1">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="N97" s="1">
         <v>0</v>
       </c>
-      <c r="P97" s="1" t="s">
-        <v>40</v>
+      <c r="P97" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B98" s="3">
-        <v>3002</v>
+        <v>3006</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5913,116 +5915,116 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B99" s="3">
-        <v>3003</v>
+        <v>3007</v>
       </c>
       <c r="C99" s="1">
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F99" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G99" s="1">
+        <v>1</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1">
+        <v>2</v>
+      </c>
+      <c r="K99" s="1">
+        <v>0</v>
+      </c>
+      <c r="L99" s="1">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1">
+        <v>0</v>
+      </c>
+      <c r="N99" s="1">
+        <v>0</v>
+      </c>
+      <c r="P99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A100" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B100" s="3">
+        <v>3008</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G99" s="1">
-        <v>1</v>
-      </c>
-      <c r="H99" s="1">
-        <v>0</v>
-      </c>
-      <c r="I99" s="1">
-        <v>0</v>
-      </c>
-      <c r="J99" s="1">
-        <v>2</v>
-      </c>
-      <c r="K99" s="1">
-        <v>0</v>
-      </c>
-      <c r="L99" s="1">
-        <v>0</v>
-      </c>
-      <c r="M99" s="1">
-        <v>0</v>
-      </c>
-      <c r="N99" s="1">
-        <v>0</v>
-      </c>
-      <c r="P99" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A100" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B100" s="3">
-        <v>3004</v>
-      </c>
-      <c r="C100" s="1">
-        <v>0</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F100" s="1" t="s">
+      <c r="G100" s="1">
+        <v>1</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2</v>
+      </c>
+      <c r="K100" s="1">
+        <v>0</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1">
+        <v>0</v>
+      </c>
+      <c r="P100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A101" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B101" s="3">
+        <v>3009</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="G100" s="1">
-        <v>1</v>
-      </c>
-      <c r="H100" s="1">
-        <v>0</v>
-      </c>
-      <c r="I100" s="1">
-        <v>0</v>
-      </c>
-      <c r="J100" s="1">
-        <v>2</v>
-      </c>
-      <c r="K100" s="1">
-        <v>0</v>
-      </c>
-      <c r="L100" s="1">
-        <v>0</v>
-      </c>
-      <c r="M100" s="1">
-        <v>0</v>
-      </c>
-      <c r="N100" s="1">
-        <v>0</v>
-      </c>
-      <c r="P100" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A101" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B101" s="3">
-        <v>3005</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -6054,22 +6056,22 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="B102" s="3">
-        <v>3006</v>
+        <v>3010</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -6101,22 +6103,22 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="B103" s="3">
-        <v>3007</v>
+        <v>3011</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -6148,22 +6150,22 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="B104" s="3">
-        <v>3008</v>
+        <v>3012</v>
       </c>
       <c r="C104" s="1">
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -6195,22 +6197,22 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B105" s="3">
-        <v>3009</v>
+        <v>3013</v>
       </c>
       <c r="C105" s="1">
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -6242,22 +6244,22 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B106" s="3">
-        <v>3010</v>
+        <v>3100</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -6289,22 +6291,22 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B107" s="3">
-        <v>3011</v>
+        <v>3102</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>157</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -6336,22 +6338,22 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B108" s="3">
-        <v>3012</v>
+        <v>3104</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>158</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -6383,22 +6385,22 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B109" s="3">
-        <v>3013</v>
+        <v>3106</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -6430,22 +6432,22 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B110" s="3">
-        <v>3100</v>
+        <v>3107</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>159</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -6477,22 +6479,22 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B111" s="3">
-        <v>3102</v>
+        <v>3108</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G111" s="1">
         <v>1</v>
@@ -6524,22 +6526,22 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B112" s="3">
-        <v>3104</v>
+        <v>3110</v>
       </c>
       <c r="C112" s="1">
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>161</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G112" s="1">
         <v>1</v>
@@ -6571,22 +6573,22 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B113" s="3">
-        <v>3106</v>
+        <v>3111</v>
       </c>
       <c r="C113" s="1">
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G113" s="1">
         <v>1</v>
@@ -6618,22 +6620,22 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B114" s="3">
-        <v>3107</v>
+        <v>3112</v>
       </c>
       <c r="C114" s="1">
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>162</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -6665,22 +6667,22 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B115" s="3">
-        <v>3108</v>
+        <v>61</v>
+      </c>
+      <c r="B115" s="1">
+        <v>3114</v>
       </c>
       <c r="C115" s="1">
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>163</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G115" s="1">
         <v>1</v>
@@ -6707,194 +6709,6 @@
         <v>0</v>
       </c>
       <c r="P115" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A116" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B116" s="3">
-        <v>3110</v>
-      </c>
-      <c r="C116" s="1">
-        <v>0</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="G116" s="1">
-        <v>1</v>
-      </c>
-      <c r="H116" s="1">
-        <v>0</v>
-      </c>
-      <c r="I116" s="1">
-        <v>0</v>
-      </c>
-      <c r="J116" s="1">
-        <v>2</v>
-      </c>
-      <c r="K116" s="1">
-        <v>0</v>
-      </c>
-      <c r="L116" s="1">
-        <v>0</v>
-      </c>
-      <c r="M116" s="1">
-        <v>0</v>
-      </c>
-      <c r="N116" s="1">
-        <v>0</v>
-      </c>
-      <c r="P116" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A117" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B117" s="3">
-        <v>3111</v>
-      </c>
-      <c r="C117" s="1">
-        <v>0</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="G117" s="1">
-        <v>1</v>
-      </c>
-      <c r="H117" s="1">
-        <v>0</v>
-      </c>
-      <c r="I117" s="1">
-        <v>0</v>
-      </c>
-      <c r="J117" s="1">
-        <v>2</v>
-      </c>
-      <c r="K117" s="1">
-        <v>0</v>
-      </c>
-      <c r="L117" s="1">
-        <v>0</v>
-      </c>
-      <c r="M117" s="1">
-        <v>0</v>
-      </c>
-      <c r="N117" s="1">
-        <v>0</v>
-      </c>
-      <c r="P117" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A118" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B118" s="3">
-        <v>3112</v>
-      </c>
-      <c r="C118" s="1">
-        <v>0</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G118" s="1">
-        <v>1</v>
-      </c>
-      <c r="H118" s="1">
-        <v>0</v>
-      </c>
-      <c r="I118" s="1">
-        <v>0</v>
-      </c>
-      <c r="J118" s="1">
-        <v>2</v>
-      </c>
-      <c r="K118" s="1">
-        <v>0</v>
-      </c>
-      <c r="L118" s="1">
-        <v>0</v>
-      </c>
-      <c r="M118" s="1">
-        <v>0</v>
-      </c>
-      <c r="N118" s="1">
-        <v>0</v>
-      </c>
-      <c r="P118" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A119" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B119" s="1">
-        <v>3114</v>
-      </c>
-      <c r="C119" s="1">
-        <v>0</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G119" s="1">
-        <v>1</v>
-      </c>
-      <c r="H119" s="1">
-        <v>0</v>
-      </c>
-      <c r="I119" s="1">
-        <v>0</v>
-      </c>
-      <c r="J119" s="1">
-        <v>2</v>
-      </c>
-      <c r="K119" s="1">
-        <v>0</v>
-      </c>
-      <c r="L119" s="1">
-        <v>0</v>
-      </c>
-      <c r="M119" s="1">
-        <v>0</v>
-      </c>
-      <c r="N119" s="1">
-        <v>0</v>
-      </c>
-      <c r="P119" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="348">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -308,10 +308,6 @@
     <t>天使</t>
   </si>
   <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>女战士</t>
   </si>
   <si>
@@ -439,14 +435,6 @@
   </si>
   <si>
     <t>Head/Boy2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -540,670 +528,691 @@
     <t>Head/女骑士</t>
   </si>
   <si>
+    <t>Head/渔夫</t>
+  </si>
+  <si>
+    <t>Head/船长</t>
+  </si>
+  <si>
+    <t>Head/水手</t>
+  </si>
+  <si>
+    <t>Head/游侠</t>
+  </si>
+  <si>
+    <t>Head/王子</t>
+  </si>
+  <si>
+    <t>Head/王后</t>
+  </si>
+  <si>
+    <t>Head/管家</t>
+  </si>
+  <si>
+    <t>Head/鸭子</t>
+  </si>
+  <si>
+    <t>Head/绵羊</t>
+  </si>
+  <si>
+    <t>Head/猪</t>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+  </si>
+  <si>
+    <t>Head/马</t>
+  </si>
+  <si>
+    <t>Head/松鼠</t>
+  </si>
+  <si>
+    <t>Head/野兔</t>
+  </si>
+  <si>
+    <t>Head/火烈鸟</t>
+  </si>
+  <si>
+    <t>Head/鹿</t>
+  </si>
+  <si>
+    <t>Head/刺猬</t>
+  </si>
+  <si>
+    <t>Head/大象</t>
+  </si>
+  <si>
+    <t>Head/企鹅</t>
+  </si>
+  <si>
+    <t>Head/袋鼠</t>
+  </si>
+  <si>
+    <t>Head/Rabbit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/亚度尼斯</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/修女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/公主</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/国王</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/坎蒂丝</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/天使</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女仆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布拉德利</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布蓝达</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/希贝儿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/帕特里克</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/朵儿洁</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/梅林</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/渔夫</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/船长</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/水手</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/游侠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/爱格伯特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/牧师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王后</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸭</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/白兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/松鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/野兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/火烈鸟</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/刺猬</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/大象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/企鹅</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/袋鼠</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/SmallChicken</t>
+  </si>
+  <si>
+    <t>Icon/Chicken</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/Rabbit</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/松鼠</t>
+  </si>
+  <si>
+    <t>Icon/野兔</t>
+  </si>
+  <si>
+    <t>Icon/火烈鸟</t>
+  </si>
+  <si>
+    <t>Icon/鹿</t>
+  </si>
+  <si>
+    <t>Icon/刺猬</t>
+  </si>
+  <si>
+    <t>Icon/大象</t>
+  </si>
+  <si>
+    <t>Icon/企鹅</t>
+  </si>
+  <si>
+    <t>Icon/袋鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/侦探</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鬼族男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女魔族</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小精灵红</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通士兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/轻战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Head/朵儿洁</t>
-  </si>
-  <si>
-    <t>Head/渔夫</t>
-  </si>
-  <si>
-    <t>Head/船长</t>
-  </si>
-  <si>
-    <t>Head/水手</t>
-  </si>
-  <si>
-    <t>Head/游侠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/金发女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Head/牧师</t>
-  </si>
-  <si>
-    <t>Head/王子</t>
-  </si>
-  <si>
-    <t>Head/王后</t>
-  </si>
-  <si>
-    <t>Head/管家</t>
-  </si>
-  <si>
-    <t>Head/金发女</t>
-  </si>
-  <si>
-    <t>Head/鸭子</t>
-  </si>
-  <si>
-    <t>Head/绵羊</t>
-  </si>
-  <si>
-    <t>Head/猪</t>
-  </si>
-  <si>
-    <t>Head/奶牛</t>
-  </si>
-  <si>
-    <t>Head/马</t>
-  </si>
-  <si>
-    <t>Head/松鼠</t>
-  </si>
-  <si>
-    <t>Head/野兔</t>
-  </si>
-  <si>
-    <t>Head/火烈鸟</t>
-  </si>
-  <si>
-    <t>Head/鹿</t>
-  </si>
-  <si>
-    <t>Head/刺猬</t>
-  </si>
-  <si>
-    <t>Head/大象</t>
-  </si>
-  <si>
-    <t>Head/企鹅</t>
-  </si>
-  <si>
-    <t>Head/袋鼠</t>
-  </si>
-  <si>
-    <t>Head/Rabbit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/亚度尼斯</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/修女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/公主</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/国王</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/坎蒂丝</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/天使</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女仆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布拉德利</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布蓝达</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/希贝儿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/帕特里克</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/朵儿洁</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/梅林</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/渔夫</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/船长</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/水手</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/游侠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/爱格伯特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/牧师</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王后</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/管家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/艾琳娜</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/莱特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/金发女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/阿尔杰农</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/贵族骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老英雄</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老公公</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武道女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/格斗家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/战斗学者</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/异国女子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小花</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小美</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小混混</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/官员</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女诗人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/商人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/双辫女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/匪徒</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/制服小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔女郎</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸭</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/白兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/松鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/野兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/火烈鸟</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/刺猬</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/大象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/企鹅</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/袋鼠</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/格吉尔</t>
-  </si>
-  <si>
-    <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/马</t>
-  </si>
-  <si>
-    <t>Icon/玛德琳</t>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-  </si>
-  <si>
-    <t>Icon/丝特芬妮</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/修女</t>
-  </si>
-  <si>
-    <t>Icon/公主</t>
-  </si>
-  <si>
-    <t>Icon/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Icon/国王</t>
-  </si>
-  <si>
-    <t>Icon/天使</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Icon/女仆</t>
-  </si>
-  <si>
-    <t>Icon/朵儿洁</t>
-  </si>
-  <si>
-    <t>Icon/渔夫</t>
-  </si>
-  <si>
-    <t>Icon/船长</t>
-  </si>
-  <si>
-    <t>Icon/水手</t>
-  </si>
-  <si>
-    <t>Icon/游侠</t>
-  </si>
-  <si>
-    <t>Icon/牧师</t>
-  </si>
-  <si>
-    <t>Icon/王子</t>
-  </si>
-  <si>
-    <t>Icon/王后</t>
-  </si>
-  <si>
-    <t>Icon/管家</t>
-  </si>
-  <si>
-    <t>Icon/SmallChicken</t>
-  </si>
-  <si>
-    <t>Icon/Chicken</t>
-  </si>
-  <si>
-    <t>Icon/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/Rabbit</t>
-  </si>
-  <si>
-    <t>Icon/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/猪</t>
-  </si>
-  <si>
-    <t>Icon/奶牛</t>
-  </si>
-  <si>
-    <t>Icon/松鼠</t>
-  </si>
-  <si>
-    <t>Icon/野兔</t>
-  </si>
-  <si>
-    <t>Icon/火烈鸟</t>
-  </si>
-  <si>
-    <t>Icon/鹿</t>
-  </si>
-  <si>
-    <t>Icon/刺猬</t>
-  </si>
-  <si>
-    <t>Icon/大象</t>
-  </si>
-  <si>
-    <t>Icon/企鹅</t>
-  </si>
-  <si>
-    <t>Icon/袋鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鬼族男</t>
-  </si>
-  <si>
-    <t>女魔族</t>
-  </si>
-  <si>
-    <t>小精灵红</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/侦探</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/鬼族男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女魔族</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小精灵红</t>
-  </si>
-  <si>
-    <t>中年路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中年路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红发小孩</t>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-  </si>
-  <si>
-    <t>路人女</t>
-  </si>
-  <si>
-    <t>黄衣服小女孩</t>
-  </si>
-  <si>
-    <t>路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者</t>
-  </si>
-  <si>
-    <t>服务员</t>
-  </si>
-  <si>
-    <t>船员</t>
-  </si>
-  <si>
-    <t>贵族商人</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通士兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/轻战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1603,11 +1612,11 @@
     <col min="6" max="6" width="38.375" style="1" customWidth="1"/>
     <col min="7" max="8" width="10.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="7.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13.375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="14.375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="1" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="11.625" style="1" customWidth="1"/>
     <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
     <col min="17" max="16384" width="7.75" style="1"/>
@@ -1674,7 +1683,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1724,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
@@ -1771,7 +1780,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1818,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1856,7 +1865,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1865,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -1912,7 +1921,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>27</v>
@@ -1962,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>35</v>
@@ -2012,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>36</v>
@@ -2062,13 +2071,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -2103,7 +2112,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -2112,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2159,13 +2168,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>263</v>
+        <v>345</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2206,13 +2215,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2244,7 +2253,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2253,13 +2262,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2300,13 +2309,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2338,7 +2347,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>115</v>
+        <v>339</v>
       </c>
       <c r="B17" s="1">
         <v>14</v>
@@ -2347,13 +2356,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>116</v>
+        <v>335</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2378,6 +2387,9 @@
       </c>
       <c r="N17" s="1">
         <v>0</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="P17" s="1">
         <v>1</v>
@@ -2394,13 +2406,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2432,7 +2444,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="B19" s="1">
         <v>16</v>
@@ -2441,13 +2453,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2479,7 +2491,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2488,13 +2500,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2526,7 +2538,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2535,13 +2547,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2573,7 +2585,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2582,13 +2594,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2620,7 +2632,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2629,13 +2641,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2667,7 +2679,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2676,13 +2688,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2714,7 +2726,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2723,13 +2735,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2761,7 +2773,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2770,13 +2782,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2808,7 +2820,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2817,13 +2829,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>141</v>
+        <v>343</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2855,7 +2867,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2864,13 +2876,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2902,7 +2914,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2911,13 +2923,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2949,7 +2961,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2958,13 +2970,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2996,7 +3008,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -3005,13 +3017,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -3043,7 +3055,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -3052,13 +3064,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -3090,7 +3102,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -3099,13 +3111,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -3137,7 +3149,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -3146,13 +3158,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>146</v>
+        <v>346</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -3184,7 +3196,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -3193,13 +3205,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -3231,7 +3243,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -3240,13 +3252,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -3278,7 +3290,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -3287,13 +3299,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -3325,7 +3337,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -3334,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -3372,7 +3384,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -3381,13 +3393,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -3419,7 +3431,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -3428,13 +3440,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -3466,7 +3478,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -3475,13 +3487,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>150</v>
+        <v>344</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -3513,7 +3525,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3522,13 +3534,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3560,7 +3572,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3569,13 +3581,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3607,7 +3619,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3616,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3648,7 +3660,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3657,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3689,7 +3701,7 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3698,7 +3710,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3730,7 +3742,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3739,7 +3751,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3771,7 +3783,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3780,7 +3792,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3812,7 +3824,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3821,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3853,7 +3865,7 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3862,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3894,7 +3906,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3903,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3935,7 +3947,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3944,7 +3956,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3976,7 +3988,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3985,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -4017,7 +4029,7 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -4026,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -4058,7 +4070,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -4067,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -4099,7 +4111,7 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -4108,7 +4120,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -4140,7 +4152,7 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -4149,7 +4161,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -4181,7 +4193,7 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -4190,7 +4202,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -4222,7 +4234,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -4231,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -4263,7 +4275,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -4272,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -4304,7 +4316,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -4313,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -4345,7 +4357,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -4354,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -4386,7 +4398,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -4395,7 +4407,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -4427,7 +4439,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -4436,7 +4448,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4468,7 +4480,7 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -4477,7 +4489,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -4509,7 +4521,7 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -4518,7 +4530,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -4550,7 +4562,7 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -4559,7 +4571,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -4591,7 +4603,7 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -4600,7 +4612,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -4641,7 +4653,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -4682,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -4723,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -4764,7 +4776,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -4805,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -4846,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -4887,7 +4899,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -4928,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4960,7 +4972,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4969,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -5001,7 +5013,7 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -5010,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -5042,7 +5054,7 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -5051,7 +5063,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -5083,7 +5095,7 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -5125,7 +5137,7 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -5167,7 +5179,7 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -5209,7 +5221,7 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -5251,7 +5263,7 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -5293,7 +5305,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -5335,7 +5347,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -5377,7 +5389,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -5419,7 +5431,7 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -5461,7 +5473,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -5503,7 +5515,7 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -5554,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5595,13 +5607,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5633,7 +5645,7 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -5642,13 +5654,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5680,7 +5692,7 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -5689,13 +5701,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -5727,7 +5739,7 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B95" s="3">
         <v>3003</v>
@@ -5736,13 +5748,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -5783,13 +5795,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -5821,7 +5833,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -5830,13 +5842,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -5868,7 +5880,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -5877,13 +5889,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5915,7 +5927,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B99" s="3">
         <v>3007</v>
@@ -5924,13 +5936,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -5962,7 +5974,7 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -5971,13 +5983,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -6018,13 +6030,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -6065,13 +6077,13 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -6112,13 +6124,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -6159,13 +6171,13 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -6206,13 +6218,13 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -6253,13 +6265,13 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -6300,13 +6312,13 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -6347,13 +6359,13 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -6394,13 +6406,13 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -6441,13 +6453,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -6488,13 +6500,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G111" s="1">
         <v>1</v>
@@ -6535,13 +6547,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G112" s="1">
         <v>1</v>
@@ -6582,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G113" s="1">
         <v>1</v>
@@ -6629,13 +6641,13 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -6676,13 +6688,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G115" s="1">
         <v>1</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -1119,100 +1119,101 @@
     <t>红发小孩</t>
   </si>
   <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通士兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/轻战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/金发女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/牧师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女仆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>纺织婆婆</t>
-  </si>
-  <si>
-    <t>路人女</t>
-  </si>
-  <si>
-    <t>黄衣服小女孩</t>
-  </si>
-  <si>
-    <t>路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者</t>
-  </si>
-  <si>
-    <t>服务员</t>
-  </si>
-  <si>
-    <t>船员</t>
-  </si>
-  <si>
-    <t>贵族商人</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通士兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/轻战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>家具店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/金发女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/牧师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女仆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2168,7 +2169,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>256</v>
@@ -2347,7 +2348,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B17" s="1">
         <v>14</v>
@@ -2359,7 +2360,7 @@
         <v>311</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>165</v>
@@ -2389,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P17" s="1">
         <v>1</v>
@@ -2444,7 +2445,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B19" s="1">
         <v>16</v>
@@ -2491,7 +2492,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2500,7 +2501,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>136</v>
@@ -2773,7 +2774,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2832,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>175</v>
@@ -3055,7 +3056,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -3102,7 +3103,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -3161,7 +3162,7 @@
         <v>266</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>182</v>
@@ -3302,10 +3303,10 @@
         <v>296</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -3490,7 +3491,7 @@
         <v>290</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>188</v>
@@ -3572,7 +3573,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3742,7 +3743,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3751,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -5221,7 +5222,7 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -5263,7 +5264,7 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -5305,7 +5306,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -5347,7 +5348,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -5389,7 +5390,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -5431,7 +5432,7 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -5473,7 +5474,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -5515,7 +5516,7 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="336">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -97,28 +97,6 @@
     <t>packageId</t>
   </si>
   <si>
-    <t>nextTalkEventId</t>
-  </si>
-  <si>
-    <t>tempTalkEventId</t>
-  </si>
-  <si>
-    <t>shopName</t>
-  </si>
-  <si>
-    <t>functionIds</t>
-  </si>
-  <si>
-    <t>植物店</t>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
     <t>Head/OldWoman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,22 +109,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>playerOperateEventId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>fightBehavior</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>动物店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/Character/丝特芬妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,10 +134,6 @@
   </si>
   <si>
     <t>Head/Chicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,9,10,11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1162,10 +1124,6 @@
   </si>
   <si>
     <t>Head/Girl7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>家具店</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1603,27 +1561,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:P115"/>
+  <dimension ref="A2:N115"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="38.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.375" style="1" customWidth="1"/>
     <col min="7" max="8" width="10.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="7.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="13.375" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="14.375" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.375" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="7.75" style="1"/>
+    <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1657,23 +1610,8 @@
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:11" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1684,7 +1622,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1702,28 +1640,13 @@
         <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1734,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
@@ -1757,22 +1680,10 @@
       <c r="K4" s="1">
         <v>1</v>
       </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1781,7 +1692,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1804,22 +1715,10 @@
       <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1828,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1851,22 +1750,10 @@
       <c r="K6" s="1">
         <v>0</v>
       </c>
-      <c r="L6" s="1">
-        <v>8001</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1875,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -1898,22 +1785,10 @@
       <c r="K7" s="1">
         <v>0</v>
       </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>200</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -1922,13 +1797,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1945,25 +1820,10 @@
       <c r="K8" s="1">
         <v>0</v>
       </c>
-      <c r="L8" s="1">
-        <v>8003</v>
-      </c>
-      <c r="M8" s="1">
-        <v>8003</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1972,13 +1832,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1995,25 +1855,10 @@
       <c r="K9" s="1">
         <v>0</v>
       </c>
-      <c r="L9" s="1">
-        <v>8002</v>
-      </c>
-      <c r="M9" s="1">
-        <v>8002</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -2022,13 +1867,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -2045,25 +1890,10 @@
       <c r="K10" s="1">
         <v>0</v>
       </c>
-      <c r="L10" s="1">
-        <v>8004</v>
-      </c>
-      <c r="M10" s="1">
-        <v>8004</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -2072,13 +1902,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -2095,25 +1925,10 @@
       <c r="K11" s="1">
         <v>0</v>
       </c>
-      <c r="L11" s="1">
-        <v>8005</v>
-      </c>
-      <c r="M11" s="1">
-        <v>8005</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -2122,13 +1937,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2145,22 +1960,10 @@
       <c r="K12" s="1">
         <v>1</v>
       </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
@@ -2169,13 +1972,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2192,22 +1995,10 @@
       <c r="K13" s="1">
         <v>1</v>
       </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B14" s="1">
         <v>11</v>
@@ -2216,13 +2007,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2239,22 +2030,10 @@
       <c r="K14" s="1">
         <v>1</v>
       </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2263,13 +2042,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2286,22 +2065,10 @@
       <c r="K15" s="1">
         <v>1</v>
       </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B16" s="1">
         <v>13</v>
@@ -2310,13 +2077,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2333,22 +2100,10 @@
       <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="B17" s="1">
         <v>14</v>
@@ -2357,13 +2112,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2380,25 +2135,10 @@
       <c r="K17" s="1">
         <v>1</v>
       </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="P17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
@@ -2407,13 +2147,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2430,22 +2170,10 @@
       <c r="K18" s="1">
         <v>1</v>
       </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B19" s="1">
         <v>16</v>
@@ -2454,13 +2182,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2477,22 +2205,10 @@
       <c r="K19" s="1">
         <v>1</v>
       </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2501,13 +2217,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2524,22 +2240,10 @@
       <c r="K20" s="1">
         <v>1</v>
       </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2548,13 +2252,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2571,22 +2275,10 @@
       <c r="K21" s="1">
         <v>1</v>
       </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2595,13 +2287,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2618,22 +2310,10 @@
       <c r="K22" s="1">
         <v>1</v>
       </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2642,13 +2322,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2665,22 +2345,10 @@
       <c r="K23" s="1">
         <v>1</v>
       </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2689,13 +2357,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2712,22 +2380,10 @@
       <c r="K24" s="1">
         <v>1</v>
       </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2736,13 +2392,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2759,22 +2415,10 @@
       <c r="K25" s="1">
         <v>1</v>
       </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2783,13 +2427,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2806,22 +2450,10 @@
       <c r="K26" s="1">
         <v>1</v>
       </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2830,13 +2462,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2853,22 +2485,10 @@
       <c r="K27" s="1">
         <v>1</v>
       </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2877,13 +2497,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2900,22 +2520,10 @@
       <c r="K28" s="1">
         <v>1</v>
       </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2924,13 +2532,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2947,22 +2555,10 @@
       <c r="K29" s="1">
         <v>1</v>
       </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2971,13 +2567,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2994,22 +2590,10 @@
       <c r="K30" s="1">
         <v>1</v>
       </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -3018,13 +2602,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -3041,22 +2625,10 @@
       <c r="K31" s="1">
         <v>1</v>
       </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -3065,13 +2637,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -3088,22 +2660,10 @@
       <c r="K32" s="1">
         <v>1</v>
       </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -3112,13 +2672,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -3135,22 +2695,10 @@
       <c r="K33" s="1">
         <v>1</v>
       </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -3159,13 +2707,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -3182,22 +2730,10 @@
       <c r="K34" s="1">
         <v>1</v>
       </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="P34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -3206,13 +2742,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -3229,22 +2765,10 @@
       <c r="K35" s="1">
         <v>1</v>
       </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -3253,13 +2777,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -3276,22 +2800,10 @@
       <c r="K36" s="1">
         <v>1</v>
       </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -3300,13 +2812,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -3323,22 +2835,10 @@
       <c r="K37" s="1">
         <v>1</v>
       </c>
-      <c r="L37" s="1">
-        <v>0</v>
-      </c>
-      <c r="M37" s="1">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1">
-        <v>0</v>
-      </c>
-      <c r="P37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -3347,13 +2847,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -3370,22 +2870,10 @@
       <c r="K38" s="1">
         <v>1</v>
       </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -3394,13 +2882,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -3417,22 +2905,10 @@
       <c r="K39" s="1">
         <v>1</v>
       </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -3441,13 +2917,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -3464,22 +2940,10 @@
       <c r="K40" s="1">
         <v>1</v>
       </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -3488,13 +2952,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -3511,22 +2975,10 @@
       <c r="K41" s="1">
         <v>1</v>
       </c>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3535,13 +2987,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3558,22 +3010,10 @@
       <c r="K42" s="1">
         <v>1</v>
       </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3582,13 +3022,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3605,22 +3045,10 @@
       <c r="K43" s="1">
         <v>1</v>
       </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
-      <c r="M43" s="1">
-        <v>0</v>
-      </c>
-      <c r="N43" s="1">
-        <v>0</v>
-      </c>
-      <c r="P43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3629,7 +3057,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3646,22 +3074,10 @@
       <c r="K44" s="1">
         <v>1</v>
       </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3670,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3687,22 +3103,10 @@
       <c r="K45" s="1">
         <v>1</v>
       </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
-      <c r="M45" s="1">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1">
-        <v>0</v>
-      </c>
-      <c r="P45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3711,7 +3115,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3728,22 +3132,10 @@
       <c r="K46" s="1">
         <v>1</v>
       </c>
-      <c r="L46" s="1">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3752,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3769,22 +3161,10 @@
       <c r="K47" s="1">
         <v>1</v>
       </c>
-      <c r="L47" s="1">
-        <v>0</v>
-      </c>
-      <c r="M47" s="1">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
-      <c r="P47" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3793,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3810,22 +3190,10 @@
       <c r="K48" s="1">
         <v>1</v>
       </c>
-      <c r="L48" s="1">
-        <v>0</v>
-      </c>
-      <c r="M48" s="1">
-        <v>0</v>
-      </c>
-      <c r="N48" s="1">
-        <v>0</v>
-      </c>
-      <c r="P48" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3834,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3851,22 +3219,10 @@
       <c r="K49" s="1">
         <v>1</v>
       </c>
-      <c r="L49" s="1">
-        <v>0</v>
-      </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3875,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3892,22 +3248,10 @@
       <c r="K50" s="1">
         <v>1</v>
       </c>
-      <c r="L50" s="1">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3916,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3933,22 +3277,10 @@
       <c r="K51" s="1">
         <v>1</v>
       </c>
-      <c r="L51" s="1">
-        <v>0</v>
-      </c>
-      <c r="M51" s="1">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3957,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3974,22 +3306,10 @@
       <c r="K52" s="1">
         <v>1</v>
       </c>
-      <c r="L52" s="1">
-        <v>0</v>
-      </c>
-      <c r="M52" s="1">
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3998,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -4015,22 +3335,10 @@
       <c r="K53" s="1">
         <v>1</v>
       </c>
-      <c r="L53" s="1">
-        <v>0</v>
-      </c>
-      <c r="M53" s="1">
-        <v>0</v>
-      </c>
-      <c r="N53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -4039,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -4056,22 +3364,10 @@
       <c r="K54" s="1">
         <v>1</v>
       </c>
-      <c r="L54" s="1">
-        <v>0</v>
-      </c>
-      <c r="M54" s="1">
-        <v>0</v>
-      </c>
-      <c r="N54" s="1">
-        <v>0</v>
-      </c>
-      <c r="P54" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -4080,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -4097,22 +3393,10 @@
       <c r="K55" s="1">
         <v>1</v>
       </c>
-      <c r="L55" s="1">
-        <v>0</v>
-      </c>
-      <c r="M55" s="1">
-        <v>0</v>
-      </c>
-      <c r="N55" s="1">
-        <v>0</v>
-      </c>
-      <c r="P55" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -4121,7 +3405,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -4138,22 +3422,10 @@
       <c r="K56" s="1">
         <v>1</v>
       </c>
-      <c r="L56" s="1">
-        <v>0</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -4162,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -4179,22 +3451,10 @@
       <c r="K57" s="1">
         <v>1</v>
       </c>
-      <c r="L57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -4203,7 +3463,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -4220,22 +3480,10 @@
       <c r="K58" s="1">
         <v>1</v>
       </c>
-      <c r="L58" s="1">
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -4244,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -4261,22 +3509,10 @@
       <c r="K59" s="1">
         <v>1</v>
       </c>
-      <c r="L59" s="1">
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1">
-        <v>0</v>
-      </c>
-      <c r="P59" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -4285,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -4302,22 +3538,10 @@
       <c r="K60" s="1">
         <v>1</v>
       </c>
-      <c r="L60" s="1">
-        <v>0</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>0</v>
-      </c>
-      <c r="P60" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -4326,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -4343,22 +3567,10 @@
       <c r="K61" s="1">
         <v>1</v>
       </c>
-      <c r="L61" s="1">
-        <v>0</v>
-      </c>
-      <c r="M61" s="1">
-        <v>0</v>
-      </c>
-      <c r="N61" s="1">
-        <v>0</v>
-      </c>
-      <c r="P61" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -4367,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -4384,22 +3596,10 @@
       <c r="K62" s="1">
         <v>1</v>
       </c>
-      <c r="L62" s="1">
-        <v>0</v>
-      </c>
-      <c r="M62" s="1">
-        <v>0</v>
-      </c>
-      <c r="N62" s="1">
-        <v>0</v>
-      </c>
-      <c r="P62" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -4408,7 +3608,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -4425,22 +3625,10 @@
       <c r="K63" s="1">
         <v>1</v>
       </c>
-      <c r="L63" s="1">
-        <v>0</v>
-      </c>
-      <c r="M63" s="1">
-        <v>0</v>
-      </c>
-      <c r="N63" s="1">
-        <v>0</v>
-      </c>
-      <c r="P63" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -4449,7 +3637,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4466,22 +3654,10 @@
       <c r="K64" s="1">
         <v>1</v>
       </c>
-      <c r="L64" s="1">
-        <v>0</v>
-      </c>
-      <c r="M64" s="1">
-        <v>0</v>
-      </c>
-      <c r="N64" s="1">
-        <v>0</v>
-      </c>
-      <c r="P64" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -4490,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -4507,22 +3683,10 @@
       <c r="K65" s="1">
         <v>1</v>
       </c>
-      <c r="L65" s="1">
-        <v>0</v>
-      </c>
-      <c r="M65" s="1">
-        <v>0</v>
-      </c>
-      <c r="N65" s="1">
-        <v>0</v>
-      </c>
-      <c r="P65" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -4531,7 +3695,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -4548,22 +3712,10 @@
       <c r="K66" s="1">
         <v>1</v>
       </c>
-      <c r="L66" s="1">
-        <v>0</v>
-      </c>
-      <c r="M66" s="1">
-        <v>0</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -4572,7 +3724,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -4589,22 +3741,10 @@
       <c r="K67" s="1">
         <v>1</v>
       </c>
-      <c r="L67" s="1">
-        <v>0</v>
-      </c>
-      <c r="M67" s="1">
-        <v>0</v>
-      </c>
-      <c r="N67" s="1">
-        <v>0</v>
-      </c>
-      <c r="P67" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -4613,7 +3753,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -4630,22 +3770,10 @@
       <c r="K68" s="1">
         <v>1</v>
       </c>
-      <c r="L68" s="1">
-        <v>0</v>
-      </c>
-      <c r="M68" s="1">
-        <v>0</v>
-      </c>
-      <c r="N68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B69" s="1">
         <v>66</v>
@@ -4654,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -4671,22 +3799,10 @@
       <c r="K69" s="1">
         <v>1</v>
       </c>
-      <c r="L69" s="1">
-        <v>0</v>
-      </c>
-      <c r="M69" s="1">
-        <v>0</v>
-      </c>
-      <c r="N69" s="1">
-        <v>0</v>
-      </c>
-      <c r="P69" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B70" s="1">
         <v>67</v>
@@ -4695,7 +3811,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -4712,22 +3828,10 @@
       <c r="K70" s="1">
         <v>1</v>
       </c>
-      <c r="L70" s="1">
-        <v>0</v>
-      </c>
-      <c r="M70" s="1">
-        <v>0</v>
-      </c>
-      <c r="N70" s="1">
-        <v>0</v>
-      </c>
-      <c r="P70" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B71" s="1">
         <v>68</v>
@@ -4736,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -4753,22 +3857,10 @@
       <c r="K71" s="1">
         <v>1</v>
       </c>
-      <c r="L71" s="1">
-        <v>0</v>
-      </c>
-      <c r="M71" s="1">
-        <v>0</v>
-      </c>
-      <c r="N71" s="1">
-        <v>0</v>
-      </c>
-      <c r="P71" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B72" s="1">
         <v>69</v>
@@ -4777,7 +3869,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -4794,22 +3886,10 @@
       <c r="K72" s="1">
         <v>1</v>
       </c>
-      <c r="L72" s="1">
-        <v>0</v>
-      </c>
-      <c r="M72" s="1">
-        <v>0</v>
-      </c>
-      <c r="N72" s="1">
-        <v>0</v>
-      </c>
-      <c r="P72" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1">
         <v>70</v>
@@ -4818,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -4835,22 +3915,10 @@
       <c r="K73" s="1">
         <v>1</v>
       </c>
-      <c r="L73" s="1">
-        <v>0</v>
-      </c>
-      <c r="M73" s="1">
-        <v>0</v>
-      </c>
-      <c r="N73" s="1">
-        <v>0</v>
-      </c>
-      <c r="P73" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B74" s="1">
         <v>71</v>
@@ -4859,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -4876,22 +3944,10 @@
       <c r="K74" s="1">
         <v>1</v>
       </c>
-      <c r="L74" s="1">
-        <v>0</v>
-      </c>
-      <c r="M74" s="1">
-        <v>0</v>
-      </c>
-      <c r="N74" s="1">
-        <v>0</v>
-      </c>
-      <c r="P74" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B75" s="1">
         <v>72</v>
@@ -4900,7 +3956,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -4917,22 +3973,10 @@
       <c r="K75" s="1">
         <v>1</v>
       </c>
-      <c r="L75" s="1">
-        <v>0</v>
-      </c>
-      <c r="M75" s="1">
-        <v>0</v>
-      </c>
-      <c r="N75" s="1">
-        <v>0</v>
-      </c>
-      <c r="P75" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B76" s="1">
         <v>73</v>
@@ -4941,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4958,22 +4002,10 @@
       <c r="K76" s="1">
         <v>1</v>
       </c>
-      <c r="L76" s="1">
-        <v>0</v>
-      </c>
-      <c r="M76" s="1">
-        <v>0</v>
-      </c>
-      <c r="N76" s="1">
-        <v>0</v>
-      </c>
-      <c r="P76" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4982,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4999,22 +4031,10 @@
       <c r="K77" s="1">
         <v>1</v>
       </c>
-      <c r="L77" s="1">
-        <v>0</v>
-      </c>
-      <c r="M77" s="1">
-        <v>0</v>
-      </c>
-      <c r="N77" s="1">
-        <v>0</v>
-      </c>
-      <c r="P77" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -5023,7 +4043,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -5040,22 +4060,10 @@
       <c r="K78" s="1">
         <v>1</v>
       </c>
-      <c r="L78" s="1">
-        <v>0</v>
-      </c>
-      <c r="M78" s="1">
-        <v>0</v>
-      </c>
-      <c r="N78" s="1">
-        <v>0</v>
-      </c>
-      <c r="P78" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -5064,7 +4072,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -5081,22 +4089,10 @@
       <c r="K79" s="1">
         <v>1</v>
       </c>
-      <c r="L79" s="1">
-        <v>0</v>
-      </c>
-      <c r="M79" s="1">
-        <v>0</v>
-      </c>
-      <c r="N79" s="1">
-        <v>0</v>
-      </c>
-      <c r="P79" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -5123,22 +4119,10 @@
       <c r="K80" s="1">
         <v>1</v>
       </c>
-      <c r="L80" s="1">
-        <v>0</v>
-      </c>
-      <c r="M80" s="1">
-        <v>0</v>
-      </c>
-      <c r="N80" s="1">
-        <v>0</v>
-      </c>
-      <c r="P80" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -5165,22 +4149,10 @@
       <c r="K81" s="1">
         <v>1</v>
       </c>
-      <c r="L81" s="1">
-        <v>0</v>
-      </c>
-      <c r="M81" s="1">
-        <v>0</v>
-      </c>
-      <c r="N81" s="1">
-        <v>0</v>
-      </c>
-      <c r="P81" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -5207,22 +4179,10 @@
       <c r="K82" s="1">
         <v>1</v>
       </c>
-      <c r="L82" s="1">
-        <v>0</v>
-      </c>
-      <c r="M82" s="1">
-        <v>0</v>
-      </c>
-      <c r="N82" s="1">
-        <v>0</v>
-      </c>
-      <c r="P82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -5249,22 +4209,10 @@
       <c r="K83" s="1">
         <v>1</v>
       </c>
-      <c r="L83" s="1">
-        <v>0</v>
-      </c>
-      <c r="M83" s="1">
-        <v>0</v>
-      </c>
-      <c r="N83" s="1">
-        <v>0</v>
-      </c>
-      <c r="P83" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -5291,22 +4239,10 @@
       <c r="K84" s="1">
         <v>1</v>
       </c>
-      <c r="L84" s="1">
-        <v>0</v>
-      </c>
-      <c r="M84" s="1">
-        <v>0</v>
-      </c>
-      <c r="N84" s="1">
-        <v>0</v>
-      </c>
-      <c r="P84" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -5333,22 +4269,10 @@
       <c r="K85" s="1">
         <v>1</v>
       </c>
-      <c r="L85" s="1">
-        <v>0</v>
-      </c>
-      <c r="M85" s="1">
-        <v>0</v>
-      </c>
-      <c r="N85" s="1">
-        <v>0</v>
-      </c>
-      <c r="P85" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -5375,22 +4299,10 @@
       <c r="K86" s="1">
         <v>1</v>
       </c>
-      <c r="L86" s="1">
-        <v>0</v>
-      </c>
-      <c r="M86" s="1">
-        <v>0</v>
-      </c>
-      <c r="N86" s="1">
-        <v>0</v>
-      </c>
-      <c r="P86" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -5417,22 +4329,10 @@
       <c r="K87" s="1">
         <v>1</v>
       </c>
-      <c r="L87" s="1">
-        <v>0</v>
-      </c>
-      <c r="M87" s="1">
-        <v>0</v>
-      </c>
-      <c r="N87" s="1">
-        <v>0</v>
-      </c>
-      <c r="P87" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -5459,22 +4359,10 @@
       <c r="K88" s="1">
         <v>1</v>
       </c>
-      <c r="L88" s="1">
-        <v>0</v>
-      </c>
-      <c r="M88" s="1">
-        <v>0</v>
-      </c>
-      <c r="N88" s="1">
-        <v>0</v>
-      </c>
-      <c r="P88" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -5501,22 +4389,10 @@
       <c r="K89" s="1">
         <v>1</v>
       </c>
-      <c r="L89" s="1">
-        <v>0</v>
-      </c>
-      <c r="M89" s="1">
-        <v>0</v>
-      </c>
-      <c r="N89" s="1">
-        <v>0</v>
-      </c>
-      <c r="P89" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -5543,20 +4419,8 @@
       <c r="K90" s="1">
         <v>1</v>
       </c>
-      <c r="L90" s="1">
-        <v>0</v>
-      </c>
-      <c r="M90" s="1">
-        <v>0</v>
-      </c>
-      <c r="N90" s="1">
-        <v>0</v>
-      </c>
-      <c r="P90" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
         <v>14</v>
       </c>
@@ -5567,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -5584,22 +4448,10 @@
       <c r="K91" s="1">
         <v>0</v>
       </c>
-      <c r="L91" s="1">
-        <v>0</v>
-      </c>
-      <c r="M91" s="1">
-        <v>0</v>
-      </c>
-      <c r="N91" s="1">
-        <v>0</v>
-      </c>
-      <c r="P91" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    </row>
+    <row r="92" spans="1:11" ht="27" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B92" s="1">
         <v>3000</v>
@@ -5608,13 +4460,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -5631,22 +4483,10 @@
       <c r="K92" s="1">
         <v>0</v>
       </c>
-      <c r="L92" s="1">
-        <v>8100</v>
-      </c>
-      <c r="M92" s="1">
-        <v>8100</v>
-      </c>
-      <c r="N92" s="1">
-        <v>0</v>
-      </c>
-      <c r="P92" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -5655,13 +4495,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -5678,22 +4518,10 @@
       <c r="K93" s="1">
         <v>0</v>
       </c>
-      <c r="L93" s="1">
-        <v>8100</v>
-      </c>
-      <c r="M93" s="1">
-        <v>8100</v>
-      </c>
-      <c r="N93" s="1">
-        <v>0</v>
-      </c>
-      <c r="P93" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -5702,13 +4530,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -5725,22 +4553,10 @@
       <c r="K94" s="1">
         <v>0</v>
       </c>
-      <c r="L94" s="1">
-        <v>0</v>
-      </c>
-      <c r="M94" s="1">
-        <v>0</v>
-      </c>
-      <c r="N94" s="1">
-        <v>0</v>
-      </c>
-      <c r="P94" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B95" s="3">
         <v>3003</v>
@@ -5749,13 +4565,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -5772,22 +4588,10 @@
       <c r="K95" s="1">
         <v>0</v>
       </c>
-      <c r="L95" s="1">
-        <v>0</v>
-      </c>
-      <c r="M95" s="1">
-        <v>0</v>
-      </c>
-      <c r="N95" s="1">
-        <v>0</v>
-      </c>
-      <c r="P95" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B96" s="3">
         <v>3004</v>
@@ -5796,13 +4600,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -5819,22 +4623,10 @@
       <c r="K96" s="1">
         <v>0</v>
       </c>
-      <c r="L96" s="1">
-        <v>0</v>
-      </c>
-      <c r="M96" s="1">
-        <v>0</v>
-      </c>
-      <c r="N96" s="1">
-        <v>0</v>
-      </c>
-      <c r="P96" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -5843,13 +4635,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -5866,22 +4658,10 @@
       <c r="K97" s="1">
         <v>0</v>
       </c>
-      <c r="L97" s="1">
-        <v>0</v>
-      </c>
-      <c r="M97" s="1">
-        <v>0</v>
-      </c>
-      <c r="N97" s="1">
-        <v>0</v>
-      </c>
-      <c r="P97" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -5890,13 +4670,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -5913,22 +4693,10 @@
       <c r="K98" s="1">
         <v>0</v>
       </c>
-      <c r="L98" s="1">
-        <v>0</v>
-      </c>
-      <c r="M98" s="1">
-        <v>0</v>
-      </c>
-      <c r="N98" s="1">
-        <v>0</v>
-      </c>
-      <c r="P98" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B99" s="3">
         <v>3007</v>
@@ -5937,13 +4705,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -5960,22 +4728,10 @@
       <c r="K99" s="1">
         <v>0</v>
       </c>
-      <c r="L99" s="1">
-        <v>0</v>
-      </c>
-      <c r="M99" s="1">
-        <v>0</v>
-      </c>
-      <c r="N99" s="1">
-        <v>0</v>
-      </c>
-      <c r="P99" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -5984,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -6007,22 +4763,10 @@
       <c r="K100" s="1">
         <v>0</v>
       </c>
-      <c r="L100" s="1">
-        <v>0</v>
-      </c>
-      <c r="M100" s="1">
-        <v>0</v>
-      </c>
-      <c r="N100" s="1">
-        <v>0</v>
-      </c>
-      <c r="P100" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B101" s="3">
         <v>3009</v>
@@ -6031,13 +4775,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -6054,22 +4798,10 @@
       <c r="K101" s="1">
         <v>0</v>
       </c>
-      <c r="L101" s="1">
-        <v>0</v>
-      </c>
-      <c r="M101" s="1">
-        <v>0</v>
-      </c>
-      <c r="N101" s="1">
-        <v>0</v>
-      </c>
-      <c r="P101" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B102" s="3">
         <v>3010</v>
@@ -6078,13 +4810,13 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -6101,22 +4833,10 @@
       <c r="K102" s="1">
         <v>0</v>
       </c>
-      <c r="L102" s="1">
-        <v>0</v>
-      </c>
-      <c r="M102" s="1">
-        <v>0</v>
-      </c>
-      <c r="N102" s="1">
-        <v>0</v>
-      </c>
-      <c r="P102" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B103" s="3">
         <v>3011</v>
@@ -6125,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -6148,22 +4868,10 @@
       <c r="K103" s="1">
         <v>0</v>
       </c>
-      <c r="L103" s="1">
-        <v>0</v>
-      </c>
-      <c r="M103" s="1">
-        <v>0</v>
-      </c>
-      <c r="N103" s="1">
-        <v>0</v>
-      </c>
-      <c r="P103" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B104" s="3">
         <v>3012</v>
@@ -6172,13 +4880,13 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -6195,22 +4903,10 @@
       <c r="K104" s="1">
         <v>0</v>
       </c>
-      <c r="L104" s="1">
-        <v>0</v>
-      </c>
-      <c r="M104" s="1">
-        <v>0</v>
-      </c>
-      <c r="N104" s="1">
-        <v>0</v>
-      </c>
-      <c r="P104" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B105" s="3">
         <v>3013</v>
@@ -6219,13 +4915,13 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -6242,22 +4938,10 @@
       <c r="K105" s="1">
         <v>0</v>
       </c>
-      <c r="L105" s="1">
-        <v>0</v>
-      </c>
-      <c r="M105" s="1">
-        <v>0</v>
-      </c>
-      <c r="N105" s="1">
-        <v>0</v>
-      </c>
-      <c r="P105" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B106" s="3">
         <v>3100</v>
@@ -6266,13 +4950,13 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -6289,22 +4973,10 @@
       <c r="K106" s="1">
         <v>0</v>
       </c>
-      <c r="L106" s="1">
-        <v>0</v>
-      </c>
-      <c r="M106" s="1">
-        <v>0</v>
-      </c>
-      <c r="N106" s="1">
-        <v>0</v>
-      </c>
-      <c r="P106" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B107" s="3">
         <v>3102</v>
@@ -6313,13 +4985,13 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -6336,22 +5008,10 @@
       <c r="K107" s="1">
         <v>0</v>
       </c>
-      <c r="L107" s="1">
-        <v>0</v>
-      </c>
-      <c r="M107" s="1">
-        <v>0</v>
-      </c>
-      <c r="N107" s="1">
-        <v>0</v>
-      </c>
-      <c r="P107" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B108" s="3">
         <v>3104</v>
@@ -6360,13 +5020,13 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -6383,22 +5043,10 @@
       <c r="K108" s="1">
         <v>0</v>
       </c>
-      <c r="L108" s="1">
-        <v>0</v>
-      </c>
-      <c r="M108" s="1">
-        <v>0</v>
-      </c>
-      <c r="N108" s="1">
-        <v>0</v>
-      </c>
-      <c r="P108" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B109" s="3">
         <v>3106</v>
@@ -6407,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -6430,22 +5078,10 @@
       <c r="K109" s="1">
         <v>0</v>
       </c>
-      <c r="L109" s="1">
-        <v>0</v>
-      </c>
-      <c r="M109" s="1">
-        <v>0</v>
-      </c>
-      <c r="N109" s="1">
-        <v>0</v>
-      </c>
-      <c r="P109" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B110" s="3">
         <v>3107</v>
@@ -6454,13 +5090,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -6477,22 +5113,10 @@
       <c r="K110" s="1">
         <v>0</v>
       </c>
-      <c r="L110" s="1">
-        <v>0</v>
-      </c>
-      <c r="M110" s="1">
-        <v>0</v>
-      </c>
-      <c r="N110" s="1">
-        <v>0</v>
-      </c>
-      <c r="P110" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B111" s="3">
         <v>3108</v>
@@ -6501,13 +5125,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G111" s="1">
         <v>1</v>
@@ -6524,22 +5148,10 @@
       <c r="K111" s="1">
         <v>0</v>
       </c>
-      <c r="L111" s="1">
-        <v>0</v>
-      </c>
-      <c r="M111" s="1">
-        <v>0</v>
-      </c>
-      <c r="N111" s="1">
-        <v>0</v>
-      </c>
-      <c r="P111" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B112" s="3">
         <v>3110</v>
@@ -6548,13 +5160,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="G112" s="1">
         <v>1</v>
@@ -6571,22 +5183,10 @@
       <c r="K112" s="1">
         <v>0</v>
       </c>
-      <c r="L112" s="1">
-        <v>0</v>
-      </c>
-      <c r="M112" s="1">
-        <v>0</v>
-      </c>
-      <c r="N112" s="1">
-        <v>0</v>
-      </c>
-      <c r="P112" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B113" s="3">
         <v>3111</v>
@@ -6595,13 +5195,13 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G113" s="1">
         <v>1</v>
@@ -6618,22 +5218,10 @@
       <c r="K113" s="1">
         <v>0</v>
       </c>
-      <c r="L113" s="1">
-        <v>0</v>
-      </c>
-      <c r="M113" s="1">
-        <v>0</v>
-      </c>
-      <c r="N113" s="1">
-        <v>0</v>
-      </c>
-      <c r="P113" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B114" s="3">
         <v>3112</v>
@@ -6642,13 +5230,13 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -6665,22 +5253,10 @@
       <c r="K114" s="1">
         <v>0</v>
       </c>
-      <c r="L114" s="1">
-        <v>0</v>
-      </c>
-      <c r="M114" s="1">
-        <v>0</v>
-      </c>
-      <c r="N114" s="1">
-        <v>0</v>
-      </c>
-      <c r="P114" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.15">
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B115" s="1">
         <v>3114</v>
@@ -6689,13 +5265,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="G115" s="1">
         <v>1</v>
@@ -6711,18 +5287,6 @@
       </c>
       <c r="K115" s="1">
         <v>0</v>
-      </c>
-      <c r="L115" s="1">
-        <v>0</v>
-      </c>
-      <c r="M115" s="1">
-        <v>0</v>
-      </c>
-      <c r="N115" s="1">
-        <v>0</v>
-      </c>
-      <c r="P115" s="1">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -1561,7 +1561,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:N115"/>
+  <dimension ref="A2:K115"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="338">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -579,599 +579,608 @@
     <t>Prefabs/Character/天使</t>
   </si>
   <si>
+    <t>Prefabs/Character/女仆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布拉德利</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布蓝达</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/希贝儿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/帕特里克</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/朵儿洁</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/梅林</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/渔夫</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/船长</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/水手</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/游侠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/爱格伯特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/牧师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王后</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸭</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/白兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/松鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/野兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/火烈鸟</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/刺猬</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/大象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/企鹅</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/袋鼠</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/SmallChicken</t>
+  </si>
+  <si>
+    <t>Icon/Chicken</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/Rabbit</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/松鼠</t>
+  </si>
+  <si>
+    <t>Icon/野兔</t>
+  </si>
+  <si>
+    <t>Icon/火烈鸟</t>
+  </si>
+  <si>
+    <t>Icon/鹿</t>
+  </si>
+  <si>
+    <t>Icon/刺猬</t>
+  </si>
+  <si>
+    <t>Icon/大象</t>
+  </si>
+  <si>
+    <t>Icon/企鹅</t>
+  </si>
+  <si>
+    <t>Icon/袋鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/侦探</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鬼族男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女魔族</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小精灵红</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通士兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/轻战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/金发女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/牧师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女仆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Prefabs/Character/奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女仆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布拉德利</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布蓝达</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/希贝儿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/帕特里克</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/朵儿洁</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/梅林</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/渔夫</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/船长</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/水手</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/游侠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/爱格伯特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/牧师</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王后</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/管家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/艾琳娜</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/莱特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/金发女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/阿尔杰农</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/贵族骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老英雄</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老公公</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武道女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/格斗家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/战斗学者</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/异国女子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小花</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小美</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小混混</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/官员</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女诗人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/商人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/双辫女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/匪徒</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/制服小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔女郎</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸭</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/白兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/松鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/野兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/火烈鸟</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/刺猬</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/大象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/企鹅</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/袋鼠</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/格吉尔</t>
-  </si>
-  <si>
-    <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/马</t>
-  </si>
-  <si>
-    <t>Icon/玛德琳</t>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-  </si>
-  <si>
-    <t>Icon/丝特芬妮</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/公主</t>
-  </si>
-  <si>
-    <t>Icon/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Icon/国王</t>
-  </si>
-  <si>
-    <t>Icon/天使</t>
-  </si>
-  <si>
-    <t>Icon/朵儿洁</t>
-  </si>
-  <si>
-    <t>Icon/渔夫</t>
-  </si>
-  <si>
-    <t>Icon/船长</t>
-  </si>
-  <si>
-    <t>Icon/水手</t>
-  </si>
-  <si>
-    <t>Icon/游侠</t>
-  </si>
-  <si>
-    <t>Icon/牧师</t>
-  </si>
-  <si>
-    <t>Icon/王子</t>
-  </si>
-  <si>
-    <t>Icon/王后</t>
-  </si>
-  <si>
-    <t>Icon/管家</t>
-  </si>
-  <si>
-    <t>Icon/SmallChicken</t>
-  </si>
-  <si>
-    <t>Icon/Chicken</t>
-  </si>
-  <si>
-    <t>Icon/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/Rabbit</t>
-  </si>
-  <si>
-    <t>Icon/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/猪</t>
-  </si>
-  <si>
-    <t>Icon/奶牛</t>
-  </si>
-  <si>
-    <t>Icon/松鼠</t>
-  </si>
-  <si>
-    <t>Icon/野兔</t>
-  </si>
-  <si>
-    <t>Icon/火烈鸟</t>
-  </si>
-  <si>
-    <t>Icon/鹿</t>
-  </si>
-  <si>
-    <t>Icon/刺猬</t>
-  </si>
-  <si>
-    <t>Icon/大象</t>
-  </si>
-  <si>
-    <t>Icon/企鹅</t>
-  </si>
-  <si>
-    <t>Icon/袋鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鬼族男</t>
-  </si>
-  <si>
-    <t>女魔族</t>
-  </si>
-  <si>
-    <t>小精灵红</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/侦探</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/鬼族男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女魔族</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小精灵红</t>
-  </si>
-  <si>
-    <t>中年路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中年路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红发小孩</t>
-  </si>
-  <si>
-    <t>路人女</t>
-  </si>
-  <si>
-    <t>黄衣服小女孩</t>
-  </si>
-  <si>
-    <t>路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者</t>
-  </si>
-  <si>
-    <t>服务员</t>
-  </si>
-  <si>
-    <t>船员</t>
-  </si>
-  <si>
-    <t>贵族商人</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通士兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/轻战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Head/Girl7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/金发女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/牧师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女仆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1657,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>15</v>
@@ -1692,7 +1701,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1727,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1762,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>101</v>
@@ -1797,7 +1806,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>20</v>
@@ -1832,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>25</v>
@@ -1867,7 +1876,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>26</v>
@@ -1902,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>27</v>
@@ -1928,7 +1937,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1937,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>102</v>
@@ -1972,10 +1981,10 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>150</v>
@@ -2007,7 +2016,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>121</v>
@@ -2033,7 +2042,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2042,7 +2051,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>122</v>
@@ -2077,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>123</v>
@@ -2103,19 +2112,19 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B17" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>323</v>
+        <v>103</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>154</v>
@@ -2147,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>124</v>
@@ -2173,22 +2182,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B19" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>103</v>
+        <v>337</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>156</v>
+        <v>336</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2208,7 +2217,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2217,13 +2226,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>125</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2243,7 +2252,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2252,13 +2261,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>126</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2278,7 +2287,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2287,13 +2296,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>104</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2313,7 +2322,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2322,13 +2331,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>105</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2348,7 +2357,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2357,13 +2366,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>107</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2392,13 +2401,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>108</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2418,7 +2427,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2427,13 +2436,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>109</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2462,13 +2471,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2488,7 +2497,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2497,13 +2506,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2532,13 +2541,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>127</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2567,13 +2576,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>128</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2602,13 +2611,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>129</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2628,7 +2637,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2637,13 +2646,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>130</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2663,7 +2672,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2672,13 +2681,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>111</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2707,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2742,13 +2751,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>131</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -2777,13 +2786,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -2803,7 +2812,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -2812,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -2847,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -2873,7 +2882,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -2882,13 +2891,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>113</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -2908,7 +2917,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -2917,13 +2926,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>114</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -2943,7 +2952,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -2952,13 +2961,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -2978,7 +2987,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -2987,13 +2996,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>115</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3013,7 +3022,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3022,13 +3031,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>116</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3057,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3086,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3115,7 +3124,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3135,7 +3144,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3144,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3173,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3202,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3231,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3260,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3289,7 +3298,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3318,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3347,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3376,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -3405,7 +3414,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3434,7 +3443,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3463,7 +3472,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -3492,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -3521,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3550,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -3579,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -3608,7 +3617,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -3637,7 +3646,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -3666,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -3695,7 +3704,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -3724,7 +3733,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -3753,7 +3762,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -3782,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -3811,7 +3820,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -3840,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -3869,7 +3878,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -3898,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -3927,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -3956,7 +3965,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -3985,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4005,7 +4014,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4014,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4034,7 +4043,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -4043,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4063,7 +4072,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -4072,7 +4081,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4092,7 +4101,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -4122,7 +4131,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -4152,7 +4161,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -4182,13 +4191,19 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
       </c>
       <c r="C83" s="1">
         <v>1</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="F83" s="1" t="str">
         <f>"Prefabs/Character/"&amp;A83</f>
@@ -4212,7 +4227,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -4242,7 +4257,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -4272,7 +4287,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -4302,7 +4317,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -4332,7 +4347,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -4362,7 +4377,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -4392,7 +4407,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -4431,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -4460,13 +4475,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -4495,13 +4510,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -4530,13 +4545,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>134</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -4565,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>134</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -4600,13 +4615,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -4635,13 +4650,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -4670,13 +4685,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -4705,13 +4720,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -4740,13 +4755,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>136</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -4775,13 +4790,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>136</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -4810,13 +4825,13 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -4845,13 +4860,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -4880,13 +4895,13 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -4915,13 +4930,13 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -4950,13 +4965,13 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>139</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -4985,13 +5000,13 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>140</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -5020,13 +5035,13 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>141</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -5055,13 +5070,13 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -5090,13 +5105,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -5125,13 +5140,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G111" s="1">
         <v>1</v>
@@ -5160,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G112" s="1">
         <v>1</v>
@@ -5195,13 +5210,13 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G113" s="1">
         <v>1</v>
@@ -5230,13 +5245,13 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -5265,13 +5280,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G115" s="1">
         <v>1</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory_hub\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="339">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,10 +68,6 @@
   </si>
   <si>
     <t>Prefabs/Character/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -388,14 +384,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Head/Boy2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1181,6 +1169,21 @@
   </si>
   <si>
     <t>Head/Girl7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有鞍马</t>
+  </si>
+  <si>
+    <t>Icon/有鞍马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/有鞍马</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1631,7 +1634,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1646,13 +1649,13 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.15">
@@ -1666,10 +1669,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
@@ -1692,7 +1695,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1701,10 +1704,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>11</v>
@@ -1727,7 +1730,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1736,10 +1739,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>12</v>
@@ -1762,7 +1765,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1771,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>238</v>
+        <v>336</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>101</v>
+        <v>337</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1797,7 +1800,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -1806,13 +1809,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1832,7 +1835,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1841,13 +1844,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1867,7 +1870,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -1876,13 +1879,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1902,7 +1905,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1911,13 +1914,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1937,7 +1940,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1946,13 +1949,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1972,7 +1975,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
@@ -1981,13 +1984,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2007,7 +2010,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1">
         <v>11</v>
@@ -2016,13 +2019,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2042,7 +2045,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2051,13 +2054,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2077,7 +2080,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1">
         <v>13</v>
@@ -2086,13 +2089,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2112,7 +2115,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -2121,13 +2124,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2147,7 +2150,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
@@ -2156,13 +2159,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2182,7 +2185,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B19" s="1">
         <v>14</v>
@@ -2191,13 +2194,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2217,7 +2220,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2226,13 +2229,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2252,7 +2255,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2261,13 +2264,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2287,7 +2290,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2296,13 +2299,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2322,7 +2325,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2331,13 +2334,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2357,7 +2360,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2366,13 +2369,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2392,7 +2395,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2401,13 +2404,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2427,7 +2430,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2436,13 +2439,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2462,7 +2465,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2471,13 +2474,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2497,7 +2500,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2506,13 +2509,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2532,7 +2535,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2541,13 +2544,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2567,7 +2570,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2576,13 +2579,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2602,7 +2605,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -2611,13 +2614,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2637,7 +2640,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2646,13 +2649,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2672,7 +2675,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2681,13 +2684,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2707,7 +2710,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -2716,13 +2719,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2742,7 +2745,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -2751,13 +2754,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -2777,7 +2780,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -2786,13 +2789,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -2812,7 +2815,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -2821,13 +2824,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -2847,7 +2850,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -2856,13 +2859,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -2882,7 +2885,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -2891,13 +2894,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -2917,7 +2920,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -2926,13 +2929,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -2952,7 +2955,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -2961,13 +2964,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -2987,7 +2990,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -2996,13 +2999,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3022,7 +3025,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3031,13 +3034,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3057,7 +3060,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3066,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3086,7 +3089,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3095,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3115,7 +3118,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3124,7 +3127,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3144,7 +3147,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3153,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3173,7 +3176,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3182,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3202,7 +3205,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3211,7 +3214,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3231,7 +3234,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3240,7 +3243,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3260,7 +3263,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3269,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3289,7 +3292,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3298,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3318,7 +3321,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3327,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3347,7 +3350,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -3356,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3376,7 +3379,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -3385,7 +3388,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -3405,7 +3408,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -3414,7 +3417,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3434,7 +3437,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -3443,7 +3446,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3463,7 +3466,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -3472,7 +3475,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -3492,7 +3495,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -3501,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -3521,7 +3524,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -3530,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3550,7 +3553,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -3559,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -3579,7 +3582,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -3588,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -3608,7 +3611,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -3617,7 +3620,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -3637,7 +3640,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -3646,7 +3649,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -3666,7 +3669,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -3675,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -3695,7 +3698,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -3704,7 +3707,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -3724,7 +3727,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -3733,7 +3736,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -3753,7 +3756,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -3762,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -3782,7 +3785,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B69" s="1">
         <v>66</v>
@@ -3791,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -3811,7 +3814,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B70" s="1">
         <v>67</v>
@@ -3820,7 +3823,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -3840,7 +3843,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1">
         <v>68</v>
@@ -3849,7 +3852,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -3869,7 +3872,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B72" s="1">
         <v>69</v>
@@ -3878,7 +3881,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -3898,7 +3901,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" s="1">
         <v>70</v>
@@ -3907,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -3927,7 +3930,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B74" s="1">
         <v>71</v>
@@ -3936,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -3956,7 +3959,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B75" s="1">
         <v>72</v>
@@ -3965,7 +3968,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -3985,7 +3988,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B76" s="1">
         <v>73</v>
@@ -3994,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4014,7 +4017,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4023,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4043,7 +4046,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -4052,7 +4055,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4072,7 +4075,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -4081,7 +4084,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4101,7 +4104,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -4131,7 +4134,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -4161,7 +4164,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -4191,7 +4194,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -4200,10 +4203,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F83" s="1" t="str">
         <f>"Prefabs/Character/"&amp;A83</f>
@@ -4227,7 +4230,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -4257,7 +4260,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -4287,7 +4290,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -4317,7 +4320,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -4347,7 +4350,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -4377,7 +4380,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -4407,7 +4410,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -4437,7 +4440,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B91" s="1">
         <v>100</v>
@@ -4446,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -4466,7 +4469,7 @@
     </row>
     <row r="92" spans="1:11" ht="27" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B92" s="1">
         <v>3000</v>
@@ -4475,13 +4478,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -4501,7 +4504,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -4510,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -4536,7 +4539,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -4545,13 +4548,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -4571,7 +4574,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B95" s="3">
         <v>3003</v>
@@ -4580,13 +4583,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -4606,7 +4609,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B96" s="3">
         <v>3004</v>
@@ -4615,13 +4618,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -4641,7 +4644,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -4650,13 +4653,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -4676,7 +4679,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -4685,13 +4688,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -4711,7 +4714,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B99" s="3">
         <v>3007</v>
@@ -4720,13 +4723,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -4746,7 +4749,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -4755,13 +4758,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -4781,7 +4784,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B101" s="3">
         <v>3009</v>
@@ -4790,13 +4793,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -4816,7 +4819,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B102" s="3">
         <v>3010</v>
@@ -4825,13 +4828,13 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -4851,7 +4854,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B103" s="3">
         <v>3011</v>
@@ -4860,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -4886,7 +4889,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B104" s="3">
         <v>3012</v>
@@ -4895,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -4921,7 +4924,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B105" s="3">
         <v>3013</v>
@@ -4930,13 +4933,13 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -4956,7 +4959,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B106" s="3">
         <v>3100</v>
@@ -4965,13 +4968,13 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -4991,7 +4994,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B107" s="3">
         <v>3102</v>
@@ -5000,13 +5003,13 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -5026,7 +5029,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B108" s="3">
         <v>3104</v>
@@ -5035,13 +5038,13 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -5061,7 +5064,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B109" s="3">
         <v>3106</v>
@@ -5070,13 +5073,13 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -5096,7 +5099,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B110" s="3">
         <v>3107</v>
@@ -5105,13 +5108,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -5131,7 +5134,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B111" s="3">
         <v>3108</v>
@@ -5140,13 +5143,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G111" s="1">
         <v>1</v>
@@ -5166,7 +5169,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B112" s="3">
         <v>3110</v>
@@ -5175,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G112" s="1">
         <v>1</v>
@@ -5201,7 +5204,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B113" s="3">
         <v>3111</v>
@@ -5210,13 +5213,13 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G113" s="1">
         <v>1</v>
@@ -5236,7 +5239,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B114" s="3">
         <v>3112</v>
@@ -5245,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -5271,7 +5274,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B115" s="1">
         <v>3114</v>
@@ -5280,13 +5283,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G115" s="1">
         <v>1</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="346">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -165,55 +165,1004 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火烈鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鹿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺猬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>企鹅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>袋鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔女郎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莎拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制服小孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>女诗人</t>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>武道女</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杰克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/woman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/公主</t>
+  </si>
+  <si>
+    <t>Head/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Head/国王</t>
+  </si>
+  <si>
+    <t>Head/天使</t>
+  </si>
+  <si>
+    <t>Head/女仆</t>
+  </si>
+  <si>
+    <t>Head/女骑士</t>
+  </si>
+  <si>
+    <t>Head/渔夫</t>
+  </si>
+  <si>
+    <t>Head/船长</t>
+  </si>
+  <si>
+    <t>Head/水手</t>
+  </si>
+  <si>
+    <t>Head/游侠</t>
+  </si>
+  <si>
+    <t>Head/王子</t>
+  </si>
+  <si>
+    <t>Head/王后</t>
+  </si>
+  <si>
+    <t>Head/管家</t>
+  </si>
+  <si>
+    <t>Head/鸭子</t>
+  </si>
+  <si>
+    <t>Head/绵羊</t>
+  </si>
+  <si>
+    <t>Head/猪</t>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+  </si>
+  <si>
+    <t>Head/马</t>
+  </si>
+  <si>
+    <t>Head/松鼠</t>
+  </si>
+  <si>
+    <t>Head/野兔</t>
+  </si>
+  <si>
+    <t>Head/火烈鸟</t>
+  </si>
+  <si>
+    <t>Head/鹿</t>
+  </si>
+  <si>
+    <t>Head/刺猬</t>
+  </si>
+  <si>
+    <t>Head/大象</t>
+  </si>
+  <si>
+    <t>Head/企鹅</t>
+  </si>
+  <si>
+    <t>Head/袋鼠</t>
+  </si>
+  <si>
+    <t>Head/Rabbit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/亚度尼斯</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/修女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/公主</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/国王</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/坎蒂丝</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/天使</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女仆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布拉德利</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布蓝达</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/希贝儿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/帕特里克</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/朵儿洁</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/梅林</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/渔夫</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/船长</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/水手</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/游侠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/爱格伯特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/牧师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王后</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸡</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸭</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/白兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/松鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/野兔</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/火烈鸟</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鹿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/刺猬</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/大象</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/企鹅</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/袋鼠</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/松鼠</t>
+  </si>
+  <si>
+    <t>Icon/野兔</t>
+  </si>
+  <si>
+    <t>Icon/火烈鸟</t>
+  </si>
+  <si>
+    <t>Icon/鹿</t>
+  </si>
+  <si>
+    <t>Icon/刺猬</t>
+  </si>
+  <si>
+    <t>Icon/大象</t>
+  </si>
+  <si>
+    <t>Icon/企鹅</t>
+  </si>
+  <si>
+    <t>Icon/袋鼠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/侦探</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鬼族男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女魔族</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小精灵红</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通士兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/轻战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/金发女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/牧师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女仆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有鞍马</t>
+  </si>
+  <si>
+    <t>Icon/有鞍马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/有鞍马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>幼鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>幼牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>松鼠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野兔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火烈鸟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼鹿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刺猬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>企鹅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>袋鼠</t>
+    <t>Icon/幼鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鸭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/幼鸭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -221,226 +1170,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>幼马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侦探</t>
-  </si>
-  <si>
-    <t>琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兔女郎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莎拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>制服小孩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>勇者女</t>
-  </si>
-  <si>
-    <t>勇者男</t>
-  </si>
-  <si>
-    <t>匪徒</t>
-  </si>
-  <si>
-    <t>双辫女孩</t>
-  </si>
-  <si>
-    <t>商人</t>
-  </si>
-  <si>
-    <t>罗伊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天使</t>
-  </si>
-  <si>
-    <t>女战士</t>
-  </si>
-  <si>
-    <t>女诗人</t>
-  </si>
-  <si>
-    <t>女轻战士</t>
-  </si>
-  <si>
-    <t>官员</t>
-  </si>
-  <si>
-    <t>小女孩</t>
-  </si>
-  <si>
-    <t>小女孩2</t>
-  </si>
-  <si>
-    <t>小孩</t>
-  </si>
-  <si>
-    <t>小混混</t>
-  </si>
-  <si>
-    <t>小男孩</t>
-  </si>
-  <si>
-    <t>小男孩2</t>
-  </si>
-  <si>
-    <t>小美</t>
-  </si>
-  <si>
-    <t>小花</t>
-  </si>
-  <si>
-    <t>异国女子</t>
-  </si>
-  <si>
-    <t>战斗学者</t>
-  </si>
-  <si>
-    <t>格斗家</t>
-  </si>
-  <si>
-    <t>武士</t>
-  </si>
-  <si>
-    <t>武道女</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游侠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杰克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老公公</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老英雄</t>
-  </si>
-  <si>
-    <t>贵族骑士</t>
-  </si>
-  <si>
-    <t>重装女战士</t>
-  </si>
-  <si>
-    <t>重装战士</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>iconName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼鸭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldMan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/woman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/man</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/man1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl5</t>
+    <t>Icon/幼兔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -448,7 +1178,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>鸭子</t>
+    <t>Icon/家兔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -456,734 +1186,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Icon/幼绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>幼猪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Head/公主</t>
-  </si>
-  <si>
-    <t>Head/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Head/国王</t>
-  </si>
-  <si>
-    <t>Head/天使</t>
-  </si>
-  <si>
-    <t>Head/女仆</t>
-  </si>
-  <si>
-    <t>Head/女骑士</t>
-  </si>
-  <si>
-    <t>Head/渔夫</t>
-  </si>
-  <si>
-    <t>Head/船长</t>
-  </si>
-  <si>
-    <t>Head/水手</t>
-  </si>
-  <si>
-    <t>Head/游侠</t>
-  </si>
-  <si>
-    <t>Head/王子</t>
-  </si>
-  <si>
-    <t>Head/王后</t>
-  </si>
-  <si>
-    <t>Head/管家</t>
-  </si>
-  <si>
-    <t>Head/鸭子</t>
-  </si>
-  <si>
-    <t>Head/绵羊</t>
-  </si>
-  <si>
-    <t>Head/猪</t>
-  </si>
-  <si>
-    <t>Head/奶牛</t>
-  </si>
-  <si>
-    <t>Head/马</t>
-  </si>
-  <si>
-    <t>Head/松鼠</t>
-  </si>
-  <si>
-    <t>Head/野兔</t>
-  </si>
-  <si>
-    <t>Head/火烈鸟</t>
-  </si>
-  <si>
-    <t>Head/鹿</t>
-  </si>
-  <si>
-    <t>Head/刺猬</t>
-  </si>
-  <si>
-    <t>Head/大象</t>
-  </si>
-  <si>
-    <t>Head/企鹅</t>
-  </si>
-  <si>
-    <t>Head/袋鼠</t>
-  </si>
-  <si>
-    <t>Head/Rabbit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/亚度尼斯</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/修女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/公主</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/国王</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/坎蒂丝</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/天使</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女仆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布拉德利</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布蓝达</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/希贝儿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/帕特里克</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/朵儿洁</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/梅林</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/渔夫</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/船长</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/水手</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/游侠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/爱格伯特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/牧师</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王后</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/管家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/艾琳娜</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/莱特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/金发女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/阿尔杰农</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/贵族骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老英雄</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老公公</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武道女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/格斗家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/战斗学者</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/异国女子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小花</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小美</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小混混</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/官员</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女诗人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/商人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/双辫女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/匪徒</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/制服小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔女郎</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸭</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/白兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/松鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/野兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/火烈鸟</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/刺猬</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/大象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/企鹅</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/袋鼠</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/格吉尔</t>
-  </si>
-  <si>
-    <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/马</t>
-  </si>
-  <si>
-    <t>Icon/玛德琳</t>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-  </si>
-  <si>
-    <t>Icon/丝特芬妮</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/公主</t>
-  </si>
-  <si>
-    <t>Icon/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Icon/国王</t>
-  </si>
-  <si>
-    <t>Icon/天使</t>
-  </si>
-  <si>
-    <t>Icon/朵儿洁</t>
-  </si>
-  <si>
-    <t>Icon/渔夫</t>
-  </si>
-  <si>
-    <t>Icon/船长</t>
-  </si>
-  <si>
-    <t>Icon/水手</t>
-  </si>
-  <si>
-    <t>Icon/游侠</t>
-  </si>
-  <si>
-    <t>Icon/牧师</t>
-  </si>
-  <si>
-    <t>Icon/王子</t>
-  </si>
-  <si>
-    <t>Icon/王后</t>
-  </si>
-  <si>
-    <t>Icon/管家</t>
-  </si>
-  <si>
-    <t>Icon/SmallChicken</t>
-  </si>
-  <si>
-    <t>Icon/Chicken</t>
-  </si>
-  <si>
-    <t>Icon/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/Rabbit</t>
-  </si>
-  <si>
-    <t>Icon/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/猪</t>
-  </si>
-  <si>
-    <t>Icon/奶牛</t>
-  </si>
-  <si>
-    <t>Icon/松鼠</t>
-  </si>
-  <si>
-    <t>Icon/野兔</t>
-  </si>
-  <si>
-    <t>Icon/火烈鸟</t>
-  </si>
-  <si>
-    <t>Icon/鹿</t>
-  </si>
-  <si>
-    <t>Icon/刺猬</t>
-  </si>
-  <si>
-    <t>Icon/大象</t>
-  </si>
-  <si>
-    <t>Icon/企鹅</t>
-  </si>
-  <si>
-    <t>Icon/袋鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鬼族男</t>
-  </si>
-  <si>
-    <t>女魔族</t>
-  </si>
-  <si>
-    <t>小精灵红</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/侦探</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/鬼族男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女魔族</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小精灵红</t>
-  </si>
-  <si>
-    <t>中年路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中年路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红发小孩</t>
-  </si>
-  <si>
-    <t>路人女</t>
-  </si>
-  <si>
-    <t>黄衣服小女孩</t>
-  </si>
-  <si>
-    <t>路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者</t>
-  </si>
-  <si>
-    <t>服务员</t>
-  </si>
-  <si>
-    <t>船员</t>
-  </si>
-  <si>
-    <t>贵族商人</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通士兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/轻战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/金发女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/牧师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女仆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有鞍马</t>
-  </si>
-  <si>
-    <t>Icon/有鞍马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/有鞍马</t>
+    <t>Icon/幼猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/幼牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/幼马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/幼象</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1634,7 +1665,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1669,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>14</v>
@@ -1704,7 +1735,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
@@ -1739,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -1765,7 +1796,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1774,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1809,7 +1840,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -1844,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>24</v>
@@ -1879,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>25</v>
@@ -1914,13 +1945,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1940,7 +1971,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1949,13 +1980,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1975,7 +2006,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
@@ -1984,13 +2015,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2010,7 +2041,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B14" s="1">
         <v>11</v>
@@ -2019,13 +2050,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2045,7 +2076,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2054,13 +2085,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2080,7 +2111,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B16" s="1">
         <v>13</v>
@@ -2089,13 +2120,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2115,7 +2146,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -2124,13 +2155,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2150,7 +2181,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
@@ -2159,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2185,7 +2216,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B19" s="1">
         <v>14</v>
@@ -2194,13 +2225,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2220,7 +2251,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2229,13 +2260,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2255,7 +2286,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2264,13 +2295,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2290,7 +2321,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2299,13 +2330,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2325,7 +2356,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2334,13 +2365,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2360,7 +2391,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2369,13 +2400,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2395,7 +2426,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2404,13 +2435,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2430,7 +2461,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2439,13 +2470,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2465,7 +2496,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2474,13 +2505,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2500,7 +2531,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2509,13 +2540,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2535,7 +2566,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2544,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2570,7 +2601,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2579,13 +2610,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2605,7 +2636,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -2614,13 +2645,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2640,7 +2671,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2649,13 +2680,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2675,7 +2706,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2684,13 +2715,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2710,7 +2741,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -2719,13 +2750,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2745,7 +2776,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -2754,13 +2785,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -2780,7 +2811,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -2789,13 +2820,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -2815,7 +2846,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -2824,13 +2855,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -2850,7 +2881,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -2859,13 +2890,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -2885,7 +2916,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -2894,13 +2925,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -2920,7 +2951,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -2929,13 +2960,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -2955,7 +2986,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -2964,13 +2995,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -2990,7 +3021,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -2999,13 +3030,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3025,7 +3056,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3034,13 +3065,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3060,7 +3091,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3069,7 +3100,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3089,7 +3120,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3098,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3118,7 +3149,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3127,7 +3158,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3147,7 +3178,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3156,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3176,7 +3207,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3185,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3205,7 +3236,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3214,7 +3245,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3234,7 +3265,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3243,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3263,7 +3294,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3272,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3292,7 +3323,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3301,7 +3332,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3321,7 +3352,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3330,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3350,7 +3381,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -3359,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3379,7 +3410,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -3388,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -3408,7 +3439,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -3417,7 +3448,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3437,7 +3468,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -3446,7 +3477,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3466,7 +3497,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -3475,7 +3506,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -3495,7 +3526,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -3504,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -3524,7 +3555,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -3533,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3553,7 +3584,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -3562,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -3582,7 +3613,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -3591,7 +3622,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -3611,7 +3642,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -3620,7 +3651,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -3640,7 +3671,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -3649,7 +3680,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -3669,7 +3700,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -3678,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -3698,7 +3729,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -3707,7 +3738,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -3727,7 +3758,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -3736,7 +3767,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -3756,7 +3787,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -3765,7 +3796,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -3785,7 +3816,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B69" s="1">
         <v>66</v>
@@ -3794,7 +3825,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -3814,7 +3845,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B70" s="1">
         <v>67</v>
@@ -3823,7 +3854,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -3843,7 +3874,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B71" s="1">
         <v>68</v>
@@ -3852,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -3872,7 +3903,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B72" s="1">
         <v>69</v>
@@ -3881,7 +3912,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -3901,7 +3932,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B73" s="1">
         <v>70</v>
@@ -3910,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -3930,7 +3961,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B74" s="1">
         <v>71</v>
@@ -3939,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -3959,7 +3990,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B75" s="1">
         <v>72</v>
@@ -3968,7 +3999,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -3988,7 +4019,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B76" s="1">
         <v>73</v>
@@ -3997,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4017,7 +4048,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4026,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4046,7 +4077,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -4055,7 +4086,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4075,7 +4106,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -4084,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4104,7 +4135,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -4134,7 +4165,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -4164,7 +4195,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -4194,7 +4225,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -4203,10 +4234,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="F83" s="1" t="str">
         <f>"Prefabs/Character/"&amp;A83</f>
@@ -4230,7 +4261,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -4260,7 +4291,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -4290,7 +4321,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -4320,7 +4351,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -4350,7 +4381,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -4380,7 +4411,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -4410,7 +4441,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -4449,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -4469,7 +4500,7 @@
     </row>
     <row r="92" spans="1:11" ht="27" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>37</v>
+        <v>327</v>
       </c>
       <c r="B92" s="1">
         <v>3000</v>
@@ -4478,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>255</v>
+        <v>328</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -4504,7 +4535,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>98</v>
+        <v>329</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -4513,13 +4544,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -4539,7 +4570,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>331</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -4548,13 +4579,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="G94" s="1">
         <v>1</v>
@@ -4574,7 +4605,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B95" s="3">
         <v>3003</v>
@@ -4583,13 +4614,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G95" s="1">
         <v>1</v>
@@ -4609,7 +4640,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>50</v>
+        <v>333</v>
       </c>
       <c r="B96" s="3">
         <v>3004</v>
@@ -4618,13 +4649,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>258</v>
+        <v>334</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="G96" s="1">
         <v>1</v>
@@ -4644,7 +4675,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>114</v>
+        <v>335</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -4653,13 +4684,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -4679,7 +4710,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>116</v>
+        <v>337</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -4688,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>259</v>
+        <v>338</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G98" s="1">
         <v>1</v>
@@ -4714,7 +4745,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B99" s="3">
         <v>3007</v>
@@ -4723,13 +4754,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="G99" s="1">
         <v>1</v>
@@ -4749,7 +4780,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>117</v>
+        <v>339</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -4758,13 +4789,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -4793,13 +4824,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="G101" s="1">
         <v>1</v>
@@ -4819,7 +4850,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>38</v>
+        <v>341</v>
       </c>
       <c r="B102" s="3">
         <v>3010</v>
@@ -4828,13 +4859,13 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -4863,13 +4894,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -4889,7 +4920,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B104" s="3">
         <v>3012</v>
@@ -4898,13 +4929,13 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -4924,7 +4955,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B105" s="3">
         <v>3013</v>
@@ -4933,13 +4964,13 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>235</v>
+        <v>343</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -4959,7 +4990,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B106" s="3">
         <v>3100</v>
@@ -4968,13 +4999,13 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -4994,7 +5025,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B107" s="3">
         <v>3102</v>
@@ -5003,13 +5034,13 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -5029,7 +5060,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B108" s="3">
         <v>3104</v>
@@ -5038,13 +5069,13 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
@@ -5064,7 +5095,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B109" s="3">
         <v>3106</v>
@@ -5073,13 +5104,13 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
@@ -5099,7 +5130,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B110" s="3">
         <v>3107</v>
@@ -5108,13 +5139,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G110" s="1">
         <v>1</v>
@@ -5134,7 +5165,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B111" s="3">
         <v>3108</v>
@@ -5143,13 +5174,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G111" s="1">
         <v>1</v>
@@ -5169,7 +5200,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>46</v>
+        <v>344</v>
       </c>
       <c r="B112" s="3">
         <v>3110</v>
@@ -5178,13 +5209,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G112" s="1">
         <v>1</v>
@@ -5204,7 +5235,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B113" s="3">
         <v>3111</v>
@@ -5213,13 +5244,13 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="G113" s="1">
         <v>1</v>
@@ -5239,7 +5270,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B114" s="3">
         <v>3112</v>
@@ -5248,13 +5279,13 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G114" s="1">
         <v>1</v>
@@ -5274,7 +5305,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B115" s="1">
         <v>3114</v>
@@ -5283,13 +5314,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="G115" s="1">
         <v>1</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -4518,7 +4518,7 @@
         <v>197</v>
       </c>
       <c r="G92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>198</v>
       </c>
       <c r="G93" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>199</v>
       </c>
       <c r="G94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>200</v>
       </c>
       <c r="G95" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -4658,7 +4658,7 @@
         <v>201</v>
       </c>
       <c r="G96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -4693,7 +4693,7 @@
         <v>202</v>
       </c>
       <c r="G97" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>203</v>
       </c>
       <c r="G98" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>204</v>
       </c>
       <c r="G99" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -4798,7 +4798,7 @@
         <v>205</v>
       </c>
       <c r="G100" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -4833,7 +4833,7 @@
         <v>206</v>
       </c>
       <c r="G101" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>207</v>
       </c>
       <c r="G102" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>208</v>
       </c>
       <c r="G103" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>209</v>
       </c>
       <c r="G104" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>210</v>
       </c>
       <c r="G105" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -5008,7 +5008,7 @@
         <v>211</v>
       </c>
       <c r="G106" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         <v>212</v>
       </c>
       <c r="G107" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>213</v>
       </c>
       <c r="G108" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -5113,7 +5113,7 @@
         <v>214</v>
       </c>
       <c r="G109" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         <v>215</v>
       </c>
       <c r="G110" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>216</v>
       </c>
       <c r="G111" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>217</v>
       </c>
       <c r="G112" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -5253,7 +5253,7 @@
         <v>218</v>
       </c>
       <c r="G113" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -5288,7 +5288,7 @@
         <v>219</v>
       </c>
       <c r="G114" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -5323,7 +5323,7 @@
         <v>220</v>
       </c>
       <c r="G115" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="347">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -770,10 +770,6 @@
   </si>
   <si>
     <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/主角女</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1215,6 +1211,14 @@
   </si>
   <si>
     <t>Icon/幼象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/主角女</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1735,13 +1739,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>224</v>
+        <v>345</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>346</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1770,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -1796,7 +1800,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1805,13 +1809,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1840,7 +1844,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -1875,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>24</v>
@@ -1910,7 +1914,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>25</v>
@@ -1971,7 +1975,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1980,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>93</v>
@@ -2015,10 +2019,10 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>138</v>
@@ -2050,7 +2054,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>109</v>
@@ -2085,7 +2089,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>110</v>
@@ -2120,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>111</v>
@@ -2146,7 +2150,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -2155,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>94</v>
@@ -2190,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>112</v>
@@ -2216,7 +2220,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B19" s="1">
         <v>14</v>
@@ -2225,13 +2229,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2251,7 +2255,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2260,7 +2264,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>113</v>
@@ -2286,7 +2290,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2295,7 +2299,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>114</v>
@@ -2321,7 +2325,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2330,7 +2334,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>95</v>
@@ -2356,7 +2360,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2365,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>96</v>
@@ -2391,7 +2395,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2400,7 +2404,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>98</v>
@@ -2435,7 +2439,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>99</v>
@@ -2461,7 +2465,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2470,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>100</v>
@@ -2505,10 +2509,10 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>151</v>
@@ -2531,7 +2535,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2540,7 +2544,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>101</v>
@@ -2575,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>115</v>
@@ -2610,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>116</v>
@@ -2645,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>117</v>
@@ -2671,7 +2675,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2680,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>118</v>
@@ -2706,7 +2710,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2715,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>102</v>
@@ -2750,10 +2754,10 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>158</v>
@@ -2785,7 +2789,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>119</v>
@@ -2820,7 +2824,7 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>120</v>
@@ -2846,7 +2850,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -2855,13 +2859,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -2890,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>121</v>
@@ -2916,7 +2920,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -2925,7 +2929,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>104</v>
@@ -2951,7 +2955,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -2960,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>105</v>
@@ -2986,7 +2990,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -2995,10 +2999,10 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>164</v>
@@ -3021,7 +3025,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3030,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>106</v>
@@ -3056,7 +3060,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3065,13 +3069,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>107</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3178,7 +3182,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3187,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -4028,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4048,7 +4052,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4057,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4077,7 +4081,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -4086,7 +4090,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4106,7 +4110,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -4115,7 +4119,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4135,7 +4139,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -4165,7 +4169,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -4195,7 +4199,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -4225,7 +4229,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -4234,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="F83" s="1" t="str">
         <f>"Prefabs/Character/"&amp;A83</f>
@@ -4261,7 +4265,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -4291,7 +4295,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -4321,7 +4325,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -4351,7 +4355,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -4381,7 +4385,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -4411,7 +4415,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -4441,7 +4445,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -4500,7 +4504,7 @@
     </row>
     <row r="92" spans="1:11" ht="27" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B92" s="1">
         <v>3000</v>
@@ -4509,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>27</v>
@@ -4535,7 +4539,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -4544,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>28</v>
@@ -4570,7 +4574,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -4579,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>122</v>
@@ -4614,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>122</v>
@@ -4640,7 +4644,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B96" s="3">
         <v>3004</v>
@@ -4649,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>135</v>
@@ -4675,7 +4679,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -4684,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>135</v>
@@ -4710,7 +4714,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -4719,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>123</v>
@@ -4754,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>123</v>
@@ -4780,7 +4784,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -4789,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>124</v>
@@ -4824,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>124</v>
@@ -4850,7 +4854,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B102" s="3">
         <v>3010</v>
@@ -4859,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>125</v>
@@ -4894,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>125</v>
@@ -4929,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>126</v>
@@ -4964,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>126</v>
@@ -4999,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>127</v>
@@ -5034,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>128</v>
@@ -5069,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>129</v>
@@ -5104,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>130</v>
@@ -5139,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>130</v>
@@ -5174,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>131</v>
@@ -5200,7 +5204,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B112" s="3">
         <v>3110</v>
@@ -5209,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>132</v>
@@ -5244,7 +5248,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>132</v>
@@ -5279,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>133</v>
@@ -5314,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>134</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -1123,9 +1123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>有鞍马</t>
-  </si>
-  <si>
     <t>Icon/有鞍马</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1219,6 +1216,10 @@
   </si>
   <si>
     <t>Prefabs/Character/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1739,13 +1740,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1800,7 +1801,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1809,13 +1810,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -4504,7 +4505,7 @@
     </row>
     <row r="92" spans="1:11" ht="27" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B92" s="1">
         <v>3000</v>
@@ -4513,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>27</v>
@@ -4539,7 +4540,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -4548,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>28</v>
@@ -4574,7 +4575,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -4583,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>122</v>
@@ -4644,7 +4645,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B96" s="3">
         <v>3004</v>
@@ -4653,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>135</v>
@@ -4679,7 +4680,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -4688,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>135</v>
@@ -4714,7 +4715,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -4723,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>123</v>
@@ -4784,7 +4785,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -4793,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>124</v>
@@ -4854,7 +4855,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B102" s="3">
         <v>3010</v>
@@ -4863,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>125</v>
@@ -4968,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>126</v>
@@ -5204,7 +5205,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B112" s="3">
         <v>3110</v>
@@ -5213,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>132</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="325">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -125,14 +125,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Head/SmallChicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Chicken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>布莱兹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -157,1029 +149,1017 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔女郎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莎拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制服小孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>女诗人</t>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>武道女</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杰克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/woman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/公主</t>
+  </si>
+  <si>
+    <t>Head/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Head/国王</t>
+  </si>
+  <si>
+    <t>Head/天使</t>
+  </si>
+  <si>
+    <t>Head/女仆</t>
+  </si>
+  <si>
+    <t>Head/女骑士</t>
+  </si>
+  <si>
+    <t>Head/渔夫</t>
+  </si>
+  <si>
+    <t>Head/船长</t>
+  </si>
+  <si>
+    <t>Head/水手</t>
+  </si>
+  <si>
+    <t>Head/游侠</t>
+  </si>
+  <si>
+    <t>Head/王子</t>
+  </si>
+  <si>
+    <t>Head/王后</t>
+  </si>
+  <si>
+    <t>Head/管家</t>
+  </si>
+  <si>
+    <t>Head/鸭子</t>
+  </si>
+  <si>
+    <t>Head/绵羊</t>
+  </si>
+  <si>
+    <t>Head/猪</t>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+  </si>
+  <si>
+    <t>Head/马</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/亚度尼斯</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/修女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/公主</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/国王</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/坎蒂丝</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/天使</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女仆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布拉德利</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布蓝达</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/希贝儿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/帕特里克</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/朵儿洁</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/梅林</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/渔夫</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/船长</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/水手</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/游侠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/爱格伯特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/牧师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王后</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鬼族男</t>
+  </si>
+  <si>
+    <t>女魔族</t>
+  </si>
+  <si>
+    <t>小精灵红</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/侦探</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/鬼族男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女魔族</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小精灵红</t>
+  </si>
+  <si>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红发小孩</t>
+  </si>
+  <si>
+    <t>路人女</t>
+  </si>
+  <si>
+    <t>黄衣服小女孩</t>
+  </si>
+  <si>
+    <t>路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者</t>
+  </si>
+  <si>
+    <t>服务员</t>
+  </si>
+  <si>
+    <t>船员</t>
+  </si>
+  <si>
+    <t>贵族商人</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通士兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/轻战士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/金发女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/牧师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/女仆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼兔子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡</t>
+  </si>
+  <si>
+    <t>Icon/火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>猪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>奶牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>松鼠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野兔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火烈鸟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼鹿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刺猬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>企鹅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>袋鼠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侦探</t>
-  </si>
-  <si>
-    <t>琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兔女郎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莎拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>制服小孩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>勇者女</t>
-  </si>
-  <si>
-    <t>勇者男</t>
-  </si>
-  <si>
-    <t>匪徒</t>
-  </si>
-  <si>
-    <t>双辫女孩</t>
-  </si>
-  <si>
-    <t>商人</t>
-  </si>
-  <si>
-    <t>罗伊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天使</t>
-  </si>
-  <si>
-    <t>女战士</t>
-  </si>
-  <si>
-    <t>女诗人</t>
-  </si>
-  <si>
-    <t>女轻战士</t>
-  </si>
-  <si>
-    <t>官员</t>
-  </si>
-  <si>
-    <t>小女孩</t>
-  </si>
-  <si>
-    <t>小女孩2</t>
-  </si>
-  <si>
-    <t>小孩</t>
-  </si>
-  <si>
-    <t>小混混</t>
-  </si>
-  <si>
-    <t>小男孩</t>
-  </si>
-  <si>
-    <t>小男孩2</t>
-  </si>
-  <si>
-    <t>小美</t>
-  </si>
-  <si>
-    <t>小花</t>
-  </si>
-  <si>
-    <t>异国女子</t>
-  </si>
-  <si>
-    <t>战斗学者</t>
-  </si>
-  <si>
-    <t>格斗家</t>
-  </si>
-  <si>
-    <t>武士</t>
-  </si>
-  <si>
-    <t>武道女</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游侠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杰克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老公公</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老英雄</t>
-  </si>
-  <si>
-    <t>贵族骑士</t>
-  </si>
-  <si>
-    <t>重装女战士</t>
-  </si>
-  <si>
-    <t>重装战士</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>iconName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldMan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/woman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/man</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/man1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸭子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/公主</t>
-  </si>
-  <si>
-    <t>Head/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Head/国王</t>
-  </si>
-  <si>
-    <t>Head/天使</t>
-  </si>
-  <si>
-    <t>Head/女仆</t>
-  </si>
-  <si>
-    <t>Head/女骑士</t>
-  </si>
-  <si>
-    <t>Head/渔夫</t>
-  </si>
-  <si>
-    <t>Head/船长</t>
-  </si>
-  <si>
-    <t>Head/水手</t>
-  </si>
-  <si>
-    <t>Head/游侠</t>
-  </si>
-  <si>
-    <t>Head/王子</t>
-  </si>
-  <si>
-    <t>Head/王后</t>
-  </si>
-  <si>
-    <t>Head/管家</t>
-  </si>
-  <si>
-    <t>Head/鸭子</t>
-  </si>
-  <si>
-    <t>Head/绵羊</t>
-  </si>
-  <si>
-    <t>Head/猪</t>
-  </si>
-  <si>
-    <t>Head/奶牛</t>
-  </si>
-  <si>
-    <t>Head/马</t>
-  </si>
-  <si>
-    <t>Head/松鼠</t>
-  </si>
-  <si>
-    <t>Head/野兔</t>
-  </si>
-  <si>
-    <t>Head/火烈鸟</t>
-  </si>
-  <si>
-    <t>Head/鹿</t>
-  </si>
-  <si>
-    <t>Head/刺猬</t>
-  </si>
-  <si>
-    <t>Head/大象</t>
-  </si>
-  <si>
-    <t>Head/企鹅</t>
-  </si>
-  <si>
-    <t>Head/袋鼠</t>
-  </si>
-  <si>
-    <t>Head/Rabbit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/亚度尼斯</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/修女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/公主</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/国王</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/坎蒂丝</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/天使</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女仆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布拉德利</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布蓝达</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/希贝儿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/帕特里克</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/朵儿洁</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/梅林</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/渔夫</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/船长</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/水手</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/游侠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/爱格伯特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/牧师</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王后</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/管家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/艾琳娜</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/莱特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/金发女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/阿尔杰农</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/贵族骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老英雄</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老公公</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武道女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/格斗家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/战斗学者</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/异国女子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小花</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小美</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小混混</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/官员</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女诗人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/商人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/双辫女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/匪徒</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/制服小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔女郎</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸡</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鸭</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/白兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小马</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/松鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/野兔</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/火烈鸟</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鹿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/刺猬</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/大象</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/企鹅</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/袋鼠</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/格吉尔</t>
-  </si>
-  <si>
-    <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/马</t>
-  </si>
-  <si>
-    <t>Icon/玛德琳</t>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-  </si>
-  <si>
-    <t>Icon/丝特芬妮</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/公主</t>
-  </si>
-  <si>
-    <t>Icon/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Icon/国王</t>
-  </si>
-  <si>
-    <t>Icon/天使</t>
-  </si>
-  <si>
-    <t>Icon/朵儿洁</t>
-  </si>
-  <si>
-    <t>Icon/渔夫</t>
-  </si>
-  <si>
-    <t>Icon/船长</t>
-  </si>
-  <si>
-    <t>Icon/水手</t>
-  </si>
-  <si>
-    <t>Icon/游侠</t>
-  </si>
-  <si>
-    <t>Icon/牧师</t>
-  </si>
-  <si>
-    <t>Icon/王子</t>
-  </si>
-  <si>
-    <t>Icon/王后</t>
-  </si>
-  <si>
-    <t>Icon/管家</t>
-  </si>
-  <si>
-    <t>Icon/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/猪</t>
-  </si>
-  <si>
-    <t>Icon/奶牛</t>
-  </si>
-  <si>
-    <t>Icon/松鼠</t>
-  </si>
-  <si>
-    <t>Icon/野兔</t>
-  </si>
-  <si>
-    <t>Icon/火烈鸟</t>
-  </si>
-  <si>
-    <t>Icon/鹿</t>
-  </si>
-  <si>
-    <t>Icon/刺猬</t>
-  </si>
-  <si>
-    <t>Icon/大象</t>
-  </si>
-  <si>
-    <t>Icon/企鹅</t>
-  </si>
-  <si>
-    <t>Icon/袋鼠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鬼族男</t>
-  </si>
-  <si>
-    <t>女魔族</t>
-  </si>
-  <si>
-    <t>小精灵红</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/侦探</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/鬼族男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女魔族</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小精灵红</t>
-  </si>
-  <si>
-    <t>中年路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中年路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红发小孩</t>
-  </si>
-  <si>
-    <t>路人女</t>
-  </si>
-  <si>
-    <t>黄衣服小女孩</t>
-  </si>
-  <si>
-    <t>路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者</t>
-  </si>
-  <si>
-    <t>服务员</t>
-  </si>
-  <si>
-    <t>船员</t>
-  </si>
-  <si>
-    <t>贵族商人</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通士兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/轻战士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/金发女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/牧师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/女仆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/有鞍马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/有鞍马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/幼鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼鸭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/幼鸭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼兔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/幼兔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>家兔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/家兔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/幼绵羊</t>
+    <t>羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>母鸡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1187,39 +1167,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Icon/幼猪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/幼牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/幼马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/幼象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马</t>
+    <t>山羊</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1287,7 +1235,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1304,6 +1252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1609,7 +1558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:K115"/>
+  <dimension ref="A2:K111"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -1670,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1705,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>14</v>
@@ -1731,7 +1680,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1740,13 +1689,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1766,7 +1715,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1775,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -1801,7 +1750,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>346</v>
+        <v>270</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1810,13 +1759,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>324</v>
+        <v>272</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1836,7 +1785,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -1845,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -1871,7 +1820,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1880,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>24</v>
@@ -1906,7 +1855,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -1915,7 +1864,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>25</v>
@@ -1941,7 +1890,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1950,13 +1899,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1976,7 +1925,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1985,13 +1934,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2011,7 +1960,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
@@ -2020,13 +1969,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2046,7 +1995,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1">
         <v>11</v>
@@ -2055,13 +2004,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2081,7 +2030,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2090,13 +2039,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2116,7 +2065,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1">
         <v>13</v>
@@ -2125,13 +2074,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2151,7 +2100,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>308</v>
+        <v>253</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -2160,13 +2109,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2186,7 +2135,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
@@ -2195,13 +2144,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2221,7 +2170,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>307</v>
+        <v>252</v>
       </c>
       <c r="B19" s="1">
         <v>14</v>
@@ -2230,13 +2179,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>282</v>
+        <v>227</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>321</v>
+        <v>266</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>320</v>
+        <v>265</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2256,7 +2205,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2265,13 +2214,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>316</v>
+        <v>261</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2291,7 +2240,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>280</v>
+        <v>225</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2300,13 +2249,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2326,7 +2275,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>278</v>
+        <v>223</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2335,13 +2284,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2361,7 +2310,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>276</v>
+        <v>221</v>
       </c>
       <c r="B23" s="1">
         <v>20</v>
@@ -2370,13 +2319,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>277</v>
+        <v>222</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -2396,7 +2345,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2405,13 +2354,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>275</v>
+        <v>220</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2431,7 +2380,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2440,13 +2389,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2466,7 +2415,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2475,13 +2424,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2501,7 +2450,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2510,13 +2459,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2536,7 +2485,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2545,13 +2494,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2571,7 +2520,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2580,13 +2529,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2606,7 +2555,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2615,13 +2564,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2641,7 +2590,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -2650,13 +2599,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2676,7 +2625,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>301</v>
+        <v>246</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2685,13 +2634,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2711,7 +2660,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2720,13 +2669,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2746,7 +2695,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -2755,13 +2704,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2781,7 +2730,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -2790,13 +2739,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -2816,7 +2765,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -2825,13 +2774,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -2851,7 +2800,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
-        <v>267</v>
+        <v>212</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -2860,13 +2809,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>268</v>
+        <v>213</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>304</v>
+        <v>249</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -2886,7 +2835,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -2895,13 +2844,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>244</v>
+        <v>197</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -2921,7 +2870,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
-        <v>265</v>
+        <v>210</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -2930,13 +2879,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>266</v>
+        <v>211</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -2956,7 +2905,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -2965,13 +2914,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>264</v>
+        <v>209</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -2991,7 +2940,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -3000,13 +2949,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -3026,7 +2975,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -3035,13 +2984,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3061,7 +3010,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3070,13 +3019,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>258</v>
+        <v>203</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>257</v>
+        <v>202</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3096,7 +3045,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3105,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3125,7 +3074,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3134,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3154,7 +3103,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3163,7 +3112,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3183,7 +3132,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3192,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3212,7 +3161,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3221,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3241,7 +3190,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3250,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3270,7 +3219,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3279,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3299,7 +3248,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3308,7 +3257,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3328,7 +3277,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3337,7 +3286,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3357,7 +3306,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3366,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3386,7 +3335,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -3395,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3415,7 +3364,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -3424,7 +3373,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -3444,7 +3393,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -3453,7 +3402,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3473,7 +3422,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -3482,7 +3431,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3502,7 +3451,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -3511,7 +3460,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -3531,7 +3480,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -3540,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -3560,7 +3509,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -3569,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3589,7 +3538,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -3598,7 +3547,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -3618,7 +3567,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -3627,7 +3576,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -3647,7 +3596,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -3656,7 +3605,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -3676,7 +3625,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -3685,7 +3634,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -3705,7 +3654,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -3714,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -3734,7 +3683,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -3743,7 +3692,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -3763,7 +3712,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -3772,7 +3721,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -3792,7 +3741,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -3801,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -3821,7 +3770,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B69" s="1">
         <v>66</v>
@@ -3830,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -3850,7 +3799,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B70" s="1">
         <v>67</v>
@@ -3859,7 +3808,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -3879,7 +3828,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B71" s="1">
         <v>68</v>
@@ -3888,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -3908,7 +3857,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B72" s="1">
         <v>69</v>
@@ -3917,7 +3866,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -3937,7 +3886,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B73" s="1">
         <v>70</v>
@@ -3946,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -3966,7 +3915,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B74" s="1">
         <v>71</v>
@@ -3975,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -3995,7 +3944,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B75" s="1">
         <v>72</v>
@@ -4004,7 +3953,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -4024,7 +3973,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B76" s="1">
         <v>73</v>
@@ -4033,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>287</v>
+        <v>232</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4053,7 +4002,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4062,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4082,7 +4031,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -4091,7 +4040,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4111,7 +4060,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>286</v>
+        <v>231</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -4120,7 +4069,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>290</v>
+        <v>235</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4140,7 +4089,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -4170,7 +4119,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>292</v>
+        <v>237</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -4200,7 +4149,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>293</v>
+        <v>238</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -4230,7 +4179,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -4239,10 +4188,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>318</v>
+        <v>263</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>319</v>
+        <v>264</v>
       </c>
       <c r="F83" s="1" t="str">
         <f>"Prefabs/Character/"&amp;A83</f>
@@ -4266,7 +4215,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>294</v>
+        <v>239</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -4296,7 +4245,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -4326,7 +4275,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -4356,7 +4305,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -4386,7 +4335,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>298</v>
+        <v>243</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -4416,7 +4365,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -4446,7 +4395,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -4485,7 +4434,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -4503,9 +4452,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="27" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B92" s="1">
         <v>3000</v>
@@ -4514,13 +4463,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>27</v>
+        <v>274</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>197</v>
+        <v>276</v>
       </c>
       <c r="G92" s="1">
         <v>2</v>
@@ -4540,7 +4489,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -4549,13 +4498,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>28</v>
+        <v>274</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>198</v>
+        <v>275</v>
       </c>
       <c r="G93" s="1">
         <v>3</v>
@@ -4575,7 +4524,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -4584,13 +4533,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>122</v>
+        <v>278</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>199</v>
+        <v>279</v>
       </c>
       <c r="G94" s="1">
         <v>2</v>
@@ -4610,7 +4559,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="B95" s="3">
         <v>3003</v>
@@ -4619,13 +4568,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="G95" s="1">
         <v>3</v>
@@ -4645,7 +4594,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>331</v>
+        <v>281</v>
       </c>
       <c r="B96" s="3">
         <v>3004</v>
@@ -4654,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="G96" s="1">
         <v>2</v>
@@ -4680,7 +4629,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -4689,13 +4638,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>135</v>
+        <v>282</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>202</v>
+        <v>285</v>
       </c>
       <c r="G97" s="1">
         <v>3</v>
@@ -4715,7 +4664,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -4724,13 +4673,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>336</v>
+        <v>199</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="G98" s="1">
         <v>3</v>
@@ -4750,7 +4699,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B99" s="3">
         <v>3007</v>
@@ -4759,13 +4708,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="G99" s="1">
         <v>4</v>
@@ -4785,7 +4734,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -4794,13 +4743,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>338</v>
+        <v>200</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>205</v>
+        <v>288</v>
       </c>
       <c r="G100" s="1">
         <v>3</v>
@@ -4820,7 +4769,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="B101" s="3">
         <v>3009</v>
@@ -4829,13 +4778,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="G101" s="1">
         <v>4</v>
@@ -4855,7 +4804,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="B102" s="3">
         <v>3010</v>
@@ -4864,13 +4813,13 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>340</v>
+        <v>201</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>125</v>
+        <v>291</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="G102" s="1">
         <v>3</v>
@@ -4890,7 +4839,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>36</v>
+        <v>289</v>
       </c>
       <c r="B103" s="3">
         <v>3011</v>
@@ -4899,13 +4848,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="G103" s="1">
         <v>4</v>
@@ -4925,7 +4874,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>37</v>
+        <v>293</v>
       </c>
       <c r="B104" s="3">
         <v>3012</v>
@@ -4934,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="G104" s="1">
         <v>4</v>
@@ -4960,7 +4909,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>47</v>
+        <v>297</v>
       </c>
       <c r="B105" s="3">
         <v>3013</v>
@@ -4969,13 +4918,13 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="G105" s="1">
         <v>3</v>
@@ -4995,25 +4944,25 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B106" s="3">
-        <v>3100</v>
+        <v>306</v>
+      </c>
+      <c r="B106" s="6">
+        <v>3104</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>249</v>
+        <v>300</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>127</v>
+        <v>298</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="G106" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -5030,25 +4979,25 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B107" s="3">
-        <v>3102</v>
+        <v>324</v>
+      </c>
+      <c r="B107" s="6">
+        <v>3105</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>128</v>
+        <v>298</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="G107" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -5065,22 +5014,22 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B108" s="3">
-        <v>3104</v>
+        <v>307</v>
+      </c>
+      <c r="B108" s="6">
+        <v>3106</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>129</v>
+        <v>304</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>213</v>
+        <v>308</v>
       </c>
       <c r="G108" s="1">
         <v>3</v>
@@ -5100,22 +5049,22 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B109" s="3">
-        <v>3106</v>
+        <v>302</v>
+      </c>
+      <c r="B109" s="6">
+        <v>3107</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>252</v>
+        <v>303</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>130</v>
+        <v>304</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>214</v>
+        <v>305</v>
       </c>
       <c r="G109" s="1">
         <v>3</v>
@@ -5135,22 +5084,22 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B110" s="3">
-        <v>3107</v>
+        <v>312</v>
+      </c>
+      <c r="B110" s="6">
+        <v>3108</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>215</v>
+        <v>313</v>
       </c>
       <c r="G110" s="1">
         <v>4</v>
@@ -5170,25 +5119,25 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B111" s="3">
-        <v>3108</v>
+        <v>321</v>
+      </c>
+      <c r="B111" s="6">
+        <v>3109</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>131</v>
+        <v>310</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>216</v>
+        <v>311</v>
       </c>
       <c r="G111" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -5200,146 +5149,6 @@
         <v>2</v>
       </c>
       <c r="K111" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A112" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B112" s="3">
-        <v>3110</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G112" s="1">
-        <v>4</v>
-      </c>
-      <c r="H112" s="1">
-        <v>0</v>
-      </c>
-      <c r="I112" s="1">
-        <v>0</v>
-      </c>
-      <c r="J112" s="1">
-        <v>2</v>
-      </c>
-      <c r="K112" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A113" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B113" s="3">
-        <v>3111</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G113" s="1">
-        <v>5</v>
-      </c>
-      <c r="H113" s="1">
-        <v>0</v>
-      </c>
-      <c r="I113" s="1">
-        <v>0</v>
-      </c>
-      <c r="J113" s="1">
-        <v>2</v>
-      </c>
-      <c r="K113" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A114" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B114" s="3">
-        <v>3112</v>
-      </c>
-      <c r="C114" s="1">
-        <v>0</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G114" s="1">
-        <v>3</v>
-      </c>
-      <c r="H114" s="1">
-        <v>0</v>
-      </c>
-      <c r="I114" s="1">
-        <v>0</v>
-      </c>
-      <c r="J114" s="1">
-        <v>2</v>
-      </c>
-      <c r="K114" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A115" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B115" s="1">
-        <v>3114</v>
-      </c>
-      <c r="C115" s="1">
-        <v>0</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G115" s="1">
-        <v>4</v>
-      </c>
-      <c r="H115" s="1">
-        <v>0</v>
-      </c>
-      <c r="I115" s="1">
-        <v>0</v>
-      </c>
-      <c r="J115" s="1">
-        <v>2</v>
-      </c>
-      <c r="K115" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -1235,7 +1235,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1252,7 +1252,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4946,8 +4945,8 @@
       <c r="A106" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B106" s="6">
-        <v>3104</v>
+      <c r="B106" s="3">
+        <v>3014</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
@@ -4981,8 +4980,8 @@
       <c r="A107" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B107" s="6">
-        <v>3105</v>
+      <c r="B107" s="3">
+        <v>3015</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
@@ -5016,8 +5015,8 @@
       <c r="A108" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B108" s="6">
-        <v>3106</v>
+      <c r="B108" s="3">
+        <v>3016</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
@@ -5051,8 +5050,8 @@
       <c r="A109" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B109" s="6">
-        <v>3107</v>
+      <c r="B109" s="3">
+        <v>3017</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
@@ -5086,8 +5085,8 @@
       <c r="A110" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B110" s="6">
-        <v>3108</v>
+      <c r="B110" s="3">
+        <v>3018</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -5121,8 +5120,8 @@
       <c r="A111" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B111" s="6">
-        <v>3109</v>
+      <c r="B111" s="3">
+        <v>3019</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -125,655 +125,603 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侦探</t>
+  </si>
+  <si>
+    <t>兔女郎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莎拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制服小孩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勇者女</t>
+  </si>
+  <si>
+    <t>勇者男</t>
+  </si>
+  <si>
+    <t>匪徒</t>
+  </si>
+  <si>
+    <t>双辫女孩</t>
+  </si>
+  <si>
+    <t>商人</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>女战士</t>
+  </si>
+  <si>
+    <t>女诗人</t>
+  </si>
+  <si>
+    <t>女轻战士</t>
+  </si>
+  <si>
+    <t>官员</t>
+  </si>
+  <si>
+    <t>小女孩</t>
+  </si>
+  <si>
+    <t>小女孩2</t>
+  </si>
+  <si>
+    <t>小孩</t>
+  </si>
+  <si>
+    <t>小混混</t>
+  </si>
+  <si>
+    <t>小男孩</t>
+  </si>
+  <si>
+    <t>小男孩2</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>小花</t>
+  </si>
+  <si>
+    <t>异国女子</t>
+  </si>
+  <si>
+    <t>战斗学者</t>
+  </si>
+  <si>
+    <t>格斗家</t>
+  </si>
+  <si>
+    <t>武士</t>
+  </si>
+  <si>
+    <t>武道女</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杰克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老公公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老英雄</t>
+  </si>
+  <si>
+    <t>贵族骑士</t>
+  </si>
+  <si>
+    <t>重装女战士</t>
+  </si>
+  <si>
+    <t>重装战士</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/woman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/man1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/公主</t>
+  </si>
+  <si>
+    <t>Head/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Head/国王</t>
+  </si>
+  <si>
+    <t>Head/天使</t>
+  </si>
+  <si>
+    <t>Head/女仆</t>
+  </si>
+  <si>
+    <t>Head/女骑士</t>
+  </si>
+  <si>
+    <t>Head/渔夫</t>
+  </si>
+  <si>
+    <t>Head/船长</t>
+  </si>
+  <si>
+    <t>Head/水手</t>
+  </si>
+  <si>
+    <t>Head/游侠</t>
+  </si>
+  <si>
+    <t>Head/王子</t>
+  </si>
+  <si>
+    <t>Head/王后</t>
+  </si>
+  <si>
+    <t>Head/管家</t>
+  </si>
+  <si>
+    <t>Head/鸭子</t>
+  </si>
+  <si>
+    <t>Head/绵羊</t>
+  </si>
+  <si>
+    <t>Head/猪</t>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+  </si>
+  <si>
+    <t>Head/马</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/亚度尼斯</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/修女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/公主</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/国王</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/坎蒂丝</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/天使</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女仆</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布拉德利</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布莱兹</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/布蓝达</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/希贝儿</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/帕特里克</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/朵儿洁</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/梅林</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/渔夫</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/船长</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/水手</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/游侠</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/爱格伯特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/牧师</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/王后</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/管家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/艾琳娜</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/莱特</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/金发女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/阿尔杰农</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/重装女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/贵族骑士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老英雄</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/老公公</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武道女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/武士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/格斗家</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/战斗学者</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/异国女子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小花</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小美</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小男孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小混混</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩2</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/官员</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女轻战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女诗人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/女战士</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/商人</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/双辫女孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/匪徒</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者女</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/勇者男</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/制服小孩</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/兔女郎</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/小丑</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/鸭子</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/绵羊</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/猪</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/格吉尔</t>
+  </si>
+  <si>
+    <t>Icon/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/玛德琳</t>
+  </si>
+  <si>
+    <t>Icon/布莱兹</t>
+  </si>
+  <si>
+    <t>Icon/丝特芬妮</t>
+  </si>
+  <si>
+    <t>Icon/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/修女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/公主</t>
+  </si>
+  <si>
+    <t>Icon/占卜婆婆</t>
+  </si>
+  <si>
+    <t>Icon/国王</t>
+  </si>
+  <si>
+    <t>Icon/天使</t>
+  </si>
+  <si>
+    <t>Icon/朵儿洁</t>
+  </si>
+  <si>
+    <t>Icon/渔夫</t>
+  </si>
+  <si>
+    <t>Icon/船长</t>
+  </si>
+  <si>
+    <t>Icon/水手</t>
+  </si>
+  <si>
+    <t>Icon/游侠</t>
+  </si>
+  <si>
+    <t>Icon/牧师</t>
+  </si>
+  <si>
+    <t>Icon/王子</t>
+  </si>
+  <si>
+    <t>Icon/王后</t>
+  </si>
+  <si>
+    <t>Icon/管家</t>
+  </si>
+  <si>
+    <t>Icon/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/猪</t>
+  </si>
+  <si>
+    <t>Icon/奶牛</t>
+  </si>
+  <si>
+    <t>Prefabs/Character/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>布莱兹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侦探</t>
-  </si>
-  <si>
-    <t>琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兔女郎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莎拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>制服小孩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>勇者女</t>
-  </si>
-  <si>
-    <t>勇者男</t>
-  </si>
-  <si>
-    <t>匪徒</t>
-  </si>
-  <si>
-    <t>双辫女孩</t>
-  </si>
-  <si>
-    <t>商人</t>
-  </si>
-  <si>
-    <t>罗伊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天使</t>
-  </si>
-  <si>
-    <t>女战士</t>
-  </si>
-  <si>
-    <t>女诗人</t>
-  </si>
-  <si>
-    <t>女轻战士</t>
-  </si>
-  <si>
-    <t>官员</t>
-  </si>
-  <si>
-    <t>小女孩</t>
-  </si>
-  <si>
-    <t>小女孩2</t>
-  </si>
-  <si>
-    <t>小孩</t>
-  </si>
-  <si>
-    <t>小混混</t>
-  </si>
-  <si>
-    <t>小男孩</t>
-  </si>
-  <si>
-    <t>小男孩2</t>
-  </si>
-  <si>
-    <t>小美</t>
-  </si>
-  <si>
-    <t>小花</t>
-  </si>
-  <si>
-    <t>异国女子</t>
-  </si>
-  <si>
-    <t>战斗学者</t>
-  </si>
-  <si>
-    <t>格斗家</t>
-  </si>
-  <si>
-    <t>武士</t>
-  </si>
-  <si>
-    <t>武道女</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游侠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杰克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老公公</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老英雄</t>
-  </si>
-  <si>
-    <t>贵族骑士</t>
-  </si>
-  <si>
-    <t>重装女战士</t>
-  </si>
-  <si>
-    <t>重装战士</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>iconName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldMan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/woman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/man</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/man1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Girl5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/公主</t>
-  </si>
-  <si>
-    <t>Head/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Head/国王</t>
-  </si>
-  <si>
-    <t>Head/天使</t>
-  </si>
-  <si>
-    <t>Head/女仆</t>
-  </si>
-  <si>
-    <t>Head/女骑士</t>
-  </si>
-  <si>
-    <t>Head/渔夫</t>
-  </si>
-  <si>
-    <t>Head/船长</t>
-  </si>
-  <si>
-    <t>Head/水手</t>
-  </si>
-  <si>
-    <t>Head/游侠</t>
-  </si>
-  <si>
-    <t>Head/王子</t>
-  </si>
-  <si>
-    <t>Head/王后</t>
-  </si>
-  <si>
-    <t>Head/管家</t>
-  </si>
-  <si>
-    <t>Head/鸭子</t>
-  </si>
-  <si>
-    <t>Head/绵羊</t>
-  </si>
-  <si>
-    <t>Head/猪</t>
-  </si>
-  <si>
-    <t>Head/奶牛</t>
-  </si>
-  <si>
-    <t>Head/马</t>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/亚度尼斯</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/修女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/公主</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/国王</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/坎蒂丝</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/天使</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女仆</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布拉德利</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布莱兹</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/布蓝达</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/希贝儿</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/帕特里克</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/朵儿洁</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/梅林</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/渔夫</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/船长</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/水手</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/游侠</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/爱格伯特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/牧师</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/王后</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/管家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/艾琳娜</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/莱特</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/金发女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/阿尔杰农</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/重装女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/贵族骑士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老英雄</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/老公公</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武道女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/武士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/格斗家</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/战斗学者</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/异国女子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小花</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小美</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小男孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小混混</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩2</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/官员</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女轻战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女诗人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/女战士</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/商人</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/双辫女孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/匪徒</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者女</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/勇者男</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/制服小孩</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔女郎</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/小丑</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/鸭子</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/绵羊</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/猪</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/奶牛</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/格吉尔</t>
-  </si>
-  <si>
-    <t>Icon/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/玛德琳</t>
-  </si>
-  <si>
     <t>Icon/布莱兹</t>
-  </si>
-  <si>
-    <t>Icon/丝特芬妮</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/修女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/公主</t>
-  </si>
-  <si>
-    <t>Icon/占卜婆婆</t>
-  </si>
-  <si>
-    <t>Icon/国王</t>
-  </si>
-  <si>
-    <t>Icon/天使</t>
-  </si>
-  <si>
-    <t>Icon/朵儿洁</t>
-  </si>
-  <si>
-    <t>Icon/渔夫</t>
-  </si>
-  <si>
-    <t>Icon/船长</t>
-  </si>
-  <si>
-    <t>Icon/水手</t>
-  </si>
-  <si>
-    <t>Icon/游侠</t>
-  </si>
-  <si>
-    <t>Icon/牧师</t>
-  </si>
-  <si>
-    <t>Icon/王子</t>
-  </si>
-  <si>
-    <t>Icon/王后</t>
-  </si>
-  <si>
-    <t>Icon/管家</t>
-  </si>
-  <si>
-    <t>Icon/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/猪</t>
-  </si>
-  <si>
-    <t>Icon/奶牛</t>
-  </si>
-  <si>
-    <t>Prefabs/Character/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/布莱兹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -785,10 +733,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon/女骑士</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -877,26 +821,6 @@
   </si>
   <si>
     <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1168,6 +1092,82 @@
   </si>
   <si>
     <t>山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗伊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1207,7 +1207,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1217,6 +1217,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1235,7 +1241,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1251,6 +1257,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1618,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1653,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>14</v>
@@ -1679,7 +1688,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1688,13 +1697,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1713,8 +1722,8 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A6" s="4" t="s">
-        <v>29</v>
+      <c r="A6" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1723,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -1749,7 +1758,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="B7" s="1">
         <v>4</v>
@@ -1758,13 +1767,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1784,7 +1793,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>306</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -1793,7 +1802,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -1819,7 +1828,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>307</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1828,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>24</v>
@@ -1854,7 +1863,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
@@ -1863,7 +1872,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>25</v>
@@ -1889,7 +1898,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>310</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1898,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1924,7 +1933,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>182</v>
+        <v>309</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1933,13 +1942,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1959,7 +1968,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
@@ -1968,13 +1977,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1993,8 +2002,8 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
-        <v>36</v>
+      <c r="A14" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B14" s="1">
         <v>11</v>
@@ -2003,13 +2012,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2029,7 +2038,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="B15" s="1">
         <v>12</v>
@@ -2038,13 +2047,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2063,8 +2072,8 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>43</v>
+      <c r="A16" s="6" t="s">
+        <v>312</v>
       </c>
       <c r="B16" s="1">
         <v>13</v>
@@ -2073,13 +2082,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -2099,7 +2108,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -2108,13 +2117,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -2133,8 +2142,8 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
-        <v>44</v>
+      <c r="A18" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
@@ -2143,13 +2152,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -2169,7 +2178,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>252</v>
+        <v>313</v>
       </c>
       <c r="B19" s="1">
         <v>14</v>
@@ -2178,13 +2187,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -2204,7 +2213,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B20" s="1">
         <v>17</v>
@@ -2213,13 +2222,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -2239,7 +2248,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="B21" s="1">
         <v>18</v>
@@ -2248,13 +2257,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2274,7 +2283,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B22" s="1">
         <v>19</v>
@@ -2283,13 +2292,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -2307,44 +2316,44 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B23" s="1">
+    <row r="23" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B23" s="6">
         <v>20</v>
       </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>2</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6">
+        <v>2</v>
+      </c>
+      <c r="K23" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B24" s="1">
         <v>21</v>
@@ -2353,13 +2362,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2379,7 +2388,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B25" s="1">
         <v>22</v>
@@ -2388,13 +2397,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2414,7 +2423,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="B26" s="1">
         <v>23</v>
@@ -2423,13 +2432,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2449,7 +2458,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>110</v>
+        <v>317</v>
       </c>
       <c r="B27" s="1">
         <v>24</v>
@@ -2458,13 +2467,13 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2484,7 +2493,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>215</v>
+        <v>318</v>
       </c>
       <c r="B28" s="1">
         <v>25</v>
@@ -2493,13 +2502,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2519,7 +2528,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B29" s="1">
         <v>26</v>
@@ -2528,13 +2537,13 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2554,7 +2563,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B30" s="1">
         <v>27</v>
@@ -2563,13 +2572,13 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2589,7 +2598,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
@@ -2598,13 +2607,13 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2624,7 +2633,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
@@ -2633,13 +2642,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2659,7 +2668,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>256</v>
+        <v>319</v>
       </c>
       <c r="B33" s="1">
         <v>30</v>
@@ -2668,13 +2677,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2694,7 +2703,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>87</v>
+        <v>324</v>
       </c>
       <c r="B34" s="1">
         <v>31</v>
@@ -2703,13 +2712,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2728,8 +2737,8 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A35" s="1" t="s">
-        <v>66</v>
+      <c r="A35" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B35" s="1">
         <v>32</v>
@@ -2738,13 +2747,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -2763,8 +2772,8 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A36" s="1" t="s">
-        <v>67</v>
+      <c r="A36" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B36" s="1">
         <v>33</v>
@@ -2773,13 +2782,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -2798,8 +2807,8 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A37" s="4" t="s">
-        <v>212</v>
+      <c r="A37" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="B37" s="1">
         <v>34</v>
@@ -2808,13 +2817,13 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -2833,8 +2842,8 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A38" s="4" t="s">
-        <v>68</v>
+      <c r="A38" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B38" s="1">
         <v>35</v>
@@ -2843,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -2868,8 +2877,8 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A39" s="4" t="s">
-        <v>210</v>
+      <c r="A39" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="B39" s="1">
         <v>36</v>
@@ -2878,13 +2887,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -2903,8 +2912,8 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A40" s="4" t="s">
-        <v>208</v>
+      <c r="A40" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="B40" s="1">
         <v>37</v>
@@ -2913,13 +2922,13 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -2938,8 +2947,8 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A41" s="4" t="s">
-        <v>206</v>
+      <c r="A41" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -2948,13 +2957,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
@@ -2973,8 +2982,8 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A42" s="4" t="s">
-        <v>204</v>
+      <c r="A42" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="B42" s="1">
         <v>39</v>
@@ -2983,13 +2992,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -3008,8 +3017,8 @@
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A43" s="4" t="s">
-        <v>254</v>
+      <c r="A43" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="B43" s="1">
         <v>40</v>
@@ -3018,13 +3027,13 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
@@ -3044,7 +3053,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B44" s="1">
         <v>41</v>
@@ -3053,7 +3062,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
@@ -3073,7 +3082,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B45" s="1">
         <v>42</v>
@@ -3082,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3102,7 +3111,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B46" s="1">
         <v>43</v>
@@ -3111,7 +3120,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G46" s="1">
         <v>1</v>
@@ -3131,7 +3140,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="B47" s="1">
         <v>44</v>
@@ -3140,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -3160,7 +3169,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B48" s="1">
         <v>45</v>
@@ -3169,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -3189,7 +3198,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B49" s="1">
         <v>46</v>
@@ -3198,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3218,7 +3227,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B50" s="1">
         <v>47</v>
@@ -3227,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3247,7 +3256,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B51" s="1">
         <v>48</v>
@@ -3256,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3276,7 +3285,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B52" s="1">
         <v>49</v>
@@ -3285,7 +3294,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3305,7 +3314,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
@@ -3314,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3334,7 +3343,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B54" s="1">
         <v>51</v>
@@ -3343,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3363,7 +3372,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B55" s="1">
         <v>52</v>
@@ -3372,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G55" s="1">
         <v>1</v>
@@ -3392,7 +3401,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B56" s="1">
         <v>53</v>
@@ -3401,7 +3410,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3421,7 +3430,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B57" s="1">
         <v>54</v>
@@ -3430,7 +3439,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3450,7 +3459,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B58" s="1">
         <v>55</v>
@@ -3459,7 +3468,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -3479,7 +3488,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B59" s="1">
         <v>56</v>
@@ -3488,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -3508,7 +3517,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B60" s="1">
         <v>57</v>
@@ -3517,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3537,7 +3546,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B61" s="1">
         <v>58</v>
@@ -3546,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -3566,7 +3575,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B62" s="1">
         <v>59</v>
@@ -3575,7 +3584,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -3595,7 +3604,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B63" s="1">
         <v>60</v>
@@ -3604,7 +3613,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -3624,7 +3633,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B64" s="1">
         <v>61</v>
@@ -3633,7 +3642,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -3653,7 +3662,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B65" s="1">
         <v>62</v>
@@ -3662,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -3682,7 +3691,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B66" s="1">
         <v>63</v>
@@ -3691,7 +3700,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -3711,7 +3720,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B67" s="1">
         <v>64</v>
@@ -3720,7 +3729,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -3740,7 +3749,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B68" s="1">
         <v>65</v>
@@ -3749,7 +3758,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -3769,7 +3778,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B69" s="1">
         <v>66</v>
@@ -3778,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -3798,7 +3807,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B70" s="1">
         <v>67</v>
@@ -3807,7 +3816,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -3827,7 +3836,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B71" s="1">
         <v>68</v>
@@ -3836,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -3856,7 +3865,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B72" s="1">
         <v>69</v>
@@ -3865,7 +3874,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -3885,7 +3894,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B73" s="1">
         <v>70</v>
@@ -3894,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -3914,7 +3923,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B74" s="1">
         <v>71</v>
@@ -3923,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -3943,7 +3952,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B75" s="1">
         <v>72</v>
@@ -3952,7 +3961,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -3972,7 +3981,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B76" s="1">
         <v>73</v>
@@ -3981,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -4001,7 +4010,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B77" s="1">
         <v>200</v>
@@ -4010,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -4030,7 +4039,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B78" s="1">
         <v>205</v>
@@ -4039,7 +4048,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -4059,7 +4068,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B79" s="1">
         <v>206</v>
@@ -4068,7 +4077,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="G79" s="1">
         <v>1</v>
@@ -4088,7 +4097,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B80" s="1">
         <v>210</v>
@@ -4118,7 +4127,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B81" s="1">
         <v>211</v>
@@ -4148,7 +4157,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B82" s="1">
         <v>212</v>
@@ -4178,7 +4187,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="B83" s="1">
         <v>213</v>
@@ -4187,10 +4196,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="F83" s="1" t="str">
         <f>"Prefabs/Character/"&amp;A83</f>
@@ -4214,7 +4223,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B84" s="1">
         <v>214</v>
@@ -4244,7 +4253,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B85" s="1">
         <v>215</v>
@@ -4274,7 +4283,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B86" s="1">
         <v>216</v>
@@ -4304,7 +4313,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="5" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B87" s="1">
         <v>217</v>
@@ -4334,7 +4343,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="5" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B88" s="1">
         <v>218</v>
@@ -4364,7 +4373,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="5" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B89" s="1">
         <v>219</v>
@@ -4394,7 +4403,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="5" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B90" s="1">
         <v>220</v>
@@ -4433,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -4453,7 +4462,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="B92" s="1">
         <v>3000</v>
@@ -4462,13 +4471,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="G92" s="1">
         <v>2</v>
@@ -4488,7 +4497,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B93" s="1">
         <v>3001</v>
@@ -4497,13 +4506,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="G93" s="1">
         <v>3</v>
@@ -4523,7 +4532,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B94" s="3">
         <v>3002</v>
@@ -4532,13 +4541,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="G94" s="1">
         <v>2</v>
@@ -4558,7 +4567,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="B95" s="3">
         <v>3003</v>
@@ -4567,13 +4576,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G95" s="1">
         <v>3</v>
@@ -4593,7 +4602,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B96" s="3">
         <v>3004</v>
@@ -4602,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="G96" s="1">
         <v>2</v>
@@ -4628,7 +4637,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="B97" s="3">
         <v>3005</v>
@@ -4637,13 +4646,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="G97" s="1">
         <v>3</v>
@@ -4663,7 +4672,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="B98" s="3">
         <v>3006</v>
@@ -4672,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="G98" s="1">
         <v>3</v>
@@ -4698,7 +4707,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="B99" s="3">
         <v>3007</v>
@@ -4707,13 +4716,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G99" s="1">
         <v>4</v>
@@ -4733,7 +4742,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B100" s="3">
         <v>3008</v>
@@ -4742,13 +4751,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="G100" s="1">
         <v>3</v>
@@ -4768,7 +4777,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B101" s="3">
         <v>3009</v>
@@ -4777,13 +4786,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G101" s="1">
         <v>4</v>
@@ -4803,7 +4812,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="B102" s="3">
         <v>3010</v>
@@ -4812,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="G102" s="1">
         <v>3</v>
@@ -4838,7 +4847,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B103" s="3">
         <v>3011</v>
@@ -4847,13 +4856,13 @@
         <v>0</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G103" s="1">
         <v>4</v>
@@ -4873,7 +4882,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="B104" s="3">
         <v>3012</v>
@@ -4882,13 +4891,13 @@
         <v>0</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G104" s="1">
         <v>4</v>
@@ -4908,7 +4917,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="B105" s="3">
         <v>3013</v>
@@ -4917,13 +4926,13 @@
         <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="G105" s="1">
         <v>3</v>
@@ -4943,7 +4952,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="B106" s="3">
         <v>3014</v>
@@ -4952,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="G106" s="1">
         <v>4</v>
@@ -4978,7 +4987,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="B107" s="3">
         <v>3015</v>
@@ -4987,13 +4996,13 @@
         <v>0</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="G107" s="1">
         <v>4</v>
@@ -5013,7 +5022,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="B108" s="3">
         <v>3016</v>
@@ -5022,13 +5031,13 @@
         <v>0</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="G108" s="1">
         <v>3</v>
@@ -5048,7 +5057,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="B109" s="3">
         <v>3017</v>
@@ -5057,13 +5066,13 @@
         <v>0</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="G109" s="1">
         <v>3</v>
@@ -5083,7 +5092,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="B110" s="3">
         <v>3018</v>
@@ -5092,13 +5101,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="G110" s="1">
         <v>4</v>
@@ -5118,7 +5127,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="B111" s="3">
         <v>3019</v>
@@ -5127,13 +5136,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="G111" s="1">
         <v>4</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -316,469 +316,469 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Prefabs/Character/兔子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼奶牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡</t>
+  </si>
+  <si>
+    <t>Head/火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼火鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Character/幼羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼鸭子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊驼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/主角男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/主角女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/NewCharacter/黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男孩路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女孩路人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年轻路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年轻路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老年路人男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老年路人女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>士兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侍者女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Animal/母鸡</t>
+  </si>
+  <si>
+    <t>Icon/Animal/母鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Animal/鸭子</t>
+  </si>
+  <si>
+    <t>Icon/Animal/兔子</t>
+  </si>
+  <si>
+    <t>Icon/Animal/绵羊</t>
+  </si>
+  <si>
+    <t>Icon/Animal/猪</t>
+  </si>
+  <si>
+    <t>Icon/Animal/奶牛</t>
+  </si>
+  <si>
+    <t>Icon/Animal/马</t>
+  </si>
+  <si>
+    <t>Icon/Animal/山羊</t>
+  </si>
+  <si>
+    <t>Icon/Animal/火鸡</t>
+  </si>
+  <si>
+    <t>Icon/Animal/羊驼</t>
+  </si>
+  <si>
     <t>Prefabs/Character/幼兔子</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/兔子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼猪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奶牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼奶牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/奶牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼奶牛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/山羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/山羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼山羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火鸡</t>
-  </si>
-  <si>
-    <t>Head/火鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/火鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼山羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼火鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼火鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/羊驼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/羊驼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼羊驼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Character/幼羊驼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼鸭子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绵羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>羊驼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幼猪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>山羊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/主角男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/主角女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/NewCharacter/黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>男孩路人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女孩路人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年轻路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年轻路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中年路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中年路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老年路人男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老年路人女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>士兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>劳工</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侍者女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/Boy3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Animal/母鸡</t>
-  </si>
-  <si>
-    <t>Icon/Animal/母鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Animal/鸭子</t>
-  </si>
-  <si>
-    <t>Icon/Animal/兔子</t>
-  </si>
-  <si>
-    <t>Icon/Animal/绵羊</t>
-  </si>
-  <si>
-    <t>Icon/Animal/猪</t>
-  </si>
-  <si>
-    <t>Icon/Animal/奶牛</t>
-  </si>
-  <si>
-    <t>Icon/Animal/马</t>
-  </si>
-  <si>
-    <t>Icon/Animal/山羊</t>
-  </si>
-  <si>
-    <t>Icon/Animal/火鸡</t>
-  </si>
-  <si>
-    <t>Icon/Animal/羊驼</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1262,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -1298,7 +1298,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1334,7 +1334,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" s="1">
         <v>5</v>
@@ -1406,7 +1406,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1">
         <v>6</v>
@@ -1442,7 +1442,7 @@
         <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1478,7 +1478,7 @@
         <v>19</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="1">
         <v>8</v>
@@ -1514,7 +1514,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="1">
         <v>9</v>
@@ -1550,7 +1550,7 @@
         <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
@@ -1586,7 +1586,7 @@
         <v>58</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" s="1">
         <v>12</v>
@@ -1622,7 +1622,7 @@
         <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B15" s="1">
         <v>16</v>
@@ -1658,7 +1658,7 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B16" s="1">
         <v>14</v>
@@ -1694,7 +1694,7 @@
         <v>65</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B17" s="1">
         <v>17</v>
@@ -1730,7 +1730,7 @@
         <v>42</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B18" s="1">
         <v>18</v>
@@ -1766,7 +1766,7 @@
         <v>43</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B19" s="1">
         <v>19</v>
@@ -1802,7 +1802,7 @@
         <v>29</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         <v>30</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -1874,7 +1874,7 @@
         <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -1910,7 +1910,7 @@
         <v>33</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B23" s="1">
         <v>23</v>
@@ -1946,7 +1946,7 @@
         <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1">
         <v>24</v>
@@ -1982,7 +1982,7 @@
         <v>61</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="1">
         <v>25</v>
@@ -2018,7 +2018,7 @@
         <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -2090,7 +2090,7 @@
         <v>45</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B28" s="1">
         <v>28</v>
@@ -2126,7 +2126,7 @@
         <v>46</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B29" s="1">
         <v>29</v>
@@ -2162,7 +2162,7 @@
         <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" s="1">
         <v>30</v>
@@ -2198,7 +2198,7 @@
         <v>36</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B31" s="1">
         <v>31</v>
@@ -2234,7 +2234,7 @@
         <v>63</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B32" s="1">
         <v>34</v>
@@ -2267,10 +2267,10 @@
         <v>Icon/Character/瓦尔特</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B33" s="1">
         <v>35</v>
@@ -2306,7 +2306,7 @@
         <v>48</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B34" s="1">
         <v>36</v>
@@ -2342,7 +2342,7 @@
         <v>37</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" s="1">
         <v>37</v>
@@ -2378,7 +2378,7 @@
         <v>38</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B36" s="1">
         <v>38</v>
@@ -2414,7 +2414,7 @@
         <v>62</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
@@ -2434,7 +2434,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B37" s="1">
         <v>39</v>
@@ -2450,7 +2450,7 @@
         <v>39</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G37" s="1">
         <v>1</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" s="1">
         <v>40</v>
@@ -2486,7 +2486,7 @@
         <v>40</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B39" s="1">
         <v>50</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B40" s="1">
         <v>51</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B41" s="1">
         <v>52</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B42" s="1">
         <v>53</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B43" s="1">
         <v>54</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B44" s="1">
         <v>55</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B45" s="1">
         <v>56</v>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B46" s="1">
         <v>57</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B47" s="1">
         <v>58</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B48" s="1">
         <v>59</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="1">
         <v>60</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="1">
         <v>61</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" s="1">
         <v>62</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B52" s="1">
         <v>213</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="1">
         <v>3000</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>69</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B54" s="1">
         <v>3001</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>69</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B55" s="3">
         <v>3002</v>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>73</v>
@@ -3099,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>49</v>
@@ -3134,13 +3134,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -3169,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B59" s="3">
         <v>3006</v>
@@ -3204,13 +3204,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>50</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G59" s="1">
         <v>3</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B60" s="3">
         <v>3007</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>50</v>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B61" s="3">
         <v>3008</v>
@@ -3274,13 +3274,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G61" s="1">
         <v>3</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B62" s="3">
         <v>3009</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>51</v>
@@ -3335,7 +3335,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B63" s="3">
         <v>3010</v>
@@ -3344,13 +3344,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="G63" s="1">
         <v>3</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B64" s="3">
         <v>3011</v>
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>52</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" s="3">
         <v>3012</v>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G65" s="1">
         <v>4</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B66" s="3">
         <v>3013</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B67" s="3">
         <v>3014</v>
@@ -3484,13 +3484,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B68" s="3">
         <v>3015</v>
@@ -3519,13 +3519,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="G68" s="1">
         <v>4</v>
@@ -3545,7 +3545,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B69" s="3">
         <v>3016</v>
@@ -3554,13 +3554,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G69" s="1">
         <v>3</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B70" s="3">
         <v>3017</v>
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="G70" s="1">
         <v>3</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B71" s="3">
         <v>3018</v>
@@ -3624,13 +3624,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G71" s="1">
         <v>4</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B72" s="3">
         <v>3019</v>
@@ -3659,13 +3659,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="G72" s="1">
         <v>4</v>

--- a/Datas/CharacterData.xlsx
+++ b/Datas/CharacterData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory - Copy\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\RuneFactory\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="198">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -1362,9 +1362,8 @@
       <c r="C7" s="1">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Icon/Character/马</v>
+      <c r="D7" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>66</v>
